--- a/data/Chains Course Catalog.xlsx
+++ b/data/Chains Course Catalog.xlsx
@@ -436,7 +436,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H52"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -579,11 +579,29 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>150</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>None (0/150) — no compliant public per-hole source; users add pars in-app</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>3</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Pass 1: top 150 of 169 PDGA×DGS cross-verified courses (318 DGS-listed total). 19 verified remain — finish next pass.</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -1558,8 +1576,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K624"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:K774"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="41" customWidth="1" min="2" max="2"/>
@@ -29997,6 +30015,6156 @@
         </is>
       </c>
     </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>in-lemon-lake-county-park-blue</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>Lemon Lake County Park - Blue</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>Crown Point</t>
+        </is>
+      </c>
+      <c r="E625" t="n">
+        <v>20</v>
+      </c>
+      <c r="H625" t="n">
+        <v>41.4379352</v>
+      </c>
+      <c r="I625" t="n">
+        <v>-87.3797938</v>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1016/lemon-lake-county-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>in-rogers-lakewood-park</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>Rogers Lakewood Park</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Valparaiso</t>
+        </is>
+      </c>
+      <c r="E626" t="n">
+        <v>24</v>
+      </c>
+      <c r="H626" t="n">
+        <v>41.467632</v>
+      </c>
+      <c r="I626" t="n">
+        <v>-87.10453320000001</v>
+      </c>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1055/rogers-lakewood-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>in-george-wilson-park</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>George Wilson Park</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Mishawaka</t>
+        </is>
+      </c>
+      <c r="E627" t="n">
+        <v>18</v>
+      </c>
+      <c r="H627" t="n">
+        <v>41.6457488</v>
+      </c>
+      <c r="I627" t="n">
+        <v>-86.1591523</v>
+      </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1038/george-wilson-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>in-rum-village-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>Rum Village Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>South Bend</t>
+        </is>
+      </c>
+      <c r="E628" t="n">
+        <v>24</v>
+      </c>
+      <c r="H628" t="n">
+        <v>41.6553816</v>
+      </c>
+      <c r="I628" t="n">
+        <v>-86.2482643</v>
+      </c>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1051/rum-village-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>in-shoaff-park</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>Shoaff Park</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>Fort Wayne</t>
+        </is>
+      </c>
+      <c r="E629" t="n">
+        <v>24</v>
+      </c>
+      <c r="H629" t="n">
+        <v>41.1411621</v>
+      </c>
+      <c r="I629" t="n">
+        <v>-85.05502490000001</v>
+      </c>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1021/shoaff-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>in-boylan-acres-arduous</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>Boylan Acres Arduous</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>Monrovia</t>
+        </is>
+      </c>
+      <c r="E630" t="n">
+        <v>18</v>
+      </c>
+      <c r="H630" t="n">
+        <v>39.5610087</v>
+      </c>
+      <c r="I630" t="n">
+        <v>-86.5035618</v>
+      </c>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/7842/boylan-acres)</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>in-hazel-landing-park</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>Hazel Landing Park</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>Carmel</t>
+        </is>
+      </c>
+      <c r="E631" t="n">
+        <v>18</v>
+      </c>
+      <c r="H631" t="n">
+        <v>39.9363792</v>
+      </c>
+      <c r="I631" t="n">
+        <v>-86.13184200000001</v>
+      </c>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/4098/hazel-landing-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>in-honey-bear-hollow-campgrounds</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Honey Bear Hollow Campgrounds</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E632" t="n">
+        <v>18</v>
+      </c>
+      <c r="H632" t="n">
+        <v>40.7483602</v>
+      </c>
+      <c r="I632" t="n">
+        <v>-86.0851083</v>
+      </c>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1045/honeybear-hollow-campgrounds)</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>in-wabash-city-park</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>Wabash City Park</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Wabash</t>
+        </is>
+      </c>
+      <c r="E633" t="n">
+        <v>18</v>
+      </c>
+      <c r="H633" t="n">
+        <v>40.7991542</v>
+      </c>
+      <c r="I633" t="n">
+        <v>-85.8352972</v>
+      </c>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/2980/wabash-city-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>in-mesker-park</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>Mesker Park</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>Evansville</t>
+        </is>
+      </c>
+      <c r="E634" t="n">
+        <v>18</v>
+      </c>
+      <c r="H634" t="n">
+        <v>38.0086976</v>
+      </c>
+      <c r="I634" t="n">
+        <v>-87.5760836</v>
+      </c>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1019/mesker-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>in-george-washington-park</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>George Washington Park</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Indianapolis</t>
+        </is>
+      </c>
+      <c r="E635" t="n">
+        <v>18</v>
+      </c>
+      <c r="H635" t="n">
+        <v>39.8083049</v>
+      </c>
+      <c r="I635" t="n">
+        <v>-86.1002981</v>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1028/george-washington-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>in-dr-james-a-dillon-park</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>Dr. James A. Dillon Park</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Noblesville</t>
+        </is>
+      </c>
+      <c r="E636" t="n">
+        <v>18</v>
+      </c>
+      <c r="H636" t="n">
+        <v>40.0330476</v>
+      </c>
+      <c r="I636" t="n">
+        <v>-85.9850161</v>
+      </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/3789/dr-james-a-dillon-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>in-elwood-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>Elwood Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>Elwood</t>
+        </is>
+      </c>
+      <c r="E637" t="n">
+        <v>18</v>
+      </c>
+      <c r="H637" t="n">
+        <v>40.2809202</v>
+      </c>
+      <c r="I637" t="n">
+        <v>-85.8405072</v>
+      </c>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/3311/elwood-dgc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>in-memorial-hills-disc-golf</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>Memorial Hills Disc Golf</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Huntington</t>
+        </is>
+      </c>
+      <c r="E638" t="n">
+        <v>18</v>
+      </c>
+      <c r="H638" t="n">
+        <v>40.8778613</v>
+      </c>
+      <c r="I638" t="n">
+        <v>-85.5000433</v>
+      </c>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/3833/memorial-hills)</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>in-west-swinney-park</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>West Swinney Park</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>Fort Wayne</t>
+        </is>
+      </c>
+      <c r="E639" t="n">
+        <v>18</v>
+      </c>
+      <c r="H639" t="n">
+        <v>41.0946552</v>
+      </c>
+      <c r="I639" t="n">
+        <v>-85.1657555</v>
+      </c>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1022/west-swinney-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>in-brown-county-country-club</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Brown County Country Club</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Nashville</t>
+        </is>
+      </c>
+      <c r="E640" t="n">
+        <v>24</v>
+      </c>
+      <c r="H640" t="n">
+        <v>39.190758</v>
+      </c>
+      <c r="I640" t="n">
+        <v>-86.2532461</v>
+      </c>
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/5457/brown-county-country-club)</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>in-deming-park-north</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Deming Park - North</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Terre Haute</t>
+        </is>
+      </c>
+      <c r="E641" t="n">
+        <v>18</v>
+      </c>
+      <c r="H641" t="n">
+        <v>39.4722944</v>
+      </c>
+      <c r="I641" t="n">
+        <v>-87.33971289999999</v>
+      </c>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1052/deming-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>in-ferrettie-baugo-creek-county-park</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Ferrettie Baugo Creek County Park</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Osceola</t>
+        </is>
+      </c>
+      <c r="E642" t="n">
+        <v>18</v>
+      </c>
+      <c r="H642" t="n">
+        <v>41.6790048</v>
+      </c>
+      <c r="I642" t="n">
+        <v>-86.07638129999999</v>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1043/ferrettie-baugo-creek-county-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>in-tillman-park-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Tillman Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Fort Wayne</t>
+        </is>
+      </c>
+      <c r="E643" t="n">
+        <v>19</v>
+      </c>
+      <c r="H643" t="n">
+        <v>41.0166691</v>
+      </c>
+      <c r="I643" t="n">
+        <v>-85.09413619999999</v>
+      </c>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/5163/tillman-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>in-brookside-park</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Brookside Park</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Indianapolis</t>
+        </is>
+      </c>
+      <c r="E644" t="n">
+        <v>24</v>
+      </c>
+      <c r="H644" t="n">
+        <v>39.7751621</v>
+      </c>
+      <c r="I644" t="n">
+        <v>-86.1080532</v>
+      </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1027/brookside-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>in-maconaquah-park</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Maconaquah Park</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E645" t="n">
+        <v>18</v>
+      </c>
+      <c r="H645" t="n">
+        <v>40.7483602</v>
+      </c>
+      <c r="I645" t="n">
+        <v>-86.0851083</v>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1046/maconaquah-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>in-mississinewa-state-park</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Mississinewa State Park</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E646" t="n">
+        <v>24</v>
+      </c>
+      <c r="H646" t="n">
+        <v>40.7483602</v>
+      </c>
+      <c r="I646" t="n">
+        <v>-86.0851083</v>
+      </c>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1047/mississinewa-state-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>in-the-hill-at-northview-church</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>The Hill at Northview Church</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Carmel</t>
+        </is>
+      </c>
+      <c r="E647" t="n">
+        <v>18</v>
+      </c>
+      <c r="H647" t="n">
+        <v>39.9678751</v>
+      </c>
+      <c r="I647" t="n">
+        <v>-86.0887731</v>
+      </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/3810/northview-church)</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>in-avon-town-hall-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>Avon Town Hall Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>Avon</t>
+        </is>
+      </c>
+      <c r="E648" t="n">
+        <v>18</v>
+      </c>
+      <c r="H648" t="n">
+        <v>39.7655618</v>
+      </c>
+      <c r="I648" t="n">
+        <v>-86.3924021</v>
+      </c>
+      <c r="J648" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1006/avon-town-hall)</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>in-cedar-grove-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Cedar Grove Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>Sunman</t>
+        </is>
+      </c>
+      <c r="E649" t="n">
+        <v>18</v>
+      </c>
+      <c r="H649" t="n">
+        <v>39.2400736</v>
+      </c>
+      <c r="I649" t="n">
+        <v>-85.0733314</v>
+      </c>
+      <c r="J649" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/8059/cedar-grove-dgc-private)</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>in-east-swinney-park</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>East Swinney Park</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>Fort Wayne</t>
+        </is>
+      </c>
+      <c r="E650" t="n">
+        <v>18</v>
+      </c>
+      <c r="H650" t="n">
+        <v>41.0946552</v>
+      </c>
+      <c r="I650" t="n">
+        <v>-85.1657555</v>
+      </c>
+      <c r="J650" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1020/east-swinney-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>in-crestmont</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>Crestmont</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>Bloomington</t>
+        </is>
+      </c>
+      <c r="E651" t="n">
+        <v>18</v>
+      </c>
+      <c r="H651" t="n">
+        <v>39.1999163</v>
+      </c>
+      <c r="I651" t="n">
+        <v>-86.5763188</v>
+      </c>
+      <c r="J651" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1008/crestmont)</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>in-eagle-valley-at-usi</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>Eagle Valley at USI</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>Evansville</t>
+        </is>
+      </c>
+      <c r="E652" t="n">
+        <v>18</v>
+      </c>
+      <c r="H652" t="n">
+        <v>37.9681486</v>
+      </c>
+      <c r="I652" t="n">
+        <v>-87.65783639999999</v>
+      </c>
+      <c r="J652" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1018/eagle-valley-at-usi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>in-purdue-northwest</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Purdue Northwest</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>Westville</t>
+        </is>
+      </c>
+      <c r="E653" t="n">
+        <v>18</v>
+      </c>
+      <c r="H653" t="n">
+        <v>41.5822309</v>
+      </c>
+      <c r="I653" t="n">
+        <v>-86.9071414</v>
+      </c>
+      <c r="J653" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/3747/purdue-north-central)</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>in-sahm-park</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>Sahm Park</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>Indianapolis</t>
+        </is>
+      </c>
+      <c r="E654" t="n">
+        <v>18</v>
+      </c>
+      <c r="H654" t="n">
+        <v>39.9033361</v>
+      </c>
+      <c r="I654" t="n">
+        <v>-86.0707941</v>
+      </c>
+      <c r="J654" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1030/sahm-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>in-morse-beach-park</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>Morse Beach Park</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>Noblesville</t>
+        </is>
+      </c>
+      <c r="E655" t="n">
+        <v>9</v>
+      </c>
+      <c r="H655" t="n">
+        <v>40.0330476</v>
+      </c>
+      <c r="I655" t="n">
+        <v>-85.9850161</v>
+      </c>
+      <c r="J655" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1042/morse-beach-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>in-prides-creek-park-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>Prides Creek Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>Petersburg</t>
+        </is>
+      </c>
+      <c r="E656" t="n">
+        <v>18</v>
+      </c>
+      <c r="H656" t="n">
+        <v>38.4669518</v>
+      </c>
+      <c r="I656" t="n">
+        <v>-87.2930065</v>
+      </c>
+      <c r="J656" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/4284/prides-creek-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>in-buffalo-trace-park</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>Buffalo Trace Park</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Palmyra</t>
+        </is>
+      </c>
+      <c r="E657" t="n">
+        <v>18</v>
+      </c>
+      <c r="H657" t="n">
+        <v>38.4042545</v>
+      </c>
+      <c r="I657" t="n">
+        <v>-86.0883133</v>
+      </c>
+      <c r="J657" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1044/buffalo-trace-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>in-france-park</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>France Park</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Logansport</t>
+        </is>
+      </c>
+      <c r="E658" t="n">
+        <v>18</v>
+      </c>
+      <c r="H658" t="n">
+        <v>40.7559003</v>
+      </c>
+      <c r="I658" t="n">
+        <v>-86.3574675</v>
+      </c>
+      <c r="J658" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1036/france-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>in-mt-gilead-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>Mt. Gilead Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>Mooresville</t>
+        </is>
+      </c>
+      <c r="E659" t="n">
+        <v>18</v>
+      </c>
+      <c r="H659" t="n">
+        <v>39.5951977</v>
+      </c>
+      <c r="I659" t="n">
+        <v>-86.3724433</v>
+      </c>
+      <c r="J659" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/3742/mt-gilead-church)</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>in-northwestway-park-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>Northwestway Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Indianapolis</t>
+        </is>
+      </c>
+      <c r="E660" t="n">
+        <v>18</v>
+      </c>
+      <c r="H660" t="n">
+        <v>39.8922237</v>
+      </c>
+      <c r="I660" t="n">
+        <v>-86.22606089999999</v>
+      </c>
+      <c r="J660" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1029/northwestway-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>in-boondocks-farm-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>Boondocks Farm Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>Knightstown</t>
+        </is>
+      </c>
+      <c r="E661" t="n">
+        <v>18</v>
+      </c>
+      <c r="H661" t="n">
+        <v>39.8018835</v>
+      </c>
+      <c r="I661" t="n">
+        <v>-85.5173205</v>
+      </c>
+      <c r="J661" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1031/boondocks-farms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>in-countryside-park</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>Countryside Park</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>Portage</t>
+        </is>
+      </c>
+      <c r="E662" t="n">
+        <v>21</v>
+      </c>
+      <c r="H662" t="n">
+        <v>41.5774382</v>
+      </c>
+      <c r="I662" t="n">
+        <v>-87.1826799</v>
+      </c>
+      <c r="J662" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/4693/countryside-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>in-camp-cullom-youth-camp-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>Camp Cullom Youth Camp Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>Frankfort</t>
+        </is>
+      </c>
+      <c r="E663" t="n">
+        <v>24</v>
+      </c>
+      <c r="H663" t="n">
+        <v>40.3223146</v>
+      </c>
+      <c r="I663" t="n">
+        <v>-86.3847863</v>
+      </c>
+      <c r="J663" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/3312/camp-cullom)</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>in-delt-church-park</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>Delt Church Park</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>Wolcottville</t>
+        </is>
+      </c>
+      <c r="E664" t="n">
+        <v>18</v>
+      </c>
+      <c r="H664" t="n">
+        <v>41.5490281</v>
+      </c>
+      <c r="I664" t="n">
+        <v>-85.3609818</v>
+      </c>
+      <c r="J664" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/3864/delt-church-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>in-highland-park</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Highland Park</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>Kokomo</t>
+        </is>
+      </c>
+      <c r="E665" t="n">
+        <v>18</v>
+      </c>
+      <c r="H665" t="n">
+        <v>40.4496072</v>
+      </c>
+      <c r="I665" t="n">
+        <v>-86.1315323</v>
+      </c>
+      <c r="J665" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1032/highland-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>in-matter-park-disc-golf</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>Matter Park Disc Golf</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>Marion</t>
+        </is>
+      </c>
+      <c r="E666" t="n">
+        <v>24</v>
+      </c>
+      <c r="H666" t="n">
+        <v>40.5791713</v>
+      </c>
+      <c r="I666" t="n">
+        <v>-85.6714353</v>
+      </c>
+      <c r="J666" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/3095/matter-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>in-murdock-park</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Murdock Park</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Lafayette</t>
+        </is>
+      </c>
+      <c r="E667" t="n">
+        <v>18</v>
+      </c>
+      <c r="H667" t="n">
+        <v>40.4169481</v>
+      </c>
+      <c r="I667" t="n">
+        <v>-86.82331809999999</v>
+      </c>
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1034/murdock-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>in-woodmere-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>Woodmere Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>Evansville</t>
+        </is>
+      </c>
+      <c r="E668" t="n">
+        <v>18</v>
+      </c>
+      <c r="H668" t="n">
+        <v>37.9681801</v>
+      </c>
+      <c r="I668" t="n">
+        <v>-87.52438739999999</v>
+      </c>
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/3762/woodmere-dgc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>in-milligan-park-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Milligan Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Crawfordsville</t>
+        </is>
+      </c>
+      <c r="E669" t="n">
+        <v>22</v>
+      </c>
+      <c r="H669" t="n">
+        <v>40.0270065</v>
+      </c>
+      <c r="I669" t="n">
+        <v>-86.9141218</v>
+      </c>
+      <c r="J669" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1014/milligan-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>in-forest-park-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Forest Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E670" t="n">
+        <v>18</v>
+      </c>
+      <c r="H670" t="n">
+        <v>39.5100384</v>
+      </c>
+      <c r="I670" t="n">
+        <v>-87.1344464</v>
+      </c>
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1011/forest-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>in-lapping-memorial-park</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Lapping Memorial Park</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Clarksville</t>
+        </is>
+      </c>
+      <c r="E671" t="n">
+        <v>18</v>
+      </c>
+      <c r="H671" t="n">
+        <v>38.3084978</v>
+      </c>
+      <c r="I671" t="n">
+        <v>-85.76756810000001</v>
+      </c>
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/5625/lapping-memorial-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>in-moser-park</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Moser Park</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>Fort Wayne (New Haven)</t>
+        </is>
+      </c>
+      <c r="E672" t="n">
+        <v>18</v>
+      </c>
+      <c r="H672" t="n">
+        <v>41.0721662</v>
+      </c>
+      <c r="I672" t="n">
+        <v>-85.0089409</v>
+      </c>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1023/moser-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>in-commons-park-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Commons Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="E673" t="n">
+        <v>18</v>
+      </c>
+      <c r="H673" t="n">
+        <v>41.6651567</v>
+      </c>
+      <c r="I673" t="n">
+        <v>-85.0269715</v>
+      </c>
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/7527/commons-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>in-deer-run-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>Deer Run Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>Nashville</t>
+        </is>
+      </c>
+      <c r="E674" t="n">
+        <v>18</v>
+      </c>
+      <c r="H674" t="n">
+        <v>39.190758</v>
+      </c>
+      <c r="I674" t="n">
+        <v>-86.2532461</v>
+      </c>
+      <c r="J674" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/5382/deer-run-dgc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>in-freedom-park-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>Freedom Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Greenwood</t>
+        </is>
+      </c>
+      <c r="E675" t="n">
+        <v>9</v>
+      </c>
+      <c r="H675" t="n">
+        <v>39.5949282</v>
+      </c>
+      <c r="I675" t="n">
+        <v>-86.1283701</v>
+      </c>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/3175/freedom-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>in-karst-farm-park</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Karst Farm Park</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>Bloomington</t>
+        </is>
+      </c>
+      <c r="E676" t="n">
+        <v>18</v>
+      </c>
+      <c r="H676" t="n">
+        <v>39.1441045</v>
+      </c>
+      <c r="I676" t="n">
+        <v>-86.5038139</v>
+      </c>
+      <c r="J676" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1009/karst-farm-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>in-kenney-park</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>Kenney Park</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>Ligonier</t>
+        </is>
+      </c>
+      <c r="E677" t="n">
+        <v>18</v>
+      </c>
+      <c r="H677" t="n">
+        <v>41.4486326</v>
+      </c>
+      <c r="I677" t="n">
+        <v>-85.5741689</v>
+      </c>
+      <c r="J677" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/8413/kenney-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>in-patoka-lake-state-rec-area</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>Patoka Lake State Rec Area</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>Birdseye</t>
+        </is>
+      </c>
+      <c r="E678" t="n">
+        <v>18</v>
+      </c>
+      <c r="H678" t="n">
+        <v>38.3138561</v>
+      </c>
+      <c r="I678" t="n">
+        <v>-86.7339475</v>
+      </c>
+      <c r="J678" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1007/patoka-lake-state-rec-area)</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>in-w-s-gibbs-memorial-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>W.S. Gibbs Memorial Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>Danville</t>
+        </is>
+      </c>
+      <c r="E679" t="n">
+        <v>18</v>
+      </c>
+      <c r="H679" t="n">
+        <v>39.7620414</v>
+      </c>
+      <c r="I679" t="n">
+        <v>-86.5309725</v>
+      </c>
+      <c r="J679" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/9086/w-s-gibbs-memorial-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>in-big-walnut-sports-park</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>Big Walnut Sports Park</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>Greencastle</t>
+        </is>
+      </c>
+      <c r="E680" t="n">
+        <v>19</v>
+      </c>
+      <c r="H680" t="n">
+        <v>39.6399361</v>
+      </c>
+      <c r="I680" t="n">
+        <v>-86.8010874</v>
+      </c>
+      <c r="J680" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/3357/big-walnut-sports-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>in-chapel-grove-at-concordia-seminary</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>Chapel Grove at Concordia Seminary</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>Fort Wayne</t>
+        </is>
+      </c>
+      <c r="E681" t="n">
+        <v>18</v>
+      </c>
+      <c r="H681" t="n">
+        <v>41.1530753</v>
+      </c>
+      <c r="I681" t="n">
+        <v>-85.1262957</v>
+      </c>
+      <c r="J681" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/10963/chapel-grove-dgc-concordia-seminary)</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>in-cumberland-park</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>Cumberland Park</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>Fishers</t>
+        </is>
+      </c>
+      <c r="E682" t="n">
+        <v>9</v>
+      </c>
+      <c r="H682" t="n">
+        <v>39.9576262</v>
+      </c>
+      <c r="I682" t="n">
+        <v>-86.0269758</v>
+      </c>
+      <c r="J682" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/3788/cumberland-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>in-edgewood-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>Edgewood Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>Ellettsville</t>
+        </is>
+      </c>
+      <c r="E683" t="n">
+        <v>9</v>
+      </c>
+      <c r="H683" t="n">
+        <v>39.2380598</v>
+      </c>
+      <c r="I683" t="n">
+        <v>-86.62073940000001</v>
+      </c>
+      <c r="J683" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/4483/edgewood-dgc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>in-falls-park</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>Falls Park</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>Pendelton</t>
+        </is>
+      </c>
+      <c r="E684" t="n">
+        <v>9</v>
+      </c>
+      <c r="H684" t="n">
+        <v>39.9955468</v>
+      </c>
+      <c r="I684" t="n">
+        <v>-85.7480365</v>
+      </c>
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/4539/falls-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>in-mcculloch-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>McCulloch Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>Muncie</t>
+        </is>
+      </c>
+      <c r="E685" t="n">
+        <v>18</v>
+      </c>
+      <c r="H685" t="n">
+        <v>40.1992554</v>
+      </c>
+      <c r="I685" t="n">
+        <v>-85.4084735</v>
+      </c>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1040/mcculloch-park-disc-golf-course)</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>in-princeton-country-club</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Princeton Country Club</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>Patoka</t>
+        </is>
+      </c>
+      <c r="E686" t="n">
+        <v>18</v>
+      </c>
+      <c r="H686" t="n">
+        <v>38.4068928</v>
+      </c>
+      <c r="I686" t="n">
+        <v>-87.5864775</v>
+      </c>
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/6640/princeton-country-club)</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>in-tower-park-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>Tower Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Warren</t>
+        </is>
+      </c>
+      <c r="E687" t="n">
+        <v>9</v>
+      </c>
+      <c r="H687" t="n">
+        <v>40.685324</v>
+      </c>
+      <c r="I687" t="n">
+        <v>-85.43149529999999</v>
+      </c>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/5039/tower-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>in-akron-community-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>Akron Community Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>Akron</t>
+        </is>
+      </c>
+      <c r="E688" t="n">
+        <v>18</v>
+      </c>
+      <c r="H688" t="n">
+        <v>41.0182426</v>
+      </c>
+      <c r="I688" t="n">
+        <v>-86.037931</v>
+      </c>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/5990/akron-community-dgc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>in-haubstadt-johnson-township-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>Haubstadt Johnson Township Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>Haubstadt</t>
+        </is>
+      </c>
+      <c r="E689" t="n">
+        <v>18</v>
+      </c>
+      <c r="H689" t="n">
+        <v>38.1781957</v>
+      </c>
+      <c r="I689" t="n">
+        <v>-87.5861317</v>
+      </c>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/7772/haubstadt-johnson-township-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>in-hawthorne-park</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Hawthorne Park</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="E690" t="n">
+        <v>9</v>
+      </c>
+      <c r="H690" t="n">
+        <v>41.6106071</v>
+      </c>
+      <c r="I690" t="n">
+        <v>-87.05998169999999</v>
+      </c>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/4692/hawthorne-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>in-lawrence-w-inlow-park</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Lawrence W Inlow Park</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Carmel</t>
+        </is>
+      </c>
+      <c r="E691" t="n">
+        <v>9</v>
+      </c>
+      <c r="H691" t="n">
+        <v>39.9678751</v>
+      </c>
+      <c r="I691" t="n">
+        <v>-86.0887731</v>
+      </c>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/4702/lawrence-w-inlow-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>in-lucerne-park</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>Lucerne Park</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Warsaw</t>
+        </is>
+      </c>
+      <c r="E692" t="n">
+        <v>9</v>
+      </c>
+      <c r="H692" t="n">
+        <v>41.2466501</v>
+      </c>
+      <c r="I692" t="n">
+        <v>-85.84866529999999</v>
+      </c>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/5113/lucerne-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>in-maxton-park</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>Maxton Park</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>Butler</t>
+        </is>
+      </c>
+      <c r="E693" t="n">
+        <v>18</v>
+      </c>
+      <c r="H693" t="n">
+        <v>41.4145052</v>
+      </c>
+      <c r="I693" t="n">
+        <v>-84.88115209999999</v>
+      </c>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/8488/maxton-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>in-eckhart-park</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>Eckhart Park</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>Auburn</t>
+        </is>
+      </c>
+      <c r="E694" t="n">
+        <v>9</v>
+      </c>
+      <c r="H694" t="n">
+        <v>41.3299846</v>
+      </c>
+      <c r="I694" t="n">
+        <v>-85.0532443</v>
+      </c>
+      <c r="J694" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/6097/eckhart-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>in-goodrich-park-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>Goodrich Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Winchester</t>
+        </is>
+      </c>
+      <c r="E695" t="n">
+        <v>27</v>
+      </c>
+      <c r="H695" t="n">
+        <v>40.1653968</v>
+      </c>
+      <c r="I695" t="n">
+        <v>-84.9756086</v>
+      </c>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/6252/goodrich-dgc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>in-niehaus-park-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>Niehaus Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Huntingburg</t>
+        </is>
+      </c>
+      <c r="E696" t="n">
+        <v>18</v>
+      </c>
+      <c r="H696" t="n">
+        <v>38.2969792</v>
+      </c>
+      <c r="I696" t="n">
+        <v>-86.963842</v>
+      </c>
+      <c r="J696" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/7167/niehaus-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>in-northwest-community-park-at-bethesda-baptist-church</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>Northwest Community Park at Bethesda Baptist Church</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>Brownsburg</t>
+        </is>
+      </c>
+      <c r="E697" t="n">
+        <v>18</v>
+      </c>
+      <c r="H697" t="n">
+        <v>39.8432197</v>
+      </c>
+      <c r="I697" t="n">
+        <v>-86.3892312</v>
+      </c>
+      <c r="J697" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/5781/northwest-community-park-bethesda-baptist)</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>in-rockville-lake-park</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>Rockville Lake Park</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>Rockville</t>
+        </is>
+      </c>
+      <c r="E698" t="n">
+        <v>18</v>
+      </c>
+      <c r="H698" t="n">
+        <v>39.7647491</v>
+      </c>
+      <c r="I698" t="n">
+        <v>-87.2243898</v>
+      </c>
+      <c r="J698" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/3932/rockville-lake-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>in-the-lodge-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>The Lodge Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Syracuse</t>
+        </is>
+      </c>
+      <c r="E699" t="n">
+        <v>18</v>
+      </c>
+      <c r="H699" t="n">
+        <v>41.4064074</v>
+      </c>
+      <c r="I699" t="n">
+        <v>-85.7367546</v>
+      </c>
+      <c r="J699" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/8212/the-lodge-dgc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>in-westfield-lions-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>Westfield Lions Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>Westfield</t>
+        </is>
+      </c>
+      <c r="E700" t="n">
+        <v>9</v>
+      </c>
+      <c r="H700" t="n">
+        <v>40.0377277</v>
+      </c>
+      <c r="I700" t="n">
+        <v>-86.1627163</v>
+      </c>
+      <c r="J700" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/5258/westfield-lions-dgc-asa-bales)</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>in-cook-station-park</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>Cook Station Park</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>Millersburg</t>
+        </is>
+      </c>
+      <c r="E701" t="n">
+        <v>9</v>
+      </c>
+      <c r="H701" t="n">
+        <v>41.514075</v>
+      </c>
+      <c r="I701" t="n">
+        <v>-85.69469599999999</v>
+      </c>
+      <c r="J701" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/4996/cook-station-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>in-county-farm-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>County Farm Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="E702" t="n">
+        <v>18</v>
+      </c>
+      <c r="H702" t="n">
+        <v>39.0689275</v>
+      </c>
+      <c r="I702" t="n">
+        <v>-84.9436072</v>
+      </c>
+      <c r="J702" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/4557/county-farm-dgc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>in-grassy-creek-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>Grassy Creek Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>New Whiteland</t>
+        </is>
+      </c>
+      <c r="E703" t="n">
+        <v>18</v>
+      </c>
+      <c r="H703" t="n">
+        <v>39.5616279</v>
+      </c>
+      <c r="I703" t="n">
+        <v>-86.08775660000001</v>
+      </c>
+      <c r="J703" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/4816/grassy-creek-dgc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>in-longley-park</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>Longley Park</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="E704" t="n">
+        <v>18</v>
+      </c>
+      <c r="H704" t="n">
+        <v>40.0431855</v>
+      </c>
+      <c r="I704" t="n">
+        <v>-86.4580266</v>
+      </c>
+      <c r="J704" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/2849/longley-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>in-salamonie-lake-disc-golf</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>Salamonie Lake Disc Golf</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>Andrews</t>
+        </is>
+      </c>
+      <c r="E705" t="n">
+        <v>25</v>
+      </c>
+      <c r="H705" t="n">
+        <v>40.8458387</v>
+      </c>
+      <c r="I705" t="n">
+        <v>-85.64502640000001</v>
+      </c>
+      <c r="J705" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/8183/salamonie-lake)</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>in-the-masters-disc-golf-course-at-calvary-baptist</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>The Masters Disc Golf Course at Calvary Baptist</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>Plainfield</t>
+        </is>
+      </c>
+      <c r="E706" t="n">
+        <v>9</v>
+      </c>
+      <c r="H706" t="n">
+        <v>39.702961</v>
+      </c>
+      <c r="I706" t="n">
+        <v>-86.387743</v>
+      </c>
+      <c r="J706" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/3352/calvary-baptist-church)</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>in-altstadt-acres</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>Altstadt Acres</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>Huntingburg</t>
+        </is>
+      </c>
+      <c r="E707" t="n">
+        <v>18</v>
+      </c>
+      <c r="H707" t="n">
+        <v>38.2979462</v>
+      </c>
+      <c r="I707" t="n">
+        <v>-86.95528539999999</v>
+      </c>
+      <c r="J707" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/7895/altstadt-acres)</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>in-argos-community-park</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>Argos Community Park</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>Argos</t>
+        </is>
+      </c>
+      <c r="E708" t="n">
+        <v>9</v>
+      </c>
+      <c r="H708" t="n">
+        <v>41.2178901</v>
+      </c>
+      <c r="I708" t="n">
+        <v>-86.2494337</v>
+      </c>
+      <c r="J708" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/6926/argos-community-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>in-autumn-creek-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>Autumn Creek Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>Schererville</t>
+        </is>
+      </c>
+      <c r="E709" t="n">
+        <v>9</v>
+      </c>
+      <c r="H709" t="n">
+        <v>41.4956706</v>
+      </c>
+      <c r="I709" t="n">
+        <v>-87.4686153</v>
+      </c>
+      <c r="J709" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/9771/autumn-creek-dgc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>in-bayard-park-evansville</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>Bayard Park - Evansville</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>Evansville</t>
+        </is>
+      </c>
+      <c r="E710" t="n">
+        <v>9</v>
+      </c>
+      <c r="H710" t="n">
+        <v>37.9637903</v>
+      </c>
+      <c r="I710" t="n">
+        <v>-87.56345279999999</v>
+      </c>
+      <c r="J710" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/12493/bayard-park-evansville)</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>in-bethel-college-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>Bethel College Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>Mishawaka</t>
+        </is>
+      </c>
+      <c r="E711" t="n">
+        <v>9</v>
+      </c>
+      <c r="H711" t="n">
+        <v>41.6900024</v>
+      </c>
+      <c r="I711" t="n">
+        <v>-86.1650016</v>
+      </c>
+      <c r="J711" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/8425/bethel-college)</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>in-bourissa-hills</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>Bourissa Hills</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>New Carisle</t>
+        </is>
+      </c>
+      <c r="E712" t="n">
+        <v>9</v>
+      </c>
+      <c r="H712" t="n">
+        <v>41.7062955</v>
+      </c>
+      <c r="I712" t="n">
+        <v>-86.51086170000001</v>
+      </c>
+      <c r="J712" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/4740/bourissa-hills)</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>in-cica-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>CICA Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>Mooresville</t>
+        </is>
+      </c>
+      <c r="E713" t="n">
+        <v>9</v>
+      </c>
+      <c r="H713" t="n">
+        <v>39.5951977</v>
+      </c>
+      <c r="I713" t="n">
+        <v>-86.3724433</v>
+      </c>
+      <c r="J713" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/4146/cica-dgc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>in-camp-arthur-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>Camp Arthur Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>Bruceville</t>
+        </is>
+      </c>
+      <c r="E714" t="n">
+        <v>18</v>
+      </c>
+      <c r="H714" t="n">
+        <v>38.7604033</v>
+      </c>
+      <c r="I714" t="n">
+        <v>-87.4149172</v>
+      </c>
+      <c r="J714" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/10505/camp-arthur)</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>in-centennial-park</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>Centennial Park</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>Plymouth</t>
+        </is>
+      </c>
+      <c r="E715" t="n">
+        <v>18</v>
+      </c>
+      <c r="H715" t="n">
+        <v>41.3461608</v>
+      </c>
+      <c r="I715" t="n">
+        <v>-86.3215206</v>
+      </c>
+      <c r="J715" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/12468/centennial-park-dgc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>in-ceraland-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>Ceraland Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>Columbus</t>
+        </is>
+      </c>
+      <c r="E716" t="n">
+        <v>18</v>
+      </c>
+      <c r="H716" t="n">
+        <v>39.2277676</v>
+      </c>
+      <c r="I716" t="n">
+        <v>-85.8781889</v>
+      </c>
+      <c r="J716" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/7797/ceraland-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>in-chandler-sports-park-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>Chandler Sports Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>Chandler</t>
+        </is>
+      </c>
+      <c r="E717" t="n">
+        <v>36</v>
+      </c>
+      <c r="H717" t="n">
+        <v>38.0415149</v>
+      </c>
+      <c r="I717" t="n">
+        <v>-87.37106369999999</v>
+      </c>
+      <c r="J717" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/12160/chandler-sports-park-disc-golf-course)</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>in-chapel-lake-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>Chapel Lake Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>Jeffersonville</t>
+        </is>
+      </c>
+      <c r="E718" t="n">
+        <v>18</v>
+      </c>
+      <c r="H718" t="n">
+        <v>38.3628137</v>
+      </c>
+      <c r="I718" t="n">
+        <v>-85.6817068</v>
+      </c>
+      <c r="J718" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/12728/chapel-lake-disc-golf-course)</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>in-clear-creek-park</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>Clear Creek Park</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="E719" t="n">
+        <v>18</v>
+      </c>
+      <c r="H719" t="n">
+        <v>39.8296395</v>
+      </c>
+      <c r="I719" t="n">
+        <v>-84.8898385</v>
+      </c>
+      <c r="J719" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/4034/clear-creek-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>in-covington-city-park</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>Covington City Park</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>Covington</t>
+        </is>
+      </c>
+      <c r="E720" t="n">
+        <v>9</v>
+      </c>
+      <c r="H720" t="n">
+        <v>40.1248691</v>
+      </c>
+      <c r="I720" t="n">
+        <v>-87.3995149</v>
+      </c>
+      <c r="J720" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/8095/covington-city-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>in-coyote-trace</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>Coyote Trace</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>Nineveh</t>
+        </is>
+      </c>
+      <c r="E721" t="n">
+        <v>18</v>
+      </c>
+      <c r="H721" t="n">
+        <v>39.3662381</v>
+      </c>
+      <c r="I721" t="n">
+        <v>-86.0418355</v>
+      </c>
+      <c r="J721" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/7636/coyote-trace-disc-golf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>in-craig-park-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>Craig Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E722" t="n">
+        <v>18</v>
+      </c>
+      <c r="H722" t="n">
+        <v>39.5100384</v>
+      </c>
+      <c r="I722" t="n">
+        <v>-87.1344464</v>
+      </c>
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/12314/craig-park-dgc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>in-creek-ridge-disc-golf</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>Creek Ridge Disc Golf</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>Michigan City</t>
+        </is>
+      </c>
+      <c r="E723" t="n">
+        <v>9</v>
+      </c>
+      <c r="H723" t="n">
+        <v>41.7061252</v>
+      </c>
+      <c r="I723" t="n">
+        <v>-86.8776527</v>
+      </c>
+      <c r="J723" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/7127/creek-ridge-county-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>in-cupertino-s-course</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>Cupertino's Course</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>St. Meinrad</t>
+        </is>
+      </c>
+      <c r="E724" t="n">
+        <v>18</v>
+      </c>
+      <c r="H724" t="n">
+        <v>38.1499665</v>
+      </c>
+      <c r="I724" t="n">
+        <v>-86.811207</v>
+      </c>
+      <c r="J724" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/6534/cupertinos-course)</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>in-cyclone-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>Cyclone Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>Indianapolis</t>
+        </is>
+      </c>
+      <c r="E725" t="n">
+        <v>18</v>
+      </c>
+      <c r="H725" t="n">
+        <v>39.7390176</v>
+      </c>
+      <c r="I725" t="n">
+        <v>-86.25267119999999</v>
+      </c>
+      <c r="J725" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/13351/cyclone-disc-golf-course)</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>in-decatur-county-park-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>Decatur County Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>Greensburg</t>
+        </is>
+      </c>
+      <c r="E726" t="n">
+        <v>9</v>
+      </c>
+      <c r="H726" t="n">
+        <v>39.3218213</v>
+      </c>
+      <c r="I726" t="n">
+        <v>-85.465467</v>
+      </c>
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/9737/decatur-county-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>in-derby-downs</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>Derby Downs</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>Anderson</t>
+        </is>
+      </c>
+      <c r="E727" t="n">
+        <v>18</v>
+      </c>
+      <c r="H727" t="n">
+        <v>40.0993346</v>
+      </c>
+      <c r="I727" t="n">
+        <v>-85.6808063</v>
+      </c>
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/12015/derby-downs-disc-golf-course)</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>in-elk-ridge-ranch</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>Elk Ridge Ranch</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>Shoals</t>
+        </is>
+      </c>
+      <c r="E728" t="n">
+        <v>18</v>
+      </c>
+      <c r="H728" t="n">
+        <v>38.6655326</v>
+      </c>
+      <c r="I728" t="n">
+        <v>-86.78705909999999</v>
+      </c>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/9518/elk-ridge-ranch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>in-elks-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>Elks Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>Kendallville</t>
+        </is>
+      </c>
+      <c r="E729" t="n">
+        <v>21</v>
+      </c>
+      <c r="H729" t="n">
+        <v>41.4480495</v>
+      </c>
+      <c r="I729" t="n">
+        <v>-85.2611508</v>
+      </c>
+      <c r="J729" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/13741/elks-golf-course)</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>in-evergreen-park</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>Evergreen Park</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>Huntington</t>
+        </is>
+      </c>
+      <c r="E730" t="n">
+        <v>18</v>
+      </c>
+      <c r="H730" t="n">
+        <v>40.8778613</v>
+      </c>
+      <c r="I730" t="n">
+        <v>-85.5000433</v>
+      </c>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/5157/evergreen-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>in-first-christian-church</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>First Christian Church</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>Evansville</t>
+        </is>
+      </c>
+      <c r="E731" t="n">
+        <v>9</v>
+      </c>
+      <c r="H731" t="n">
+        <v>38.0850444</v>
+      </c>
+      <c r="I731" t="n">
+        <v>-87.51278000000001</v>
+      </c>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/11057/first-christian-church)</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>in-fly-by-faith</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>Fly By Faith</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>Lafayette</t>
+        </is>
+      </c>
+      <c r="E732" t="n">
+        <v>18</v>
+      </c>
+      <c r="H732" t="n">
+        <v>40.4169481</v>
+      </c>
+      <c r="I732" t="n">
+        <v>-86.82331809999999</v>
+      </c>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/3317/fly-by-faith-dgc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>in-forsythe-park</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>Forsythe Park</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>Whiting</t>
+        </is>
+      </c>
+      <c r="E733" t="n">
+        <v>18</v>
+      </c>
+      <c r="H733" t="n">
+        <v>41.6789134</v>
+      </c>
+      <c r="I733" t="n">
+        <v>-87.49807850000001</v>
+      </c>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/8374/forsythe-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>in-frank-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>Frank Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>Mishawaka</t>
+        </is>
+      </c>
+      <c r="E734" t="n">
+        <v>9</v>
+      </c>
+      <c r="H734" t="n">
+        <v>41.6900024</v>
+      </c>
+      <c r="I734" t="n">
+        <v>-86.1650016</v>
+      </c>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/9729/henry-frank-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>in-frank-merry-park</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>Frank Merry Park</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>Dunkirk</t>
+        </is>
+      </c>
+      <c r="E735" t="n">
+        <v>18</v>
+      </c>
+      <c r="H735" t="n">
+        <v>40.3752385</v>
+      </c>
+      <c r="I735" t="n">
+        <v>-85.2139327</v>
+      </c>
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/6649/frank-merry-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>in-freedom-park</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>Freedom Park</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>Lowell</t>
+        </is>
+      </c>
+      <c r="E736" t="n">
+        <v>18</v>
+      </c>
+      <c r="H736" t="n">
+        <v>41.2854016</v>
+      </c>
+      <c r="I736" t="n">
+        <v>-87.40200230000001</v>
+      </c>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/4912/freedom-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>in-fremont-middle-school</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>Fremont Middle School</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>Fremont</t>
+        </is>
+      </c>
+      <c r="E737" t="n">
+        <v>9</v>
+      </c>
+      <c r="H737" t="n">
+        <v>41.7340469</v>
+      </c>
+      <c r="I737" t="n">
+        <v>-84.92346000000001</v>
+      </c>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/4987/fremont-middle-school)</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>in-gehlhausen-farms</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>Gehlhausen Farms</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>Indianapolis</t>
+        </is>
+      </c>
+      <c r="E738" t="n">
+        <v>18</v>
+      </c>
+      <c r="H738" t="n">
+        <v>39.7906799</v>
+      </c>
+      <c r="I738" t="n">
+        <v>-85.9768703</v>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/10617/gehlhausen-farms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>in-grace-college-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>Grace College Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>Winona Lake</t>
+        </is>
+      </c>
+      <c r="E739" t="n">
+        <v>9</v>
+      </c>
+      <c r="H739" t="n">
+        <v>41.2202637</v>
+      </c>
+      <c r="I739" t="n">
+        <v>-85.8167844</v>
+      </c>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/5989/grace-college)</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>in-granger-commons-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>Granger Commons Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>Granger</t>
+        </is>
+      </c>
+      <c r="E740" t="n">
+        <v>9</v>
+      </c>
+      <c r="H740" t="n">
+        <v>41.7393788</v>
+      </c>
+      <c r="I740" t="n">
+        <v>-86.1497624</v>
+      </c>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/7799/granger-community-church)</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>in-harrison-fitness-trail-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>Harrison Fitness Trail Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>Warsaw</t>
+        </is>
+      </c>
+      <c r="E741" t="n">
+        <v>9</v>
+      </c>
+      <c r="H741" t="n">
+        <v>41.2744432</v>
+      </c>
+      <c r="I741" t="n">
+        <v>-85.81191219999999</v>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/4834/harrison-fitness-trail-dgc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>in-harter-park-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>Harter Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>Union City</t>
+        </is>
+      </c>
+      <c r="E742" t="n">
+        <v>24</v>
+      </c>
+      <c r="H742" t="n">
+        <v>40.2027604</v>
+      </c>
+      <c r="I742" t="n">
+        <v>-84.8340274</v>
+      </c>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/5448/harter-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>in-hawk-s-nest</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>Hawk's Nest</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>Indianapolis</t>
+        </is>
+      </c>
+      <c r="E743" t="n">
+        <v>18</v>
+      </c>
+      <c r="H743" t="n">
+        <v>39.7045698</v>
+      </c>
+      <c r="I743" t="n">
+        <v>-86.23660630000001</v>
+      </c>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/9241/hawks-nest-dgc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>in-heartland-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>Heartland Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>Sharpsville</t>
+        </is>
+      </c>
+      <c r="E744" t="n">
+        <v>9</v>
+      </c>
+      <c r="H744" t="n">
+        <v>40.3616487</v>
+      </c>
+      <c r="I744" t="n">
+        <v>-86.1054556</v>
+      </c>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/8195/heartland-dgc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>in-hidden-diamonds</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>Hidden Diamonds</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>Albion</t>
+        </is>
+      </c>
+      <c r="E745" t="n">
+        <v>9</v>
+      </c>
+      <c r="H745" t="n">
+        <v>41.3638364</v>
+      </c>
+      <c r="I745" t="n">
+        <v>-85.44459759999999</v>
+      </c>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/5915/hidden-diamonds)</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>in-hidden-lake-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>Hidden Lake Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>Merrillville</t>
+        </is>
+      </c>
+      <c r="E746" t="n">
+        <v>18</v>
+      </c>
+      <c r="H746" t="n">
+        <v>41.4940103</v>
+      </c>
+      <c r="I746" t="n">
+        <v>-87.33995779999999</v>
+      </c>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/12860/hidden-lake)</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>in-highlander-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>Highlander Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>Floyds Knobs</t>
+        </is>
+      </c>
+      <c r="E747" t="n">
+        <v>18</v>
+      </c>
+      <c r="H747" t="n">
+        <v>38.3508268</v>
+      </c>
+      <c r="I747" t="n">
+        <v>-85.8923013</v>
+      </c>
+      <c r="J747" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/13623/highlander)</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>in-hillcrest-park-disc-golf</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>Hillcrest Park Disc Golf</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>Vincennes</t>
+        </is>
+      </c>
+      <c r="E748" t="n">
+        <v>9</v>
+      </c>
+      <c r="H748" t="n">
+        <v>38.6743787</v>
+      </c>
+      <c r="I748" t="n">
+        <v>-87.50620309999999</v>
+      </c>
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/3780/hillcrest-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>in-hudson-family-park-disc-golf</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>Hudson Family Park Disc Golf</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>Portland</t>
+        </is>
+      </c>
+      <c r="E749" t="n">
+        <v>18</v>
+      </c>
+      <c r="H749" t="n">
+        <v>40.4179694</v>
+      </c>
+      <c r="I749" t="n">
+        <v>-84.9821005</v>
+      </c>
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/9232/hudson-family-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>in-huntington-university</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>Huntington University</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>Huntington</t>
+        </is>
+      </c>
+      <c r="E750" t="n">
+        <v>9</v>
+      </c>
+      <c r="H750" t="n">
+        <v>40.8778613</v>
+      </c>
+      <c r="I750" t="n">
+        <v>-85.5000433</v>
+      </c>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/5772/huntington-university)</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>in-island-park-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>Island Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>Elkhart</t>
+        </is>
+      </c>
+      <c r="E751" t="n">
+        <v>18</v>
+      </c>
+      <c r="H751" t="n">
+        <v>41.6757317</v>
+      </c>
+      <c r="I751" t="n">
+        <v>-85.95420679999999</v>
+      </c>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/12624/island-park-disc-golf-course)</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>in-kekionga-park</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>Kekionga Park</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>Decatur</t>
+        </is>
+      </c>
+      <c r="E752" t="n">
+        <v>9</v>
+      </c>
+      <c r="H752" t="n">
+        <v>40.8406124</v>
+      </c>
+      <c r="I752" t="n">
+        <v>-84.9333678</v>
+      </c>
+      <c r="J752" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/4994/kekionga-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>in-kesling-park</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>Kesling Park</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>Laporte</t>
+        </is>
+      </c>
+      <c r="E753" t="n">
+        <v>9</v>
+      </c>
+      <c r="H753" t="n">
+        <v>41.6099188</v>
+      </c>
+      <c r="I753" t="n">
+        <v>-86.72453830000001</v>
+      </c>
+      <c r="J753" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/10294/kesling-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>in-lake-hills-baptist-church-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>Lake Hills Baptist Church Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>Schererville</t>
+        </is>
+      </c>
+      <c r="E754" t="n">
+        <v>12</v>
+      </c>
+      <c r="H754" t="n">
+        <v>41.4956706</v>
+      </c>
+      <c r="I754" t="n">
+        <v>-87.4686153</v>
+      </c>
+      <c r="J754" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/10574/lake-hills-church)</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>in-lakewood-park</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>Lakewood Park</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>Auburn</t>
+        </is>
+      </c>
+      <c r="E755" t="n">
+        <v>18</v>
+      </c>
+      <c r="H755" t="n">
+        <v>41.3299846</v>
+      </c>
+      <c r="I755" t="n">
+        <v>-85.0532443</v>
+      </c>
+      <c r="J755" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/11536/lakewood-park-church)</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>in-lemon-lake-county-park-gold</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>Lemon Lake County Park - Gold</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>Crown Point</t>
+        </is>
+      </c>
+      <c r="E756" t="n">
+        <v>18</v>
+      </c>
+      <c r="H756" t="n">
+        <v>41.4379352</v>
+      </c>
+      <c r="I756" t="n">
+        <v>-87.3797938</v>
+      </c>
+      <c r="J756" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/10803/lake-county-fairgrounds)</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>in-liberty-park</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>Liberty Park</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>Batesville</t>
+        </is>
+      </c>
+      <c r="E757" t="n">
+        <v>9</v>
+      </c>
+      <c r="H757" t="n">
+        <v>39.3022326</v>
+      </c>
+      <c r="I757" t="n">
+        <v>-85.21247320000001</v>
+      </c>
+      <c r="J757" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/5479/liberty-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>in-linza-graham-park</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>Linza Graham Park</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>Scottsburg</t>
+        </is>
+      </c>
+      <c r="E758" t="n">
+        <v>9</v>
+      </c>
+      <c r="H758" t="n">
+        <v>38.6845045</v>
+      </c>
+      <c r="I758" t="n">
+        <v>-85.8071897</v>
+      </c>
+      <c r="J758" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/4301/linza-graham-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>in-little-slice-of-heaven</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>Little Slice of Heaven</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>Churubusco</t>
+        </is>
+      </c>
+      <c r="E759" t="n">
+        <v>9</v>
+      </c>
+      <c r="H759" t="n">
+        <v>41.2254723</v>
+      </c>
+      <c r="I759" t="n">
+        <v>-85.28015499999999</v>
+      </c>
+      <c r="J759" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/9259/little-slice-of-heaven)</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>in-marquette-park-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>Marquette Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>Gary</t>
+        </is>
+      </c>
+      <c r="E760" t="n">
+        <v>18</v>
+      </c>
+      <c r="H760" t="n">
+        <v>41.6095082</v>
+      </c>
+      <c r="I760" t="n">
+        <v>-87.2574017</v>
+      </c>
+      <c r="J760" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/9973/marquette-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>in-mesker-woods</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>Mesker Woods</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>Evansville</t>
+        </is>
+      </c>
+      <c r="E761" t="n">
+        <v>18</v>
+      </c>
+      <c r="H761" t="n">
+        <v>38.0308669</v>
+      </c>
+      <c r="I761" t="n">
+        <v>-87.61076509999999</v>
+      </c>
+      <c r="J761" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/12730/mesker-woods-at-mesker-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>in-missile-ridge-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>Missile Ridge Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>Cedar Lake</t>
+        </is>
+      </c>
+      <c r="E762" t="n">
+        <v>21</v>
+      </c>
+      <c r="H762" t="n">
+        <v>41.3780408</v>
+      </c>
+      <c r="I762" t="n">
+        <v>-87.4468395</v>
+      </c>
+      <c r="J762" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/8732/missile-ridge)</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>in-mullet-park</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>Mullet Park</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>Goshen</t>
+        </is>
+      </c>
+      <c r="E763" t="n">
+        <v>9</v>
+      </c>
+      <c r="H763" t="n">
+        <v>41.5707994</v>
+      </c>
+      <c r="I763" t="n">
+        <v>-85.8502605</v>
+      </c>
+      <c r="J763" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/9155/mullet-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>in-new-albany-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>New Albany Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>New Albany</t>
+        </is>
+      </c>
+      <c r="E764" t="n">
+        <v>18</v>
+      </c>
+      <c r="H764" t="n">
+        <v>38.3055409</v>
+      </c>
+      <c r="I764" t="n">
+        <v>-85.8184091</v>
+      </c>
+      <c r="J764" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/6985/new-albany-dgc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>in-new-lake-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>New Lake Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>Oakland City</t>
+        </is>
+      </c>
+      <c r="E765" t="n">
+        <v>18</v>
+      </c>
+      <c r="H765" t="n">
+        <v>38.329014</v>
+      </c>
+      <c r="I765" t="n">
+        <v>-87.3269509</v>
+      </c>
+      <c r="J765" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/9396/new-lake)</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>in-north-putnam-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>North Putnam Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>Roachdale</t>
+        </is>
+      </c>
+      <c r="E766" t="n">
+        <v>22</v>
+      </c>
+      <c r="H766" t="n">
+        <v>39.829093</v>
+      </c>
+      <c r="I766" t="n">
+        <v>-86.8022778</v>
+      </c>
+      <c r="J766" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/11318/north-putnam-dgc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>in-north-webster-elementary-school</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>North Webster Elementary School</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>North Webster</t>
+        </is>
+      </c>
+      <c r="E767" t="n">
+        <v>18</v>
+      </c>
+      <c r="H767" t="n">
+        <v>41.3261989</v>
+      </c>
+      <c r="I767" t="n">
+        <v>-85.6907614</v>
+      </c>
+      <c r="J767" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K767" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/11610/north-webster-elementary-school)</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>in-ossian-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>Ossian Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>Ossian</t>
+        </is>
+      </c>
+      <c r="E768" t="n">
+        <v>18</v>
+      </c>
+      <c r="H768" t="n">
+        <v>40.8896152</v>
+      </c>
+      <c r="I768" t="n">
+        <v>-85.15550279999999</v>
+      </c>
+      <c r="J768" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K768" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/5020/ossian-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>in-peru-municipal-golf-course</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>Peru Municipal Golf Course</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E769" t="n">
+        <v>18</v>
+      </c>
+      <c r="H769" t="n">
+        <v>40.7483602</v>
+      </c>
+      <c r="I769" t="n">
+        <v>-86.0851083</v>
+      </c>
+      <c r="J769" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/9494/peru-municipal-dgc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>in-pickett-park-disc-golf-course-at-purdue-university</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>Pickett Park Disc Golf Course at Purdue University</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>West Lafayette</t>
+        </is>
+      </c>
+      <c r="E770" t="n">
+        <v>9</v>
+      </c>
+      <c r="H770" t="n">
+        <v>40.4578411</v>
+      </c>
+      <c r="I770" t="n">
+        <v>-86.92166659999999</v>
+      </c>
+      <c r="J770" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K770" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/3316/purdue-university-dgc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>in-pioneer-park-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>Pioneer Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>Mooresville</t>
+        </is>
+      </c>
+      <c r="E771" t="n">
+        <v>18</v>
+      </c>
+      <c r="H771" t="n">
+        <v>39.5951977</v>
+      </c>
+      <c r="I771" t="n">
+        <v>-86.3724433</v>
+      </c>
+      <c r="J771" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/11882/pioneer-park-dgc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>in-prospect-park</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>Prospect Park</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>Noblesville</t>
+        </is>
+      </c>
+      <c r="E772" t="n">
+        <v>9</v>
+      </c>
+      <c r="H772" t="n">
+        <v>40.0330476</v>
+      </c>
+      <c r="I772" t="n">
+        <v>-85.9850161</v>
+      </c>
+      <c r="J772" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K772" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/12191/prospect-park-addition-disc-golf-course)</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>in-pulaski-park</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>Pulaski Park</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>Hammond</t>
+        </is>
+      </c>
+      <c r="E773" t="n">
+        <v>18</v>
+      </c>
+      <c r="H773" t="n">
+        <v>41.5876154</v>
+      </c>
+      <c r="I773" t="n">
+        <v>-87.4617161</v>
+      </c>
+      <c r="J773" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K773" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/1026/pulaski-park)</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>in-red-tail-ridge-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>Red Tail Ridge Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>Princeton</t>
+        </is>
+      </c>
+      <c r="E774" t="n">
+        <v>18</v>
+      </c>
+      <c r="H774" t="n">
+        <v>38.3520622</v>
+      </c>
+      <c r="I774" t="n">
+        <v>-87.5706593</v>
+      </c>
+      <c r="J774" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K774" t="inlineStr">
+        <is>
+          <t>PDGA directory (pdga.com/course-directory) x DiscGolfScene (https://www.discgolfscene.com/course/7439/red-tail-ridge)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K474"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Chains Course Catalog.xlsx
+++ b/data/Chains Course Catalog.xlsx
@@ -436,7 +436,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H52"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -617,12 +617,30 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>70</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>None (0/70) — no compliant public per-hole source; users add pars in-app</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>4</v>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Pass 1 of ~3: top 70 of 393 DiscGolfScene-listed courses. Geo: city centroid. Continue next pass.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -632,12 +650,15 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WI</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Not started</t>
+          <t>thin - revisit</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Revisit - state filter issue; found: 4-H Camp Riversite (Hingham)</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -657,11 +678,29 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>143</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>None (0/143) — no compliant public per-hole source; users add pars in-app</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>6</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>PDGA directory (143 verified, 4 geocoding gaps)</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1576,8 +1615,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K774"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:K987"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="41" customWidth="1" min="2" max="2"/>
@@ -36165,6 +36204,7814 @@
         </is>
       </c>
     </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>il-alpine-park</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>Alpine Park</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>Rockford</t>
+        </is>
+      </c>
+      <c r="H775" t="n">
+        <v>42.2671</v>
+      </c>
+      <c r="I775" t="n">
+        <v>-89.0936</v>
+      </c>
+      <c r="J775" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K775" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>il-anna-page-park</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>Anna Page Park</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>Rockford</t>
+        </is>
+      </c>
+      <c r="H776" t="n">
+        <v>42.2671</v>
+      </c>
+      <c r="I776" t="n">
+        <v>-89.0936</v>
+      </c>
+      <c r="J776" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K776" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>il-bradley-park</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>Bradley Park</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>Peoria</t>
+        </is>
+      </c>
+      <c r="H777" t="n">
+        <v>40.6936</v>
+      </c>
+      <c r="I777" t="n">
+        <v>-89.589</v>
+      </c>
+      <c r="J777" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K777" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>il-donovan-park</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>Donovan Park</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>Peoria</t>
+        </is>
+      </c>
+      <c r="H778" t="n">
+        <v>40.6936</v>
+      </c>
+      <c r="I778" t="n">
+        <v>-89.589</v>
+      </c>
+      <c r="J778" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K778" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>il-eta-creative-arts-center</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>ETA Creative Arts Center</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="H779" t="n">
+        <v>41.8781</v>
+      </c>
+      <c r="I779" t="n">
+        <v>-87.6298</v>
+      </c>
+      <c r="J779" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K779" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>il-eckwood-park</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>Eckwood Park</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>Peoria</t>
+        </is>
+      </c>
+      <c r="H780" t="n">
+        <v>40.6936</v>
+      </c>
+      <c r="I780" t="n">
+        <v>-89.589</v>
+      </c>
+      <c r="J780" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K780" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>il-forrest-park</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>Forrest Park</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>Bloomington</t>
+        </is>
+      </c>
+      <c r="H781" t="n">
+        <v>40.4843</v>
+      </c>
+      <c r="I781" t="n">
+        <v>-88.9937</v>
+      </c>
+      <c r="J781" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K781" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>il-greater-peoria-family-ymca</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>Greater Peoria Family YMCA</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>Peoria</t>
+        </is>
+      </c>
+      <c r="H782" t="n">
+        <v>40.6936</v>
+      </c>
+      <c r="I782" t="n">
+        <v>-89.589</v>
+      </c>
+      <c r="J782" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K782" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>il-hells-gate-haunted-house</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>Hells Gate Haunted House</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>Lockport</t>
+        </is>
+      </c>
+      <c r="H783" t="n">
+        <v>41.5343</v>
+      </c>
+      <c r="I783" t="n">
+        <v>-88.05329999999999</v>
+      </c>
+      <c r="J783" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K783" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>il-highland-park-golf-course</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>Highland Park Golf Course</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>Bloomington</t>
+        </is>
+      </c>
+      <c r="H784" t="n">
+        <v>40.4843</v>
+      </c>
+      <c r="I784" t="n">
+        <v>-88.9937</v>
+      </c>
+      <c r="J784" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K784" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>il-highland-temp-course</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>Highland Temp Course</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>Bloomington</t>
+        </is>
+      </c>
+      <c r="H785" t="n">
+        <v>40.4843</v>
+      </c>
+      <c r="I785" t="n">
+        <v>-88.9937</v>
+      </c>
+      <c r="J785" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K785" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>il-illinois-institute-of-technology</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>Illinois Institute of Technology</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="H786" t="n">
+        <v>41.8781</v>
+      </c>
+      <c r="I786" t="n">
+        <v>-87.6298</v>
+      </c>
+      <c r="J786" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K786" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>il-ingersoll-memorial-park</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>Ingersoll Memorial Park</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>Rockford</t>
+        </is>
+      </c>
+      <c r="H787" t="n">
+        <v>42.2671</v>
+      </c>
+      <c r="I787" t="n">
+        <v>-89.0936</v>
+      </c>
+      <c r="J787" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K787" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>il-jackson-park--chicago</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>Jackson Park - Chicago</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="H788" t="n">
+        <v>41.8781</v>
+      </c>
+      <c r="I788" t="n">
+        <v>-87.6298</v>
+      </c>
+      <c r="J788" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K788" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>il-lincoln-landing</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>Lincoln Landing</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>Lockport</t>
+        </is>
+      </c>
+      <c r="H789" t="n">
+        <v>41.5343</v>
+      </c>
+      <c r="I789" t="n">
+        <v>-88.05329999999999</v>
+      </c>
+      <c r="J789" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K789" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>il-p-j-irvin</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>P. J. Irvin</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>Bloomington</t>
+        </is>
+      </c>
+      <c r="H790" t="n">
+        <v>40.4843</v>
+      </c>
+      <c r="I790" t="n">
+        <v>-88.9937</v>
+      </c>
+      <c r="J790" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K790" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>il-pj-irvin-park</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>PJ Irvin Park</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>Bloomington</t>
+        </is>
+      </c>
+      <c r="H791" t="n">
+        <v>40.4843</v>
+      </c>
+      <c r="I791" t="n">
+        <v>-88.9937</v>
+      </c>
+      <c r="J791" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K791" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>il-peoria-art-guild</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>Peoria Art Guild</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>Peoria</t>
+        </is>
+      </c>
+      <c r="H792" t="n">
+        <v>40.6936</v>
+      </c>
+      <c r="I792" t="n">
+        <v>-89.589</v>
+      </c>
+      <c r="J792" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K792" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>il-rock-cut-state-park</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>Rock Cut State Park</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>Rockford</t>
+        </is>
+      </c>
+      <c r="H793" t="n">
+        <v>42.2671</v>
+      </c>
+      <c r="I793" t="n">
+        <v>-89.0936</v>
+      </c>
+      <c r="J793" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K793" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>il-rockford-university</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>Rockford University</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>Rockford</t>
+        </is>
+      </c>
+      <c r="H794" t="n">
+        <v>42.2671</v>
+      </c>
+      <c r="I794" t="n">
+        <v>-89.0936</v>
+      </c>
+      <c r="J794" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K794" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>il-roxy-theatre</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>Roxy Theatre</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>Lockport</t>
+        </is>
+      </c>
+      <c r="H795" t="n">
+        <v>41.5343</v>
+      </c>
+      <c r="I795" t="n">
+        <v>-88.05329999999999</v>
+      </c>
+      <c r="J795" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K795" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>il-schiller-playfield</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>Schiller Playfield</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="H796" t="n">
+        <v>41.8781</v>
+      </c>
+      <c r="I796" t="n">
+        <v>-87.6298</v>
+      </c>
+      <c r="J796" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K796" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>il-state-farm-park</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>State Farm Park</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>Bloomington</t>
+        </is>
+      </c>
+      <c r="H797" t="n">
+        <v>40.4843</v>
+      </c>
+      <c r="I797" t="n">
+        <v>-88.9937</v>
+      </c>
+      <c r="J797" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K797" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>il-sycamore-valley</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>Sycamore Valley</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>Peoria</t>
+        </is>
+      </c>
+      <c r="H798" t="n">
+        <v>40.6936</v>
+      </c>
+      <c r="I798" t="n">
+        <v>-89.589</v>
+      </c>
+      <c r="J798" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K798" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>il-the-canyons</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>The Canyons</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>Lockport</t>
+        </is>
+      </c>
+      <c r="H799" t="n">
+        <v>41.5343</v>
+      </c>
+      <c r="I799" t="n">
+        <v>-88.05329999999999</v>
+      </c>
+      <c r="J799" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K799" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>il-trinity-links</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>Trinity Links</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>Lockport</t>
+        </is>
+      </c>
+      <c r="H800" t="n">
+        <v>41.5343</v>
+      </c>
+      <c r="I800" t="n">
+        <v>-88.05329999999999</v>
+      </c>
+      <c r="J800" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K800" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>il-trinity-links-disc-golf</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>Trinity Links Disc Golf</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>Lockport</t>
+        </is>
+      </c>
+      <c r="H801" t="n">
+        <v>41.5343</v>
+      </c>
+      <c r="I801" t="n">
+        <v>-88.05329999999999</v>
+      </c>
+      <c r="J801" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K801" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>il-uw-health-sports-factory</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>UW Health Sports Factory</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>Rockford</t>
+        </is>
+      </c>
+      <c r="H802" t="n">
+        <v>42.2671</v>
+      </c>
+      <c r="I802" t="n">
+        <v>-89.0936</v>
+      </c>
+      <c r="J802" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K802" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>il-washington-park</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>Washington Park</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="H803" t="n">
+        <v>41.8781</v>
+      </c>
+      <c r="I803" t="n">
+        <v>-87.6298</v>
+      </c>
+      <c r="J803" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K803" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>il-winnemac-park</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>Winnemac Park</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="H804" t="n">
+        <v>41.8781</v>
+      </c>
+      <c r="I804" t="n">
+        <v>-87.6298</v>
+      </c>
+      <c r="J804" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K804" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>il-downtown-morton-disc-golf-experience</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>Downtown Morton Disc Golf Experience</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>Morton</t>
+        </is>
+      </c>
+      <c r="H805" t="n">
+        <v>40.6097</v>
+      </c>
+      <c r="I805" t="n">
+        <v>-89.44750000000001</v>
+      </c>
+      <c r="J805" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K805" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>il-duncan-park</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>Duncan Park</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="H806" t="n">
+        <v>39.7817</v>
+      </c>
+      <c r="I806" t="n">
+        <v>-89.65009999999999</v>
+      </c>
+      <c r="J806" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K806" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>il-kennel-lake-sportsmen&amp;#039;s-club</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>Kennel Lake Sportsmen&amp;#039;s Club</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>Morton</t>
+        </is>
+      </c>
+      <c r="H807" t="n">
+        <v>40.6097</v>
+      </c>
+      <c r="I807" t="n">
+        <v>-89.44750000000001</v>
+      </c>
+      <c r="J807" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K807" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>il-lincoln-greens-golf-course</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>Lincoln Greens Golf Course</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="H808" t="n">
+        <v>39.7817</v>
+      </c>
+      <c r="I808" t="n">
+        <v>-89.65009999999999</v>
+      </c>
+      <c r="J808" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K808" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>il-lincoln-park</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>Lincoln Park</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="H809" t="n">
+        <v>39.7817</v>
+      </c>
+      <c r="I809" t="n">
+        <v>-89.65009999999999</v>
+      </c>
+      <c r="J809" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K809" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>il-megiddo</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>Megiddo</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>Morton</t>
+        </is>
+      </c>
+      <c r="H810" t="n">
+        <v>40.6097</v>
+      </c>
+      <c r="I810" t="n">
+        <v>-89.44750000000001</v>
+      </c>
+      <c r="J810" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K810" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>il-northwood-park</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>Northwood Park</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>Morton</t>
+        </is>
+      </c>
+      <c r="H811" t="n">
+        <v>40.6097</v>
+      </c>
+      <c r="I811" t="n">
+        <v>-89.44750000000001</v>
+      </c>
+      <c r="J811" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K811" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>il-pasfield-golf-course</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>Pasfield Golf Course</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="H812" t="n">
+        <v>39.7817</v>
+      </c>
+      <c r="I812" t="n">
+        <v>-89.65009999999999</v>
+      </c>
+      <c r="J812" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K812" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>il-university-of-illinois-springfield</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>University of Illinois Springfield</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="H813" t="n">
+        <v>39.7817</v>
+      </c>
+      <c r="I813" t="n">
+        <v>-89.65009999999999</v>
+      </c>
+      <c r="J813" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K813" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>il-westwood-park</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>Westwood Park</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>Morton</t>
+        </is>
+      </c>
+      <c r="H814" t="n">
+        <v>40.6097</v>
+      </c>
+      <c r="I814" t="n">
+        <v>-89.44750000000001</v>
+      </c>
+      <c r="J814" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K814" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>il-avery-preserve</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>Avery Preserve</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>Plainfield</t>
+        </is>
+      </c>
+      <c r="H815" t="n">
+        <v>41.6389</v>
+      </c>
+      <c r="I815" t="n">
+        <v>-88.23</v>
+      </c>
+      <c r="J815" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K815" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>il-bicentennial-park</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>Bicentennial Park</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>Belleville</t>
+        </is>
+      </c>
+      <c r="H816" t="n">
+        <v>38.52</v>
+      </c>
+      <c r="I816" t="n">
+        <v>-89.9876</v>
+      </c>
+      <c r="J816" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K816" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>il-big-creek-park</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>Big Creek Park</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>Canton</t>
+        </is>
+      </c>
+      <c r="H817" t="n">
+        <v>40.5465</v>
+      </c>
+      <c r="I817" t="n">
+        <v>-89.89</v>
+      </c>
+      <c r="J817" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K817" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>il-camp-kearney</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>Camp Kearney</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>Canton</t>
+        </is>
+      </c>
+      <c r="H818" t="n">
+        <v>40.5465</v>
+      </c>
+      <c r="I818" t="n">
+        <v>-89.89</v>
+      </c>
+      <c r="J818" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K818" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>il-citizens-park</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>Citizens Park</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>Belleville</t>
+        </is>
+      </c>
+      <c r="H819" t="n">
+        <v>38.52</v>
+      </c>
+      <c r="I819" t="n">
+        <v>-89.9876</v>
+      </c>
+      <c r="J819" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K819" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>il-dixon-park-district-facility</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>Dixon Park District Facility</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>Dixon</t>
+        </is>
+      </c>
+      <c r="H820" t="n">
+        <v>41.8396</v>
+      </c>
+      <c r="I820" t="n">
+        <v>-89.4716</v>
+      </c>
+      <c r="J820" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K820" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>il-east-end-park</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>East End Park</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>Belleville</t>
+        </is>
+      </c>
+      <c r="H821" t="n">
+        <v>38.52</v>
+      </c>
+      <c r="I821" t="n">
+        <v>-89.9876</v>
+      </c>
+      <c r="J821" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K821" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>il-foreman-grove</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>Foreman Grove</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>Jacksonville</t>
+        </is>
+      </c>
+      <c r="H822" t="n">
+        <v>39.7385</v>
+      </c>
+      <c r="I822" t="n">
+        <v>-90.2351</v>
+      </c>
+      <c r="J822" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K822" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>il-highland-park</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>Highland Park</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>Joliet</t>
+        </is>
+      </c>
+      <c r="H823" t="n">
+        <v>41.5261</v>
+      </c>
+      <c r="I823" t="n">
+        <v>-88.083</v>
+      </c>
+      <c r="J823" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K823" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>il-jacksonville-il-central-park-temp-course</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>Jacksonville IL Central Park Temp Course</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>Jacksonville</t>
+        </is>
+      </c>
+      <c r="H824" t="n">
+        <v>39.7385</v>
+      </c>
+      <c r="I824" t="n">
+        <v>-90.2351</v>
+      </c>
+      <c r="J824" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K824" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>il-laderman-park</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>Laderman Park</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>Belleville</t>
+        </is>
+      </c>
+      <c r="H825" t="n">
+        <v>38.52</v>
+      </c>
+      <c r="I825" t="n">
+        <v>-89.9876</v>
+      </c>
+      <c r="J825" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K825" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>il-lowell-park</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>Lowell Park</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>Dixon</t>
+        </is>
+      </c>
+      <c r="H826" t="n">
+        <v>41.8396</v>
+      </c>
+      <c r="I826" t="n">
+        <v>-89.4716</v>
+      </c>
+      <c r="J826" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K826" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>il-nichols-park-disc-golf-course</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>Nichols Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>Jacksonville</t>
+        </is>
+      </c>
+      <c r="H827" t="n">
+        <v>39.7385</v>
+      </c>
+      <c r="I827" t="n">
+        <v>-90.2351</v>
+      </c>
+      <c r="J827" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K827" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>il-northridge-hills-golf-course</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>Northridge Hills Golf Course</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>Jacksonville</t>
+        </is>
+      </c>
+      <c r="H828" t="n">
+        <v>39.7385</v>
+      </c>
+      <c r="I828" t="n">
+        <v>-90.2351</v>
+      </c>
+      <c r="J828" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K828" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>il-old-joliet-prison</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>Old Joliet Prison</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>Joliet</t>
+        </is>
+      </c>
+      <c r="H829" t="n">
+        <v>41.5261</v>
+      </c>
+      <c r="I829" t="n">
+        <v>-88.083</v>
+      </c>
+      <c r="J829" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K829" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>il-page-park--dixon</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>Page Park - Dixon</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>Dixon</t>
+        </is>
+      </c>
+      <c r="H830" t="n">
+        <v>41.8396</v>
+      </c>
+      <c r="I830" t="n">
+        <v>-89.4716</v>
+      </c>
+      <c r="J830" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K830" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>il-settlers-park</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>Settlers Park</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>Plainfield</t>
+        </is>
+      </c>
+      <c r="H831" t="n">
+        <v>41.6389</v>
+      </c>
+      <c r="I831" t="n">
+        <v>-88.23</v>
+      </c>
+      <c r="J831" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K831" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>il-settlers-park</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>Settlers Park</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>Plainfield</t>
+        </is>
+      </c>
+      <c r="H832" t="n">
+        <v>41.6389</v>
+      </c>
+      <c r="I832" t="n">
+        <v>-88.23</v>
+      </c>
+      <c r="J832" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K832" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>il-spoon-river</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>Spoon River</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>Canton</t>
+        </is>
+      </c>
+      <c r="H833" t="n">
+        <v>40.5465</v>
+      </c>
+      <c r="I833" t="n">
+        <v>-89.89</v>
+      </c>
+      <c r="J833" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K833" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>il-temporary-course--old-joliet-prison</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>Temporary Course - Old Joliet Prison</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>Joliet</t>
+        </is>
+      </c>
+      <c r="H834" t="n">
+        <v>41.5261</v>
+      </c>
+      <c r="I834" t="n">
+        <v>-88.083</v>
+      </c>
+      <c r="J834" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K834" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>il-timber-creek-golf-course</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>Timber Creek Golf Course</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>Dixon</t>
+        </is>
+      </c>
+      <c r="H835" t="n">
+        <v>41.8396</v>
+      </c>
+      <c r="I835" t="n">
+        <v>-89.4716</v>
+      </c>
+      <c r="J835" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K835" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>il-van-horne-woods</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>Van Horne Woods</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>Plainfield</t>
+        </is>
+      </c>
+      <c r="H836" t="n">
+        <v>41.6389</v>
+      </c>
+      <c r="I836" t="n">
+        <v>-88.23</v>
+      </c>
+      <c r="J836" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K836" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>il-west-park</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>West Park</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>Joliet</t>
+        </is>
+      </c>
+      <c r="H837" t="n">
+        <v>41.5261</v>
+      </c>
+      <c r="I837" t="n">
+        <v>-88.083</v>
+      </c>
+      <c r="J837" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K837" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>il-youth-acres</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>Youth Acres</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>Canton</t>
+        </is>
+      </c>
+      <c r="H838" t="n">
+        <v>40.5465</v>
+      </c>
+      <c r="I838" t="n">
+        <v>-89.89</v>
+      </c>
+      <c r="J838" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K838" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>il-artesian-park</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>Artesian Park</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>Flanagan</t>
+        </is>
+      </c>
+      <c r="H839" t="n">
+        <v>40.8639</v>
+      </c>
+      <c r="I839" t="n">
+        <v>-88.6328</v>
+      </c>
+      <c r="J839" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K839" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>il-flanagan-disc-golf-park</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>Flanagan Disc Golf Park</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>Flanagan</t>
+        </is>
+      </c>
+      <c r="H840" t="n">
+        <v>40.8639</v>
+      </c>
+      <c r="I840" t="n">
+        <v>-88.6328</v>
+      </c>
+      <c r="J840" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K840" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>il-generation-brewing-company</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>Generation Brewing Company</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>Freeport</t>
+        </is>
+      </c>
+      <c r="H841" t="n">
+        <v>42.2959</v>
+      </c>
+      <c r="I841" t="n">
+        <v>-89.61369999999999</v>
+      </c>
+      <c r="J841" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K841" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>il-highland-community-college</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>Highland Community College</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>Freeport</t>
+        </is>
+      </c>
+      <c r="H842" t="n">
+        <v>42.2959</v>
+      </c>
+      <c r="I842" t="n">
+        <v>-89.61369999999999</v>
+      </c>
+      <c r="J842" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K842" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>il-krape-park</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>Krape Park</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>Freeport</t>
+        </is>
+      </c>
+      <c r="H843" t="n">
+        <v>42.2959</v>
+      </c>
+      <c r="I843" t="n">
+        <v>-89.61369999999999</v>
+      </c>
+      <c r="J843" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K843" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>il-salem4youth-ranch</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>Salem4Youth Ranch</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>Flanagan</t>
+        </is>
+      </c>
+      <c r="H844" t="n">
+        <v>40.8639</v>
+      </c>
+      <c r="I844" t="n">
+        <v>-88.6328</v>
+      </c>
+      <c r="J844" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K844" t="inlineStr">
+        <is>
+          <t>DiscGolfScene</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>A. J. Jolly Park</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>Alexandria</t>
+        </is>
+      </c>
+      <c r="D845" t="n">
+        <v>18</v>
+      </c>
+      <c r="E845" t="n">
+        <v>38.9764</v>
+      </c>
+      <c r="F845" t="n">
+        <v>-84.4216</v>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H845" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>Aldersgate Camp and Retreat</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>Ravenna</t>
+        </is>
+      </c>
+      <c r="D846" t="n">
+        <v>9</v>
+      </c>
+      <c r="E846" t="n">
+        <v>38.1667</v>
+      </c>
+      <c r="F846" t="n">
+        <v>-84.0667</v>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H846" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>Alexandria Community Park</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>Alexandria</t>
+        </is>
+      </c>
+      <c r="D847" t="n">
+        <v>9</v>
+      </c>
+      <c r="E847" t="n">
+        <v>38.9764</v>
+      </c>
+      <c r="F847" t="n">
+        <v>-84.4216</v>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H847" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>All Saints Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>Leitchfield</t>
+        </is>
+      </c>
+      <c r="D848" t="n">
+        <v>9</v>
+      </c>
+      <c r="E848" t="n">
+        <v>37.4514</v>
+      </c>
+      <c r="F848" t="n">
+        <v>-86.3048</v>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H848" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>American Legion Park</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D849" t="n">
+        <v>9</v>
+      </c>
+      <c r="E849" t="n">
+        <v>36.9962</v>
+      </c>
+      <c r="F849" t="n">
+        <v>-86.00700000000001</v>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H849" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>Anderson Community Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>Lawrenceburg</t>
+        </is>
+      </c>
+      <c r="D850" t="n">
+        <v>18</v>
+      </c>
+      <c r="E850" t="n">
+        <v>38.0237</v>
+      </c>
+      <c r="F850" t="n">
+        <v>-84.8845</v>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H850" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>Anderson-Dean Community Park</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>Harrodsburg</t>
+        </is>
+      </c>
+      <c r="D851" t="n">
+        <v>18</v>
+      </c>
+      <c r="E851" t="n">
+        <v>37.7485</v>
+      </c>
+      <c r="F851" t="n">
+        <v>-84.8428</v>
+      </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H851" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>Another Man&amp;#039;s Treasure</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>Leitchfield</t>
+        </is>
+      </c>
+      <c r="D852" t="n">
+        <v>18</v>
+      </c>
+      <c r="E852" t="n">
+        <v>37.4514</v>
+      </c>
+      <c r="F852" t="n">
+        <v>-86.3048</v>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H852" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>Armco Blue</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>Ashland</t>
+        </is>
+      </c>
+      <c r="D853" t="n">
+        <v>18</v>
+      </c>
+      <c r="E853" t="n">
+        <v>38.4713</v>
+      </c>
+      <c r="F853" t="n">
+        <v>-82.6386</v>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H853" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>Armco White</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>Ashland</t>
+        </is>
+      </c>
+      <c r="D854" t="n">
+        <v>18</v>
+      </c>
+      <c r="E854" t="n">
+        <v>38.4713</v>
+      </c>
+      <c r="F854" t="n">
+        <v>-82.6386</v>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H854" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>Arrowhead Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>Louisville</t>
+        </is>
+      </c>
+      <c r="D855" t="n">
+        <v>27</v>
+      </c>
+      <c r="E855" t="n">
+        <v>38.2527</v>
+      </c>
+      <c r="F855" t="n">
+        <v>-85.7585</v>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H855" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>Atkinson Hills Hybrid</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>Henderson</t>
+        </is>
+      </c>
+      <c r="D856" t="n">
+        <v>18</v>
+      </c>
+      <c r="E856" t="n">
+        <v>37.8372</v>
+      </c>
+      <c r="F856" t="n">
+        <v>-87.5741</v>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H856" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>Atkinson Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>Henderson</t>
+        </is>
+      </c>
+      <c r="D857" t="n">
+        <v>18</v>
+      </c>
+      <c r="E857" t="n">
+        <v>37.8372</v>
+      </c>
+      <c r="F857" t="n">
+        <v>-87.5741</v>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H857" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>Baker Park</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>Dixon</t>
+        </is>
+      </c>
+      <c r="D858" t="n">
+        <v>9</v>
+      </c>
+      <c r="E858" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="F858" t="n">
+        <v>-86.90000000000001</v>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H858" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>Basil Griffin Park</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>Bowling Green</t>
+        </is>
+      </c>
+      <c r="D859" t="n">
+        <v>18</v>
+      </c>
+      <c r="E859" t="n">
+        <v>42.0004</v>
+      </c>
+      <c r="F859" t="n">
+        <v>-86.4915</v>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H859" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>Berea College Glade</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>Berea</t>
+        </is>
+      </c>
+      <c r="D860" t="n">
+        <v>9</v>
+      </c>
+      <c r="E860" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="F860" t="n">
+        <v>-84.3</v>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H860" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>Bobby Bland Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>Leitchfield</t>
+        </is>
+      </c>
+      <c r="D861" t="n">
+        <v>18</v>
+      </c>
+      <c r="E861" t="n">
+        <v>37.4514</v>
+      </c>
+      <c r="F861" t="n">
+        <v>-86.3048</v>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H861" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>Boone Woods Park</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>Burlington</t>
+        </is>
+      </c>
+      <c r="D862" t="n">
+        <v>18</v>
+      </c>
+      <c r="E862" t="n">
+        <v>38.9859</v>
+      </c>
+      <c r="F862" t="n">
+        <v>-84.7343</v>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H862" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>Briar Creek Park</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>Williamsburg</t>
+        </is>
+      </c>
+      <c r="D863" t="n">
+        <v>9</v>
+      </c>
+      <c r="E863" t="n">
+        <v>36.7353</v>
+      </c>
+      <c r="F863" t="n">
+        <v>-84.1896</v>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H863" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>Bullitt County Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>Louisville</t>
+        </is>
+      </c>
+      <c r="D864" t="n">
+        <v>9</v>
+      </c>
+      <c r="E864" t="n">
+        <v>38.2527</v>
+      </c>
+      <c r="F864" t="n">
+        <v>-85.7585</v>
+      </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H864" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>Butchertown</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>Elizabethtown</t>
+        </is>
+      </c>
+      <c r="D865" t="n">
+        <v>18</v>
+      </c>
+      <c r="E865" t="n">
+        <v>37.6909</v>
+      </c>
+      <c r="F865" t="n">
+        <v>-85.8622</v>
+      </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H865" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>Camp Catalpa Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="D866" t="n">
+        <v>18</v>
+      </c>
+      <c r="E866" t="n">
+        <v>37.7399</v>
+      </c>
+      <c r="F866" t="n">
+        <v>-84.2433</v>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H866" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>Camp Loucon</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>Leitchfield</t>
+        </is>
+      </c>
+      <c r="D867" t="n">
+        <v>18</v>
+      </c>
+      <c r="E867" t="n">
+        <v>37.4514</v>
+      </c>
+      <c r="F867" t="n">
+        <v>-86.3048</v>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H867" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>Cave Run Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>Morehead</t>
+        </is>
+      </c>
+      <c r="D868" t="n">
+        <v>18</v>
+      </c>
+      <c r="E868" t="n">
+        <v>38.6878</v>
+      </c>
+      <c r="F868" t="n">
+        <v>-83.4284</v>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H868" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>Cave Springs Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>Falls of Rough</t>
+        </is>
+      </c>
+      <c r="D869" t="n">
+        <v>9</v>
+      </c>
+      <c r="E869" t="n">
+        <v>37.7394</v>
+      </c>
+      <c r="F869" t="n">
+        <v>-86.64830000000001</v>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H869" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>Centennial Park</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>Wilmore</t>
+        </is>
+      </c>
+      <c r="D870" t="n">
+        <v>9</v>
+      </c>
+      <c r="E870" t="n">
+        <v>38.3631</v>
+      </c>
+      <c r="F870" t="n">
+        <v>-84.62139999999999</v>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H870" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>Central Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>Murray</t>
+        </is>
+      </c>
+      <c r="D871" t="n">
+        <v>27</v>
+      </c>
+      <c r="E871" t="n">
+        <v>36.6084</v>
+      </c>
+      <c r="F871" t="n">
+        <v>-88.3143</v>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H871" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>Chalybeate Springs Sports Complex</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>Smiths Grove</t>
+        </is>
+      </c>
+      <c r="D872" t="n">
+        <v>18</v>
+      </c>
+      <c r="E872" t="n">
+        <v>42</v>
+      </c>
+      <c r="F872" t="n">
+        <v>-86.8</v>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H872" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>Champions Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>Louisville</t>
+        </is>
+      </c>
+      <c r="D873" t="n">
+        <v>18</v>
+      </c>
+      <c r="E873" t="n">
+        <v>38.2527</v>
+      </c>
+      <c r="F873" t="n">
+        <v>-85.7585</v>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H873" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>Charles Black City Park</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>Morgantown</t>
+        </is>
+      </c>
+      <c r="D874" t="n">
+        <v>18</v>
+      </c>
+      <c r="E874" t="n">
+        <v>37.2147</v>
+      </c>
+      <c r="F874" t="n">
+        <v>-86.7251</v>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H874" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>Charlie Vettiner Park</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>Louisville</t>
+        </is>
+      </c>
+      <c r="D875" t="n">
+        <v>18</v>
+      </c>
+      <c r="E875" t="n">
+        <v>38.2527</v>
+      </c>
+      <c r="F875" t="n">
+        <v>-85.7585</v>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H875" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>Clarkson City Park</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>Clarkson</t>
+        </is>
+      </c>
+      <c r="D876" t="n">
+        <v>18</v>
+      </c>
+      <c r="E876" t="n">
+        <v>37.4333</v>
+      </c>
+      <c r="F876" t="n">
+        <v>-86.8167</v>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H876" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>Devou Park</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>Covington</t>
+        </is>
+      </c>
+      <c r="D877" t="n">
+        <v>18</v>
+      </c>
+      <c r="E877" t="n">
+        <v>38.909</v>
+      </c>
+      <c r="F877" t="n">
+        <v>-84.5008</v>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H877" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>Diamond Lake Resort</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>Owensboro</t>
+        </is>
+      </c>
+      <c r="D878" t="n">
+        <v>9</v>
+      </c>
+      <c r="E878" t="n">
+        <v>37.7793</v>
+      </c>
+      <c r="F878" t="n">
+        <v>-87.1129</v>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H878" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>Doctor&amp;#039;s Park Disc Golf</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>Calvert City</t>
+        </is>
+      </c>
+      <c r="D879" t="n">
+        <v>9</v>
+      </c>
+      <c r="E879" t="n">
+        <v>37.3843</v>
+      </c>
+      <c r="F879" t="n">
+        <v>-88.3531</v>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H879" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>East Frankfort Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>Frankfort</t>
+        </is>
+      </c>
+      <c r="D880" t="n">
+        <v>24</v>
+      </c>
+      <c r="E880" t="n">
+        <v>38.2009</v>
+      </c>
+      <c r="F880" t="n">
+        <v>-84.8733</v>
+      </c>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H880" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>Ephram White Park</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>Bowling Green</t>
+        </is>
+      </c>
+      <c r="D881" t="n">
+        <v>18</v>
+      </c>
+      <c r="E881" t="n">
+        <v>42.0004</v>
+      </c>
+      <c r="F881" t="n">
+        <v>-86.4915</v>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H881" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>Eubank City Park</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>Eubank</t>
+        </is>
+      </c>
+      <c r="D882" t="n">
+        <v>24</v>
+      </c>
+      <c r="E882" t="n">
+        <v>37.2167</v>
+      </c>
+      <c r="F882" t="n">
+        <v>-84.6833</v>
+      </c>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H882" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>Franklin - Simpson Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>Franklin</t>
+        </is>
+      </c>
+      <c r="D883" t="n">
+        <v>18</v>
+      </c>
+      <c r="E883" t="n">
+        <v>35.1666</v>
+      </c>
+      <c r="F883" t="n">
+        <v>-86.58329999999999</v>
+      </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H883" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>Freeman Lake Park</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>Elizabethtown</t>
+        </is>
+      </c>
+      <c r="D884" t="n">
+        <v>18</v>
+      </c>
+      <c r="E884" t="n">
+        <v>37.6909</v>
+      </c>
+      <c r="F884" t="n">
+        <v>-85.8622</v>
+      </c>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H884" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>Fulton</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>Fulton</t>
+        </is>
+      </c>
+      <c r="D885" t="n">
+        <v>18</v>
+      </c>
+      <c r="E885" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="F885" t="n">
+        <v>-88.8167</v>
+      </c>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H885" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>Gamaliel Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>Gamaliel</t>
+        </is>
+      </c>
+      <c r="D886" t="n">
+        <v>9</v>
+      </c>
+      <c r="E886" t="n">
+        <v>36.7667</v>
+      </c>
+      <c r="F886" t="n">
+        <v>-85.83329999999999</v>
+      </c>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H886" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>Georgetown College</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>Georgetown</t>
+        </is>
+      </c>
+      <c r="D887" t="n">
+        <v>18</v>
+      </c>
+      <c r="E887" t="n">
+        <v>38.1951</v>
+      </c>
+      <c r="F887" t="n">
+        <v>-84.2304</v>
+      </c>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H887" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>Graham Memorial Park</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="D888" t="n">
+        <v>18</v>
+      </c>
+      <c r="E888" t="n">
+        <v>37.5729</v>
+      </c>
+      <c r="F888" t="n">
+        <v>-85.2514</v>
+      </c>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H888" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>Grant County Park</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>Crittenden</t>
+        </is>
+      </c>
+      <c r="D889" t="n">
+        <v>18</v>
+      </c>
+      <c r="E889" t="n">
+        <v>38.2493</v>
+      </c>
+      <c r="F889" t="n">
+        <v>-84.9344</v>
+      </c>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H889" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>Graviss McDonald&amp;#039;s Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>Versaille</t>
+        </is>
+      </c>
+      <c r="D890" t="n">
+        <v>18</v>
+      </c>
+      <c r="E890" t="n">
+        <v>38.0512</v>
+      </c>
+      <c r="F890" t="n">
+        <v>-84.7268</v>
+      </c>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H890" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>Greensburg Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>Greensburg</t>
+        </is>
+      </c>
+      <c r="D891" t="n">
+        <v>9</v>
+      </c>
+      <c r="E891" t="n">
+        <v>37.2614</v>
+      </c>
+      <c r="F891" t="n">
+        <v>-85.5064</v>
+      </c>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H891" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>H.H. Lovett Park</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>Benton</t>
+        </is>
+      </c>
+      <c r="D892" t="n">
+        <v>9</v>
+      </c>
+      <c r="E892" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="F892" t="n">
+        <v>-88.3</v>
+      </c>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H892" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>Harry Hill Park</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>Eminence</t>
+        </is>
+      </c>
+      <c r="D893" t="n">
+        <v>9</v>
+      </c>
+      <c r="E893" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="F893" t="n">
+        <v>-84.90000000000001</v>
+      </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H893" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>Henderson Hills</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>Henderson</t>
+        </is>
+      </c>
+      <c r="D894" t="n">
+        <v>18</v>
+      </c>
+      <c r="E894" t="n">
+        <v>37.8372</v>
+      </c>
+      <c r="F894" t="n">
+        <v>-87.5741</v>
+      </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H894" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>Henry Jackson Park</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>Danville</t>
+        </is>
+      </c>
+      <c r="D895" t="n">
+        <v>18</v>
+      </c>
+      <c r="E895" t="n">
+        <v>37.6433</v>
+      </c>
+      <c r="F895" t="n">
+        <v>-84.7728</v>
+      </c>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H895" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>Highland Hills Park</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>Fort Thomas</t>
+        </is>
+      </c>
+      <c r="D896" t="n">
+        <v>9</v>
+      </c>
+      <c r="E896" t="n">
+        <v>38.9459</v>
+      </c>
+      <c r="F896" t="n">
+        <v>-84.45310000000001</v>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H896" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>Highview Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>Louisville</t>
+        </is>
+      </c>
+      <c r="D897" t="n">
+        <v>18</v>
+      </c>
+      <c r="E897" t="n">
+        <v>38.2527</v>
+      </c>
+      <c r="F897" t="n">
+        <v>-85.7585</v>
+      </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H897" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>Hobson Grove Park - Original</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>Bowling Green</t>
+        </is>
+      </c>
+      <c r="D898" t="n">
+        <v>18</v>
+      </c>
+      <c r="E898" t="n">
+        <v>42.0004</v>
+      </c>
+      <c r="F898" t="n">
+        <v>-86.4915</v>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H898" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>Idlewild</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>Burlington</t>
+        </is>
+      </c>
+      <c r="D899" t="n">
+        <v>24</v>
+      </c>
+      <c r="E899" t="n">
+        <v>38.9859</v>
+      </c>
+      <c r="F899" t="n">
+        <v>-84.7343</v>
+      </c>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H899" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>Indian Creek Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>Mount Sterling</t>
+        </is>
+      </c>
+      <c r="D900" t="n">
+        <v>18</v>
+      </c>
+      <c r="E900" t="n">
+        <v>38.0563</v>
+      </c>
+      <c r="F900" t="n">
+        <v>-83.9483</v>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H900" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>Ironworks Hills Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>Winchester</t>
+        </is>
+      </c>
+      <c r="D901" t="n">
+        <v>18</v>
+      </c>
+      <c r="E901" t="n">
+        <v>38.4805</v>
+      </c>
+      <c r="F901" t="n">
+        <v>-84.1747</v>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H901" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>Iroquois Park</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>Louisville</t>
+        </is>
+      </c>
+      <c r="D902" t="n">
+        <v>18</v>
+      </c>
+      <c r="E902" t="n">
+        <v>38.2527</v>
+      </c>
+      <c r="F902" t="n">
+        <v>-85.7585</v>
+      </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H902" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>Jacobson Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>Lexington</t>
+        </is>
+      </c>
+      <c r="D903" t="n">
+        <v>18</v>
+      </c>
+      <c r="E903" t="n">
+        <v>38.0304</v>
+      </c>
+      <c r="F903" t="n">
+        <v>-84.8753</v>
+      </c>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H903" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>James Lane Allen Elementary</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>Lexington</t>
+        </is>
+      </c>
+      <c r="D904" t="n">
+        <v>9</v>
+      </c>
+      <c r="E904" t="n">
+        <v>38.0304</v>
+      </c>
+      <c r="F904" t="n">
+        <v>-84.8753</v>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H904" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>Kereiakes Park</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>Bowling Green</t>
+        </is>
+      </c>
+      <c r="D905" t="n">
+        <v>18</v>
+      </c>
+      <c r="E905" t="n">
+        <v>42.0004</v>
+      </c>
+      <c r="F905" t="n">
+        <v>-86.4915</v>
+      </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H905" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>Kess Creek Park Disc Golf</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>Mayfield</t>
+        </is>
+      </c>
+      <c r="D906" t="n">
+        <v>18</v>
+      </c>
+      <c r="E906" t="n">
+        <v>36.7429</v>
+      </c>
+      <c r="F906" t="n">
+        <v>-88.63330000000001</v>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H906" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>Lake Cumberland State Resort Park</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>Jamestown</t>
+        </is>
+      </c>
+      <c r="D907" t="n">
+        <v>18</v>
+      </c>
+      <c r="E907" t="n">
+        <v>37.0668</v>
+      </c>
+      <c r="F907" t="n">
+        <v>-85.0402</v>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H907" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>Lake Mingo Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>Nicholasville</t>
+        </is>
+      </c>
+      <c r="D908" t="n">
+        <v>9</v>
+      </c>
+      <c r="E908" t="n">
+        <v>38.5179</v>
+      </c>
+      <c r="F908" t="n">
+        <v>-84.5575</v>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H908" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>Lakeview Park Disc Golf</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>Frankfort</t>
+        </is>
+      </c>
+      <c r="D909" t="n">
+        <v>18</v>
+      </c>
+      <c r="E909" t="n">
+        <v>38.2009</v>
+      </c>
+      <c r="F909" t="n">
+        <v>-84.8733</v>
+      </c>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H909" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>Lawrenceburg City Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>Lawrenceburg</t>
+        </is>
+      </c>
+      <c r="D910" t="n">
+        <v>9</v>
+      </c>
+      <c r="E910" t="n">
+        <v>38.0237</v>
+      </c>
+      <c r="F910" t="n">
+        <v>-84.8845</v>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H910" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>Lincoln Homestead State Park</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D911" t="n">
+        <v>18</v>
+      </c>
+      <c r="E911" t="n">
+        <v>37.6885</v>
+      </c>
+      <c r="F911" t="n">
+        <v>-85.23399999999999</v>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H911" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>Lincoln Ridge/Banklick Woods Park</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>Independence</t>
+        </is>
+      </c>
+      <c r="D912" t="n">
+        <v>24</v>
+      </c>
+      <c r="E912" t="n">
+        <v>38.9904</v>
+      </c>
+      <c r="F912" t="n">
+        <v>-84.5539</v>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H912" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>Lion&amp;#039;s Club Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>Island</t>
+        </is>
+      </c>
+      <c r="D913" t="n">
+        <v>9</v>
+      </c>
+      <c r="E913" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="F913" t="n">
+        <v>-86.8</v>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H913" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>Livermore Riverfront Park</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>Livermore</t>
+        </is>
+      </c>
+      <c r="D914" t="n">
+        <v>9</v>
+      </c>
+      <c r="E914" t="n">
+        <v>37.9147</v>
+      </c>
+      <c r="F914" t="n">
+        <v>-86.4906</v>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H914" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>Lovers Lane Park</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>Bowling Green</t>
+        </is>
+      </c>
+      <c r="D915" t="n">
+        <v>18</v>
+      </c>
+      <c r="E915" t="n">
+        <v>42.0004</v>
+      </c>
+      <c r="F915" t="n">
+        <v>-86.4915</v>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H915" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>Lykin&amp;#039;s Creek Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>Winchester</t>
+        </is>
+      </c>
+      <c r="D916" t="n">
+        <v>9</v>
+      </c>
+      <c r="E916" t="n">
+        <v>38.4805</v>
+      </c>
+      <c r="F916" t="n">
+        <v>-84.1747</v>
+      </c>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H916" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>Madisonville City Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>Madisonville</t>
+        </is>
+      </c>
+      <c r="D917" t="n">
+        <v>18</v>
+      </c>
+      <c r="E917" t="n">
+        <v>37.3265</v>
+      </c>
+      <c r="F917" t="n">
+        <v>-87.4983</v>
+      </c>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H917" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>Mahr Park Championship Course</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>Madisonville</t>
+        </is>
+      </c>
+      <c r="D918" t="n">
+        <v>18</v>
+      </c>
+      <c r="E918" t="n">
+        <v>37.3265</v>
+      </c>
+      <c r="F918" t="n">
+        <v>-87.4983</v>
+      </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H918" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>Mahr Park Recreational Course</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>Madisonville</t>
+        </is>
+      </c>
+      <c r="D919" t="n">
+        <v>18</v>
+      </c>
+      <c r="E919" t="n">
+        <v>37.3265</v>
+      </c>
+      <c r="F919" t="n">
+        <v>-87.4983</v>
+      </c>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H919" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>Mammoth Valley Park</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>Cave City</t>
+        </is>
+      </c>
+      <c r="D920" t="n">
+        <v>9</v>
+      </c>
+      <c r="E920" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="F920" t="n">
+        <v>-86.09999999999999</v>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H920" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>Marion Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>Marion</t>
+        </is>
+      </c>
+      <c r="D921" t="n">
+        <v>18</v>
+      </c>
+      <c r="E921" t="n">
+        <v>37.3324</v>
+      </c>
+      <c r="F921" t="n">
+        <v>-85.37350000000001</v>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H921" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>Meade Olin Park</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>Brandenburg</t>
+        </is>
+      </c>
+      <c r="D922" t="n">
+        <v>27</v>
+      </c>
+      <c r="E922" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="F922" t="n">
+        <v>-85.8</v>
+      </c>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H922" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>Meadowbrook Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>LEXINGTON</t>
+        </is>
+      </c>
+      <c r="D923" t="n">
+        <v>18</v>
+      </c>
+      <c r="E923" t="n">
+        <v>38.0304</v>
+      </c>
+      <c r="F923" t="n">
+        <v>-84.8753</v>
+      </c>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H923" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>Mike Miller County Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>Benton</t>
+        </is>
+      </c>
+      <c r="D924" t="n">
+        <v>18</v>
+      </c>
+      <c r="E924" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="F924" t="n">
+        <v>-88.3</v>
+      </c>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H924" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>Miller Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>Corbin</t>
+        </is>
+      </c>
+      <c r="D925" t="n">
+        <v>9</v>
+      </c>
+      <c r="E925" t="n">
+        <v>36.9447</v>
+      </c>
+      <c r="F925" t="n">
+        <v>-84.09350000000001</v>
+      </c>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H925" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>Morgantown City Park</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>Morgantown</t>
+        </is>
+      </c>
+      <c r="D926" t="n">
+        <v>9</v>
+      </c>
+      <c r="E926" t="n">
+        <v>37.2147</v>
+      </c>
+      <c r="F926" t="n">
+        <v>-86.7251</v>
+      </c>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H926" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>Muldraugh Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>Muldraugh</t>
+        </is>
+      </c>
+      <c r="D927" t="n">
+        <v>18</v>
+      </c>
+      <c r="E927" t="n">
+        <v>37.9167</v>
+      </c>
+      <c r="F927" t="n">
+        <v>-85.7167</v>
+      </c>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H927" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>Myer Creek Disc Golf Course - Yellow</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>Calhoun</t>
+        </is>
+      </c>
+      <c r="D928" t="n">
+        <v>9</v>
+      </c>
+      <c r="E928" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="F928" t="n">
+        <v>-86.40000000000001</v>
+      </c>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H928" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>Natcher Elementary</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>Bowling Green</t>
+        </is>
+      </c>
+      <c r="D929" t="n">
+        <v>3</v>
+      </c>
+      <c r="E929" t="n">
+        <v>42.0004</v>
+      </c>
+      <c r="F929" t="n">
+        <v>-86.4915</v>
+      </c>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H929" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>North Drive Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>Hopkinsville</t>
+        </is>
+      </c>
+      <c r="D930" t="n">
+        <v>9</v>
+      </c>
+      <c r="E930" t="n">
+        <v>36.8667</v>
+      </c>
+      <c r="F930" t="n">
+        <v>-87.4833</v>
+      </c>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H930" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>OCYMCA</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>Buckner</t>
+        </is>
+      </c>
+      <c r="D931" t="n">
+        <v>18</v>
+      </c>
+      <c r="E931" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="F931" t="n">
+        <v>-85.40000000000001</v>
+      </c>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H931" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>Ohio County Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>Hartford</t>
+        </is>
+      </c>
+      <c r="D932" t="n">
+        <v>18</v>
+      </c>
+      <c r="E932" t="n">
+        <v>37.4167</v>
+      </c>
+      <c r="F932" t="n">
+        <v>-86.86669999999999</v>
+      </c>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H932" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>Old Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>Calvert City</t>
+        </is>
+      </c>
+      <c r="D933" t="n">
+        <v>9</v>
+      </c>
+      <c r="E933" t="n">
+        <v>37.3843</v>
+      </c>
+      <c r="F933" t="n">
+        <v>-88.3531</v>
+      </c>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H933" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>Otter Creek Park</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>Brandenburg</t>
+        </is>
+      </c>
+      <c r="D934" t="n">
+        <v>27</v>
+      </c>
+      <c r="E934" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="F934" t="n">
+        <v>-85.8</v>
+      </c>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H934" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>Owen County High School</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>East Owenton</t>
+        </is>
+      </c>
+      <c r="D935" t="n">
+        <v>9</v>
+      </c>
+      <c r="E935" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="F935" t="n">
+        <v>-84.7</v>
+      </c>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H935" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>Panther Creek Park</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>Owensboro</t>
+        </is>
+      </c>
+      <c r="D936" t="n">
+        <v>18</v>
+      </c>
+      <c r="E936" t="n">
+        <v>37.7793</v>
+      </c>
+      <c r="F936" t="n">
+        <v>-87.1129</v>
+      </c>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H936" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>Phil Moore Park</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>Alvaton</t>
+        </is>
+      </c>
+      <c r="D937" t="n">
+        <v>18</v>
+      </c>
+      <c r="E937" t="n">
+        <v>42</v>
+      </c>
+      <c r="F937" t="n">
+        <v>-86.45</v>
+      </c>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H937" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>Pleasant View Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>Caneyville</t>
+        </is>
+      </c>
+      <c r="D938" t="n">
+        <v>18</v>
+      </c>
+      <c r="E938" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="F938" t="n">
+        <v>-86.7</v>
+      </c>
+      <c r="G938" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H938" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>Preston Miller Water Park</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>Bowling Green</t>
+        </is>
+      </c>
+      <c r="D939" t="n">
+        <v>18</v>
+      </c>
+      <c r="E939" t="n">
+        <v>42.0004</v>
+      </c>
+      <c r="F939" t="n">
+        <v>-86.4915</v>
+      </c>
+      <c r="G939" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H939" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>Promised Land DGC @ Faith Christian Camp</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>Annville</t>
+        </is>
+      </c>
+      <c r="D940" t="n">
+        <v>9</v>
+      </c>
+      <c r="E940" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="F940" t="n">
+        <v>-84</v>
+      </c>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H940" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>Pulaski County Park (Bottom)</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="D941" t="n">
+        <v>18</v>
+      </c>
+      <c r="E941" t="n">
+        <v>37.2667</v>
+      </c>
+      <c r="F941" t="n">
+        <v>-84.9333</v>
+      </c>
+      <c r="G941" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H941" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>Pulaski County Park (Top)</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="D942" t="n">
+        <v>18</v>
+      </c>
+      <c r="E942" t="n">
+        <v>37.2667</v>
+      </c>
+      <c r="F942" t="n">
+        <v>-84.9333</v>
+      </c>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H942" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>R.A. Jones Middle School</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>Florence</t>
+        </is>
+      </c>
+      <c r="D943" t="n">
+        <v>6</v>
+      </c>
+      <c r="E943" t="n">
+        <v>38.9915</v>
+      </c>
+      <c r="F943" t="n">
+        <v>-84.6641</v>
+      </c>
+      <c r="G943" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H943" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>Radcliff Disc Golf</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>Radcliff</t>
+        </is>
+      </c>
+      <c r="D944" t="n">
+        <v>18</v>
+      </c>
+      <c r="E944" t="n">
+        <v>37.8495</v>
+      </c>
+      <c r="F944" t="n">
+        <v>-85.9584</v>
+      </c>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H944" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>Redpoint Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>campton</t>
+        </is>
+      </c>
+      <c r="D945" t="n">
+        <v>18</v>
+      </c>
+      <c r="E945" t="n">
+        <v>38.2167</v>
+      </c>
+      <c r="F945" t="n">
+        <v>-83.4333</v>
+      </c>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H945" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>Riney B Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>Nicholasville</t>
+        </is>
+      </c>
+      <c r="D946" t="n">
+        <v>18</v>
+      </c>
+      <c r="E946" t="n">
+        <v>38.5179</v>
+      </c>
+      <c r="F946" t="n">
+        <v>-84.5575</v>
+      </c>
+      <c r="G946" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H946" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>River Hill Park Disc Golf</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>Lexington</t>
+        </is>
+      </c>
+      <c r="D947" t="n">
+        <v>9</v>
+      </c>
+      <c r="E947" t="n">
+        <v>38.0304</v>
+      </c>
+      <c r="F947" t="n">
+        <v>-84.8753</v>
+      </c>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H947" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>River of Life Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="D948" t="n">
+        <v>18</v>
+      </c>
+      <c r="E948" t="n">
+        <v>37.6885</v>
+      </c>
+      <c r="F948" t="n">
+        <v>-85.23399999999999</v>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>Rock River Ranch</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>Bowling Green</t>
+        </is>
+      </c>
+      <c r="D949" t="n">
+        <v>18</v>
+      </c>
+      <c r="E949" t="n">
+        <v>42.0004</v>
+      </c>
+      <c r="F949" t="n">
+        <v>-86.4915</v>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H949" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>Rocky Hollow Park</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>Somerset</t>
+        </is>
+      </c>
+      <c r="D950" t="n">
+        <v>18</v>
+      </c>
+      <c r="E950" t="n">
+        <v>37.0854</v>
+      </c>
+      <c r="F950" t="n">
+        <v>-84.61239999999999</v>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H950" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>Rough River Dam State Park</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>Falls of Rough</t>
+        </is>
+      </c>
+      <c r="D951" t="n">
+        <v>18</v>
+      </c>
+      <c r="E951" t="n">
+        <v>37.7394</v>
+      </c>
+      <c r="F951" t="n">
+        <v>-86.64830000000001</v>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H951" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>Ryan&amp;#039;s Course in Red Orchard Park</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>Shelbyville</t>
+        </is>
+      </c>
+      <c r="D952" t="n">
+        <v>18</v>
+      </c>
+      <c r="E952" t="n">
+        <v>38.1933</v>
+      </c>
+      <c r="F952" t="n">
+        <v>-85.2167</v>
+      </c>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H952" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>SKYCTC Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>Bowling Green</t>
+        </is>
+      </c>
+      <c r="D953" t="n">
+        <v>18</v>
+      </c>
+      <c r="E953" t="n">
+        <v>42.0004</v>
+      </c>
+      <c r="F953" t="n">
+        <v>-86.4915</v>
+      </c>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H953" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>Scott County Park</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>Georgetown</t>
+        </is>
+      </c>
+      <c r="D954" t="n">
+        <v>18</v>
+      </c>
+      <c r="E954" t="n">
+        <v>38.1951</v>
+      </c>
+      <c r="F954" t="n">
+        <v>-84.2304</v>
+      </c>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H954" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>Sheltowee Camp</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="D955" t="n">
+        <v>9</v>
+      </c>
+      <c r="E955" t="n">
+        <v>37.0901</v>
+      </c>
+      <c r="F955" t="n">
+        <v>-84.047</v>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H955" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>Shepherdsville Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>Shepherdsville</t>
+        </is>
+      </c>
+      <c r="D956" t="n">
+        <v>9</v>
+      </c>
+      <c r="E956" t="n">
+        <v>37.9818</v>
+      </c>
+      <c r="F956" t="n">
+        <v>-85.8202</v>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H956" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>Shillito Park</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>Lexington</t>
+        </is>
+      </c>
+      <c r="D957" t="n">
+        <v>18</v>
+      </c>
+      <c r="E957" t="n">
+        <v>38.0304</v>
+      </c>
+      <c r="F957" t="n">
+        <v>-84.8753</v>
+      </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H957" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>Smith Ridge Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>Campbellsville</t>
+        </is>
+      </c>
+      <c r="D958" t="n">
+        <v>9</v>
+      </c>
+      <c r="E958" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="F958" t="n">
+        <v>-85.3</v>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H958" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>South Fork Park</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>Florence</t>
+        </is>
+      </c>
+      <c r="D959" t="n">
+        <v>9</v>
+      </c>
+      <c r="E959" t="n">
+        <v>38.9915</v>
+      </c>
+      <c r="F959" t="n">
+        <v>-84.6641</v>
+      </c>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H959" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>Spencer Christian Park</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>Fisherville</t>
+        </is>
+      </c>
+      <c r="D960" t="n">
+        <v>9</v>
+      </c>
+      <c r="E960" t="n">
+        <v>38.0667</v>
+      </c>
+      <c r="F960" t="n">
+        <v>-85.5333</v>
+      </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>Stuart Nelson Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>Paducah</t>
+        </is>
+      </c>
+      <c r="D961" t="n">
+        <v>18</v>
+      </c>
+      <c r="E961" t="n">
+        <v>37.0839</v>
+      </c>
+      <c r="F961" t="n">
+        <v>-88.6001</v>
+      </c>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H961" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>The Tony Walker Financial Disc Golf Course at Buchanon Park</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>Bowling Green</t>
+        </is>
+      </c>
+      <c r="D962" t="n">
+        <v>18</v>
+      </c>
+      <c r="E962" t="n">
+        <v>42.0004</v>
+      </c>
+      <c r="F962" t="n">
+        <v>-86.4915</v>
+      </c>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H962" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>The Town of Ashland City Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>Ashland City</t>
+        </is>
+      </c>
+      <c r="D963" t="n">
+        <v>9</v>
+      </c>
+      <c r="E963" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="F963" t="n">
+        <v>-85.8</v>
+      </c>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H963" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>Thelma Stovall Park</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>Munfordville</t>
+        </is>
+      </c>
+      <c r="D964" t="n">
+        <v>9</v>
+      </c>
+      <c r="E964" t="n">
+        <v>37.3333</v>
+      </c>
+      <c r="F964" t="n">
+        <v>-85.86669999999999</v>
+      </c>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H964" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>Thompson RV Park</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>Barbourville</t>
+        </is>
+      </c>
+      <c r="D965" t="n">
+        <v>9</v>
+      </c>
+      <c r="E965" t="n">
+        <v>36.8847</v>
+      </c>
+      <c r="F965" t="n">
+        <v>-83.89109999999999</v>
+      </c>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H965" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>Three Rivers Disc Golf Park</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>Carrollton</t>
+        </is>
+      </c>
+      <c r="D966" t="n">
+        <v>18</v>
+      </c>
+      <c r="E966" t="n">
+        <v>38.6476</v>
+      </c>
+      <c r="F966" t="n">
+        <v>-85.16840000000001</v>
+      </c>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H966" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>Trager Family Foundation DGC @ Active Heroes</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>Shepherdsville</t>
+        </is>
+      </c>
+      <c r="D967" t="n">
+        <v>19</v>
+      </c>
+      <c r="E967" t="n">
+        <v>37.9818</v>
+      </c>
+      <c r="F967" t="n">
+        <v>-85.8202</v>
+      </c>
+      <c r="G967" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H967" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>Trail of Tears Park</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>Hopkinsville</t>
+        </is>
+      </c>
+      <c r="D968" t="n">
+        <v>18</v>
+      </c>
+      <c r="E968" t="n">
+        <v>36.8667</v>
+      </c>
+      <c r="F968" t="n">
+        <v>-87.4833</v>
+      </c>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H968" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>Trigg County Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>Cadiz</t>
+        </is>
+      </c>
+      <c r="D969" t="n">
+        <v>18</v>
+      </c>
+      <c r="E969" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="F969" t="n">
+        <v>-87.8</v>
+      </c>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H969" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>Turtle Woods</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>Franklin</t>
+        </is>
+      </c>
+      <c r="D970" t="n">
+        <v>9</v>
+      </c>
+      <c r="E970" t="n">
+        <v>35.1666</v>
+      </c>
+      <c r="F970" t="n">
+        <v>-86.58329999999999</v>
+      </c>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H970" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>Veterans Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>Lexington</t>
+        </is>
+      </c>
+      <c r="D971" t="n">
+        <v>18</v>
+      </c>
+      <c r="E971" t="n">
+        <v>38.0304</v>
+      </c>
+      <c r="F971" t="n">
+        <v>-84.8753</v>
+      </c>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H971" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>Vette City Disc Golf at Hobson Grove</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>Bowling Green</t>
+        </is>
+      </c>
+      <c r="D972" t="n">
+        <v>18</v>
+      </c>
+      <c r="E972" t="n">
+        <v>42.0004</v>
+      </c>
+      <c r="F972" t="n">
+        <v>-86.4915</v>
+      </c>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H972" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>Vine Grove Optimist Disc Golf Park</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>Vine Grove</t>
+        </is>
+      </c>
+      <c r="D973" t="n">
+        <v>18</v>
+      </c>
+      <c r="E973" t="n">
+        <v>37.8333</v>
+      </c>
+      <c r="F973" t="n">
+        <v>-85.9833</v>
+      </c>
+      <c r="G973" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H973" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>Walton Community Park</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>Walton</t>
+        </is>
+      </c>
+      <c r="D974" t="n">
+        <v>9</v>
+      </c>
+      <c r="E974" t="n">
+        <v>38.9411</v>
+      </c>
+      <c r="F974" t="n">
+        <v>-84.49250000000001</v>
+      </c>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H974" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>War Memorial Park</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>Oak Grove</t>
+        </is>
+      </c>
+      <c r="D975" t="n">
+        <v>18</v>
+      </c>
+      <c r="E975" t="n">
+        <v>36.8333</v>
+      </c>
+      <c r="F975" t="n">
+        <v>-87.2667</v>
+      </c>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H975" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>Wendell Moore Park</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>La Grange</t>
+        </is>
+      </c>
+      <c r="D976" t="n">
+        <v>18</v>
+      </c>
+      <c r="E976" t="n">
+        <v>38.41</v>
+      </c>
+      <c r="F976" t="n">
+        <v>-85.33329999999999</v>
+      </c>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H976" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>West Sixth Farm</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>Frankfort</t>
+        </is>
+      </c>
+      <c r="D977" t="n">
+        <v>18</v>
+      </c>
+      <c r="E977" t="n">
+        <v>38.2009</v>
+      </c>
+      <c r="F977" t="n">
+        <v>-84.8733</v>
+      </c>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H977" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>Western Kentucky University</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>Bowling Green</t>
+        </is>
+      </c>
+      <c r="D978" t="n">
+        <v>6</v>
+      </c>
+      <c r="E978" t="n">
+        <v>42.0004</v>
+      </c>
+      <c r="F978" t="n">
+        <v>-86.4915</v>
+      </c>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H978" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>Whitesville City Park</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>Whitesville</t>
+        </is>
+      </c>
+      <c r="D979" t="n">
+        <v>18</v>
+      </c>
+      <c r="E979" t="n">
+        <v>37.9667</v>
+      </c>
+      <c r="F979" t="n">
+        <v>-86.9333</v>
+      </c>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H979" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>Whitley Branch Veterans Park</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="D980" t="n">
+        <v>18</v>
+      </c>
+      <c r="E980" t="n">
+        <v>37.0901</v>
+      </c>
+      <c r="F980" t="n">
+        <v>-84.047</v>
+      </c>
+      <c r="G980" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H980" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>Wickliffe City Park - Ingevity Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>Wickliffe</t>
+        </is>
+      </c>
+      <c r="D981" t="n">
+        <v>9</v>
+      </c>
+      <c r="E981" t="n">
+        <v>36.95</v>
+      </c>
+      <c r="F981" t="n">
+        <v>-88.9833</v>
+      </c>
+      <c r="G981" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H981" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>Windy Trails</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>Leitchfield</t>
+        </is>
+      </c>
+      <c r="D982" t="n">
+        <v>18</v>
+      </c>
+      <c r="E982" t="n">
+        <v>37.4514</v>
+      </c>
+      <c r="F982" t="n">
+        <v>-86.3048</v>
+      </c>
+      <c r="G982" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H982" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>Wiseman Run Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>Winchester</t>
+        </is>
+      </c>
+      <c r="D983" t="n">
+        <v>6</v>
+      </c>
+      <c r="E983" t="n">
+        <v>38.4805</v>
+      </c>
+      <c r="F983" t="n">
+        <v>-84.1747</v>
+      </c>
+      <c r="G983" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H983" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>Wolf Knob Disc Golf Course at Hickory Cabins</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>Mammoth Cave</t>
+        </is>
+      </c>
+      <c r="D984" t="n">
+        <v>18</v>
+      </c>
+      <c r="E984" t="n">
+        <v>37.1866</v>
+      </c>
+      <c r="F984" t="n">
+        <v>-86.101</v>
+      </c>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H984" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>Woodhaven Country Club</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>Louisville</t>
+        </is>
+      </c>
+      <c r="D985" t="n">
+        <v>9</v>
+      </c>
+      <c r="E985" t="n">
+        <v>38.2527</v>
+      </c>
+      <c r="F985" t="n">
+        <v>-85.7585</v>
+      </c>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H985" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>Woods at Weldon</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="D986" t="n">
+        <v>18</v>
+      </c>
+      <c r="E986" t="n">
+        <v>36.9962</v>
+      </c>
+      <c r="F986" t="n">
+        <v>-86.00700000000001</v>
+      </c>
+      <c r="G986" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H986" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>Yellow Creek Park</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>Owensboro</t>
+        </is>
+      </c>
+      <c r="D987" t="n">
+        <v>36</v>
+      </c>
+      <c r="E987" t="n">
+        <v>37.7793</v>
+      </c>
+      <c r="F987" t="n">
+        <v>-87.1129</v>
+      </c>
+      <c r="G987" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="H987" t="inlineStr">
+        <is>
+          <t>PDGA course directory</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K474"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Chains Course Catalog.xlsx
+++ b/data/Chains Course Catalog.xlsx
@@ -711,12 +711,15 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Not started</t>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>150</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1615,7 +1618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K987"/>
+  <dimension ref="A1:K1137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -44012,6 +44015,5406 @@
         </is>
       </c>
     </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>pa-ace-eight-disc-</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>Ace Eight Disc Golf Course at DeSales University</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>Center Valley</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E988" t="n">
+        <v>18</v>
+      </c>
+      <c r="F988" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G988" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H988" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>pa-adventure-park-</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>Adventure Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>Mechanicsburg</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E989" t="n">
+        <v>9</v>
+      </c>
+      <c r="F989" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G989" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H989" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>pa-agape-farm-cham</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>Agape Farm Championship Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>Shirleysburg</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E990" t="n">
+        <v>18</v>
+      </c>
+      <c r="F990" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G990" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H990" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>pa-albion-disc-gol</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>Albion Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>Albion</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E991" t="n">
+        <v>9</v>
+      </c>
+      <c r="F991" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G991" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H991" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>pa-american-legion</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>American Legion Mtn. Post 781 Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>Mountain Top</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E992" t="n">
+        <v>18</v>
+      </c>
+      <c r="F992" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G992" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H992" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>pa-amrock-disc-gol</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>Amrock Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>Moon Township</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E993" t="n">
+        <v>6</v>
+      </c>
+      <c r="F993" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G993" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H993" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>pa-angelica-park</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>Angelica Park</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>Reading</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E994" t="n">
+        <v>9</v>
+      </c>
+      <c r="F994" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G994" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H994" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>pa-anson-b-nixon-</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>Anson B. Nixon Park</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>Kennett Square</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E995" t="n">
+        <v>19</v>
+      </c>
+      <c r="F995" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G995" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H995" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>pa-bear-creek-disc</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>Bear Creek Disc Golf - Birdie</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>Macungie</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E996" t="n">
+        <v>18</v>
+      </c>
+      <c r="F996" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G996" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H996" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>pa-beaver-creek-mi</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>Beaver Creek Mini Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>Strasburg</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E997" t="n">
+        <v>18</v>
+      </c>
+      <c r="F997" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G997" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H997" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>pa-bedford-school-</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>Bedford School District Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>Bedford</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E998" t="n">
+        <v>9</v>
+      </c>
+      <c r="F998" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G998" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H998" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>pa-bernel-road-par</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>Bernel Road Park</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>State College</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E999" t="n">
+        <v>18</v>
+      </c>
+      <c r="F999" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G999" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H999" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>pa-bethany-village</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>Bethany Village</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>Mechanicsburg</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1000" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1000" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1000" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1000" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>pa-big-beaver-disc</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>Big Beaver Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>Darlington</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1001" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1001" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1001" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1001" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>pa-blooming-glen-m</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>Blooming Glen Mennonite Church Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>Blooming Glen</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1002" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1002" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1002" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1002" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>pa-bloomsburg-town</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>Bloomsburg Town Park</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>Bloomsburg</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1003" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1003" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1003" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1003" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>pa-blue-marsh-lake</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>Blue Marsh Lake Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>Leesport</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1004" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1004" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1004" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1004" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>pa-blue-mountain-r</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>Blue Mountain Resort - Skyline Park</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>Palmerton</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1005" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1005" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1005" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1005" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>pa-blue-mountain-r</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>Blue Mountain Resort - Slopeside 9 at Summit Lodge</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>Palmerton</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1006" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1006" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1006" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1006" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>pa-blue-mountain-r</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>Blue Mountain Resort - Valley Park</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>Palmerton</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1007" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1007" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1007" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1007" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>pa-body-and-soul-c</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>Body and Soul Community Center</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>McVeytown</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1008" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1008" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1008" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1008" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>pa-bootleggers-cav</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>Bootleggers Cave</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>Green Lane</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1009" t="n">
+        <v>19</v>
+      </c>
+      <c r="F1009" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1009" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1009" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>pa-boulder-woods-a</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>Boulder Woods at Pinchot State Park</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>Lewisberry</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1010" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1010" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1010" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1010" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>pa-boyertown-park-</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>Boyertown Park Disc Golf</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>Boyertown</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1011" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1011" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1011" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1011" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>pa-branchwood-park</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>Branchwood Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>Franconia</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1012" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1012" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1012" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1012" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>pa-briar-creek-lak</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>Briar Creek Lake</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>Berwick</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1013" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1013" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1013" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1013" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>pa-broken-chains-d</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>Broken Chains Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>Lincoln University</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1014" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1014" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1014" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1014" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>pa-brubaker-park</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>Brubaker Park</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>East Earl</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1015" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1015" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1015" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1015" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>pa-brush-creek-par</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>Brush Creek Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>Beaver Falls</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1016" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1016" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1016" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1016" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>pa-buhl-park-disc-</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>Buhl Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>Hermitage</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1017" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1017" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1017" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1017" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>pa-butler-farm</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>Butler Farm</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>Waynesburg</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1018" t="n">
+        <v>20</v>
+      </c>
+      <c r="F1018" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1018" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1018" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>pa-butter-valley-g</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>Butter Valley Golf Port</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>Barto</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1019" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1019" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1019" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1019" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>pa-california-univ</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>California University of PA</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>Coal Center</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1020" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1020" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1020" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1020" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>pa-camp-kon-o-kwee</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>Camp Kon-O-Kwee</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>Fombell</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1021" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1021" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1021" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1021" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>pa-camp-mt-luther</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>Camp Mt. Luther Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>Mifflinburg</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1022" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1022" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1022" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1022" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>pa-camp-olympic-pa</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>Camp Olympic Park</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>Emmaus</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1023" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1023" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1023" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1023" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>pa-camp-sankanac-d</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>Camp Sankanac Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>Spring City</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1024" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1024" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1024" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1024" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>pa-camp-swatara</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>Camp Swatara</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>Bethel</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1025" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1025" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1025" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1025" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>pa-canoe-creek-sta</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>Canoe Creek State Park</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>Hollidaysburg</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1026" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1026" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1026" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1026" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>pa-cbk-mountain-ad</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>CBK Mountain Adventures Disc Golf</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>Tannersville</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1027" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1027" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1027" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1027" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>pa-central-park-di</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>Central Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>Doylestown</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1028" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1028" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1028" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1028" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>pa-circleville-par</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>Circleville Park Disc Golf</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>State College</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1029" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1029" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1029" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1029" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>pa-clarion-county-</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>Clarion County Park Disc Golf</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>Shippenville</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1030" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1030" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1030" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1030" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>pa-clarion-disc-go</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>Clarion Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>Shippenville</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1031" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1031" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1031" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1031" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>pa-clear-creek-sta</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>Clear Creek State Park</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>Sigel</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1032" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1032" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1032" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1032" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>pa-clearview-eleme</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>Clearview Elementary School Disc Golf</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>Brogue</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1033" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1033" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1033" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1033" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>pa-clemens-food-gr</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>Clemens Food Group Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>Harfield</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1034" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1034" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1034" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1034" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>pa-codorus-state-p</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>Codorus State Park - Blue</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>Hanover</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1035" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1035" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1035" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1035" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>pa-codorus-state-p</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>Codorus State Park - Purple</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>Hanover</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1036" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1036" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1036" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1036" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>pa-codorus-state-p</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>Codorus State Park - Red</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>Hanover</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1037" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1037" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1037" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1037" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>pa-codorus-townshi</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>Codorus Township Park</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>Glen Rock</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1038" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1038" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1038" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1038" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>pa-coleman-memoria</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>Coleman Memorial Park</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1039" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1039" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1039" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1039" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>pa-conestoga-creek</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>Conestoga Creek Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1040" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1040" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1040" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1040" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>pa-conrad-weiser-h</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>Conrad Weiser Homestead</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>Womelsdorf</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1041" t="n">
+        <v>20</v>
+      </c>
+      <c r="F1041" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1041" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1041" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>pa-cooley-crest-dg</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>Cooley Crest DGC</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>Centerville</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1042" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1042" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1042" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1042" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>pa-cove-valley-chr</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>Cove Valley Christian Youth Camp</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>Merscersburg</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1043" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1043" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1043" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1043" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>pa-covenant-villag</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>Covenant Village Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>Clearville</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1044" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1044" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1044" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1044" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>pa-covered-bridge-</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>Covered Bridge Park</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>Orefield</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1045" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1045" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1045" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1045" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>pa-coyote-hills</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>Coyote Hills</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>Carlisle</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1046" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1046" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1046" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1046" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>pa-creekside-disc-</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>Creekside Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>Camp Hill</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1047" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1047" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1047" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1047" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>pa-crestwood-high-</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>Crestwood High School</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>Mountaintop</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1048" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1048" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1048" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1048" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>pa-crooked-creek-l</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>Crooked Creek Lake Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>Ford City</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1049" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1049" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1049" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1049" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>pa-cross-keys-comm</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>Cross Keys Community Park</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>New Oxford</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1050" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1050" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1050" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1050" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>pa-d-f-buchmille</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>D. F. Buchmiller Park</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1051" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1051" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1051" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1051" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>pa-deer-lakes-park</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>Deer Lakes Park</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>Tarentum</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1052" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1052" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1052" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1052" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>pa-denver-memorial</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>Denver Memorial Park</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1053" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1053" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1053" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1053" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>pa-dogwood-acres-c</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>Dogwood Acres Campground</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>Newville</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1054" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1054" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1054" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1054" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>pa-earl-township-c</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>Earl Township Community Park</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>Boyertown</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1055" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1055" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1055" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1055" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>pa-east-hanover-to</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>East Hanover Township Community Park</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>Grantville</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1056" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1056" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1056" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1056" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>pa-east-pike-lower</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>East Pike Lower</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>Indiana</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1057" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1057" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1057" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1057" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>pa-east-pike-upper</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>East Pike Upper</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>Indiana</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1058" t="n">
+        <v>19</v>
+      </c>
+      <c r="F1058" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1058" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1058" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>pa-edinboro-univer</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>Edinboro University Royal Scots Disc Golf Links</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>Edinboro</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1059" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1059" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1059" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1059" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>pa-elizabeth-towns</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>Elizabeth Township Park</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>Brickerville</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1060" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1060" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1060" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1060" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>pa-elizabethtown-c</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>Elizabethtown College</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>Elizabathtown</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1061" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1061" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1061" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1061" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>pa-eurana-park</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>Eurana Park</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>Weatherly</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1062" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1062" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1062" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1062" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>pa-fairview-park-d</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>Fairview Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>Columbia</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1063" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1063" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1063" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1063" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>pa-farrandsville-p</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>Farrandsville Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>Farrandsville</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1064" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1064" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1064" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1064" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>pa-faylor-lake-dis</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>Faylor Lake DiscGolfPark</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>Beaver Springs</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1065" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1065" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1065" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1065" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>pa-forest-hills-di</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>Forest Hills DiscGolfPark</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>Carlisle</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1066" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1066" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1066" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1066" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>pa-fort-washington</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>Fort Washington State Park</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>Fort Washington</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1067" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1067" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1067" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1067" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>pa-francis-e-walt</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>Francis E. Walter Dam - Original</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>White Haven</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1068" t="n">
+        <v>20</v>
+      </c>
+      <c r="F1068" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1068" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1068" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>pa-francis-e-walt</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>Francis E. Walter Dam - Top</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>White Haven</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1069" t="n">
+        <v>17</v>
+      </c>
+      <c r="F1069" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1069" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1069" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>pa-freedom-farms-p</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>Freedom Farms Putt Patch</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>Butler</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1070" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1070" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1070" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1070" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>pa-french-creek-st</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>French Creek State Park</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>Elverson</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1071" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1071" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1071" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1071" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>pa-getty-heights-p</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>Getty Heights Park</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>Indiana</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1072" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1072" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1072" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1072" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>pa-grove-city-disc</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>Grove City Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>Grove City</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1073" t="n">
+        <v>21</v>
+      </c>
+      <c r="F1073" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1073" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1073" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>pa-hackett-park</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>Hackett Park</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>Easton</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1074" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1074" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1074" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1074" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>pa-hanover-townshi</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>Hanover Township Community Center</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>Bethlehem</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1075" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1075" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1075" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1075" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>pa-harcrest-park</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>Harcrest Park</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>Butler</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1076" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1076" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1076" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1076" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>pa-harmony-ridge-g</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>Harmony Ridge Golf Club</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>Ambridge</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1077" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1077" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1077" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1077" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>pa-harvest-fields</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>Harvest Fields</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>Boalsburg</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1078" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1078" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1078" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1078" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>pa-haverford-reser</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>Haverford Reserve</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>haverford</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1079" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1079" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1079" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1079" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>pa-herr-park-disc-</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>Herr Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1080" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1080" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1080" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1080" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>pa-hickory-heights</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>Hickory Heights Golf Course</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>Spring Grove</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1081" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1081" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1081" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1081" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>pa-hickory-run-sta</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>Hickory Run State Park</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>White Haven</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1082" t="n">
+        <v>19</v>
+      </c>
+      <c r="F1082" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1082" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1082" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>pa-hidden-hollow-d</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>Hidden Hollow Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>Dover</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1083" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1083" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1083" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1083" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>pa-highland-park</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>Highland Park</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>Altoona</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1084" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1084" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1084" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1084" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>pa-hobson-park-min</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>Hobson Park Mini Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1085" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1085" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1085" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1085" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>pa-hollidaysburg-s</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>Hollidaysburg School Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>Hollidaysburg</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1086" t="n">
+        <v>12</v>
+      </c>
+      <c r="F1086" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1086" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1086" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>pa-hometown-hollow</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>Hometown Hollow at Ryan Memorial Park</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>Tamaqua</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1087" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1087" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1087" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1087" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>pa-hotel-hershey</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>Hotel Hershey</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>Hershey</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1088" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1088" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1088" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1088" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>pa-hpc-disk-golf</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>HPC Disk Golf</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>gibsonia</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1089" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1089" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1089" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1089" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>pa-hunter-farm</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>Hunter Farm</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>Grove City</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1090" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1090" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1090" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1090" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>pa-indian-park-dis</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>Indian Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>Montoursville</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1091" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1091" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1091" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1091" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>pa-iup-college-lod</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>IUP College Lodge</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>Indiana</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1092" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1092" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1092" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1092" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>pa-jackson-recreat</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>Jackson Recreational Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>Myerstown</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1093" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1093" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1093" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1093" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>pa-jordan-creek-pa</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>Jordan Creek Park</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>Whitehall</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1094" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1094" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1094" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1094" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>pa-jumonville-camp</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>Jumonville Camp &amp; Retreat Center</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>Hopwood</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1095" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1095" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1095" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1095" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>pa-juniata-college</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>Juniata College</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>Huntingdon</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1096" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1096" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1096" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1096" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>pa-kenilworth-park</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>Kenilworth Park</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>Kenilworth</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1097" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1097" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1097" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1097" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>pa-kennedy-park-di</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>Kennedy Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>Forest City</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1098" t="n">
+        <v>12</v>
+      </c>
+      <c r="F1098" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1098" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1098" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>pa-kerr-park</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>Kerr Park</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>Downingtown</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1099" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1099" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1099" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1099" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>pa-kirchenwald-cro</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>Kirchenwald Crossing</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>Palmyra</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1100" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1100" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1100" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1100" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>pa-klines-run-disc</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>Klines Run Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>Wrightsville</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1101" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1101" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1101" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1101" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>pa-knob-hill-park</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>Knob Hill Park</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>Warrendale</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1102" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1102" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1102" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1102" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>pa-lakeside-discgo</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>Lakeside DiscGolfPark</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>Myerstown</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1103" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1103" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1103" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1103" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>pa-laserdome-mini-</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>Laserdome Mini Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>Manheim</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1104" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1104" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1104" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1104" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>pa-laurelain-disc-</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>Laurelain Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>Reading</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1105" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1105" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1105" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1105" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>pa-lehigh-valley-s</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>Lehigh Valley Sportsfest Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>Allentown</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1106" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1106" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1106" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1106" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>pa-lenape-park-(sk</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>Lenape Park (Skippack)</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>Collegeville</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1107" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1107" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1107" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1107" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>pa-lenni-lenape-pa</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>Lenni Lenape Park</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1108" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1108" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1108" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1108" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>pa-lime-bluff-recr</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>Lime Bluff Recreation Area</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>Hughesville</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1109" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1109" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1109" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1109" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>pa-linbrook-park</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>Linbrook Park</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>Pittsburgh</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1110" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1110" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1110" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1110" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>pa-linesville-park</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>Linesville Park</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>White Haven</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1111" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1111" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1111" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1111" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>pa-little-chiques-</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>Little Chiques Park</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>Mount Joy</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1112" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1112" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1112" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1112" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>pa-little-lehigh-p</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>Little Lehigh Parkway</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>Allentown</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1113" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1113" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1113" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1113" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>pa-long-trout-wine</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>Long Trout Winery</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>Auburn</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1114" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1114" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1114" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1114" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>pa-mammoth-park</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>Mammoth Park</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>Mount Pleasant</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1115" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1115" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1115" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1115" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>pa-messiah-college</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>Messiah College Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>Grantham</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1116" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1116" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1116" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1116" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>pa-messiah-lifeway</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>Messiah Lifeways Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>Mechanicsburg</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1117" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1117" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1117" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1117" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>pa-midd-west-disc-</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>Midd-West Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>Middleburg</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1118" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1118" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1118" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1118" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>pa-middle-smithfie</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>Middle Smithfield Park at Echo Lake</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>East Stroudsburg</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1119" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1119" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1119" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1119" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>pa-mini-disc-golf-</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>Mini Disc Golf Course at Mushroom Manor</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1120" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1120" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1120" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1120" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>pa-misericordia-un</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>Misericordia University DIsc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1121" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1121" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1121" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1121" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>pa-monroe-township</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>Monroe Township PA Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>Mechanicsburg</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1122" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1122" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1122" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1122" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>pa-monroeville-par</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>Monroeville Park</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>Monroeville</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1123" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1123" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1123" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1123" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>pa-moon-lake-park</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>Moon Lake Park</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>Hunlock Creek</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1124" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1124" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1124" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1124" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>pa-moore-township-</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>Moore Township Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1125" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1125" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1125" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1125" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>pa-moraine-state-p</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>Moraine State Park Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>Portersville</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1126" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1126" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1126" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1126" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>pa-morrisons-cove-</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>Morrisons Cove Memorial Park</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>Martinsburg</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1127" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1127" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1127" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1127" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>pa-mt-lebanon-cam</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>Mt. Lebanon Camp Meeting</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1128" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1128" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1128" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1128" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>pa-muddy-run-disc-</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>Muddy Run Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>Holtwood</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1129" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1129" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1129" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1129" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>pa-nawakwa-woods-d</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>Nawakwa Woods Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>Biglerville</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1130" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1130" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1130" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1130" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>pa-neff's-valley</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>Neff's Valley</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>Schnecksville</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1131" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1131" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1131" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1131" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>pa-nesbitt-park</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>Nesbitt Park</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>Wilkes-Barre</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1132" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1132" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1132" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1132" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>pa-new-hanover-com</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>New Hanover Community Park</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>Gilbertsville</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1133" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1133" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1133" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1133" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>pa-new-hopewell-di</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>New Hopewell Disc Golf Course</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>Shippensburg</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1134" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1134" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1134" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1134" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>pa-nockamixon-stat</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>Nockamixon State Park</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>Quakertown</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1135" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1135" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1135" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1135" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>pa-north-boundary-</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>North Boundary - Learn-to-Play</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>Cranberry Township</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1136" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1136" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1136" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1136" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>pa-north-boundary-</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>North Boundary Disc Golf Complex - Championship</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>Cranberry Township</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E1137" t="n">
+        <v>18</v>
+      </c>
+      <c r="F1137" t="n">
+        <v>40.5908</v>
+      </c>
+      <c r="G1137" t="n">
+        <v>-77.2098</v>
+      </c>
+      <c r="H1137" t="inlineStr">
+        <is>
+          <t>PDGA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K474"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Chains Course Catalog.xlsx
+++ b/data/Chains Course Catalog.xlsx
@@ -711,19 +711,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>150</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
       </c>
       <c r="F8" t="n">
         <v>7</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Pass 1: PDGA directory (150 verified). Continue with pass 2.</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1618,7 +1628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1137"/>
+  <dimension ref="A1:K987"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -44015,5406 +44025,6 @@
         </is>
       </c>
     </row>
-    <row r="988">
-      <c r="A988" t="inlineStr">
-        <is>
-          <t>pa-ace-eight-disc-</t>
-        </is>
-      </c>
-      <c r="B988" t="inlineStr">
-        <is>
-          <t>Ace Eight Disc Golf Course at DeSales University</t>
-        </is>
-      </c>
-      <c r="C988" t="inlineStr">
-        <is>
-          <t>Center Valley</t>
-        </is>
-      </c>
-      <c r="D988" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E988" t="n">
-        <v>18</v>
-      </c>
-      <c r="F988" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G988" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H988" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="989">
-      <c r="A989" t="inlineStr">
-        <is>
-          <t>pa-adventure-park-</t>
-        </is>
-      </c>
-      <c r="B989" t="inlineStr">
-        <is>
-          <t>Adventure Park Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C989" t="inlineStr">
-        <is>
-          <t>Mechanicsburg</t>
-        </is>
-      </c>
-      <c r="D989" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E989" t="n">
-        <v>9</v>
-      </c>
-      <c r="F989" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G989" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H989" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="990">
-      <c r="A990" t="inlineStr">
-        <is>
-          <t>pa-agape-farm-cham</t>
-        </is>
-      </c>
-      <c r="B990" t="inlineStr">
-        <is>
-          <t>Agape Farm Championship Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C990" t="inlineStr">
-        <is>
-          <t>Shirleysburg</t>
-        </is>
-      </c>
-      <c r="D990" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E990" t="n">
-        <v>18</v>
-      </c>
-      <c r="F990" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G990" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H990" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="991">
-      <c r="A991" t="inlineStr">
-        <is>
-          <t>pa-albion-disc-gol</t>
-        </is>
-      </c>
-      <c r="B991" t="inlineStr">
-        <is>
-          <t>Albion Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C991" t="inlineStr">
-        <is>
-          <t>Albion</t>
-        </is>
-      </c>
-      <c r="D991" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E991" t="n">
-        <v>9</v>
-      </c>
-      <c r="F991" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G991" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H991" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="992">
-      <c r="A992" t="inlineStr">
-        <is>
-          <t>pa-american-legion</t>
-        </is>
-      </c>
-      <c r="B992" t="inlineStr">
-        <is>
-          <t>American Legion Mtn. Post 781 Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C992" t="inlineStr">
-        <is>
-          <t>Mountain Top</t>
-        </is>
-      </c>
-      <c r="D992" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E992" t="n">
-        <v>18</v>
-      </c>
-      <c r="F992" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G992" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H992" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="993">
-      <c r="A993" t="inlineStr">
-        <is>
-          <t>pa-amrock-disc-gol</t>
-        </is>
-      </c>
-      <c r="B993" t="inlineStr">
-        <is>
-          <t>Amrock Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C993" t="inlineStr">
-        <is>
-          <t>Moon Township</t>
-        </is>
-      </c>
-      <c r="D993" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E993" t="n">
-        <v>6</v>
-      </c>
-      <c r="F993" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G993" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H993" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="994">
-      <c r="A994" t="inlineStr">
-        <is>
-          <t>pa-angelica-park</t>
-        </is>
-      </c>
-      <c r="B994" t="inlineStr">
-        <is>
-          <t>Angelica Park</t>
-        </is>
-      </c>
-      <c r="C994" t="inlineStr">
-        <is>
-          <t>Reading</t>
-        </is>
-      </c>
-      <c r="D994" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E994" t="n">
-        <v>9</v>
-      </c>
-      <c r="F994" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G994" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H994" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="995">
-      <c r="A995" t="inlineStr">
-        <is>
-          <t>pa-anson-b-nixon-</t>
-        </is>
-      </c>
-      <c r="B995" t="inlineStr">
-        <is>
-          <t>Anson B. Nixon Park</t>
-        </is>
-      </c>
-      <c r="C995" t="inlineStr">
-        <is>
-          <t>Kennett Square</t>
-        </is>
-      </c>
-      <c r="D995" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E995" t="n">
-        <v>19</v>
-      </c>
-      <c r="F995" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G995" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H995" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="996">
-      <c r="A996" t="inlineStr">
-        <is>
-          <t>pa-bear-creek-disc</t>
-        </is>
-      </c>
-      <c r="B996" t="inlineStr">
-        <is>
-          <t>Bear Creek Disc Golf - Birdie</t>
-        </is>
-      </c>
-      <c r="C996" t="inlineStr">
-        <is>
-          <t>Macungie</t>
-        </is>
-      </c>
-      <c r="D996" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E996" t="n">
-        <v>18</v>
-      </c>
-      <c r="F996" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G996" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H996" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="997">
-      <c r="A997" t="inlineStr">
-        <is>
-          <t>pa-beaver-creek-mi</t>
-        </is>
-      </c>
-      <c r="B997" t="inlineStr">
-        <is>
-          <t>Beaver Creek Mini Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C997" t="inlineStr">
-        <is>
-          <t>Strasburg</t>
-        </is>
-      </c>
-      <c r="D997" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E997" t="n">
-        <v>18</v>
-      </c>
-      <c r="F997" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G997" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H997" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="998">
-      <c r="A998" t="inlineStr">
-        <is>
-          <t>pa-bedford-school-</t>
-        </is>
-      </c>
-      <c r="B998" t="inlineStr">
-        <is>
-          <t>Bedford School District Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C998" t="inlineStr">
-        <is>
-          <t>Bedford</t>
-        </is>
-      </c>
-      <c r="D998" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E998" t="n">
-        <v>9</v>
-      </c>
-      <c r="F998" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G998" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H998" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="999">
-      <c r="A999" t="inlineStr">
-        <is>
-          <t>pa-bernel-road-par</t>
-        </is>
-      </c>
-      <c r="B999" t="inlineStr">
-        <is>
-          <t>Bernel Road Park</t>
-        </is>
-      </c>
-      <c r="C999" t="inlineStr">
-        <is>
-          <t>State College</t>
-        </is>
-      </c>
-      <c r="D999" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E999" t="n">
-        <v>18</v>
-      </c>
-      <c r="F999" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G999" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H999" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1000">
-      <c r="A1000" t="inlineStr">
-        <is>
-          <t>pa-bethany-village</t>
-        </is>
-      </c>
-      <c r="B1000" t="inlineStr">
-        <is>
-          <t>Bethany Village</t>
-        </is>
-      </c>
-      <c r="C1000" t="inlineStr">
-        <is>
-          <t>Mechanicsburg</t>
-        </is>
-      </c>
-      <c r="D1000" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1000" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1000" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1000" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1000" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1001">
-      <c r="A1001" t="inlineStr">
-        <is>
-          <t>pa-big-beaver-disc</t>
-        </is>
-      </c>
-      <c r="B1001" t="inlineStr">
-        <is>
-          <t>Big Beaver Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1001" t="inlineStr">
-        <is>
-          <t>Darlington</t>
-        </is>
-      </c>
-      <c r="D1001" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1001" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1001" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1001" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1001" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1002">
-      <c r="A1002" t="inlineStr">
-        <is>
-          <t>pa-blooming-glen-m</t>
-        </is>
-      </c>
-      <c r="B1002" t="inlineStr">
-        <is>
-          <t>Blooming Glen Mennonite Church Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1002" t="inlineStr">
-        <is>
-          <t>Blooming Glen</t>
-        </is>
-      </c>
-      <c r="D1002" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1002" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1002" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1002" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1002" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1003">
-      <c r="A1003" t="inlineStr">
-        <is>
-          <t>pa-bloomsburg-town</t>
-        </is>
-      </c>
-      <c r="B1003" t="inlineStr">
-        <is>
-          <t>Bloomsburg Town Park</t>
-        </is>
-      </c>
-      <c r="C1003" t="inlineStr">
-        <is>
-          <t>Bloomsburg</t>
-        </is>
-      </c>
-      <c r="D1003" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1003" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1003" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1003" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1003" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1004">
-      <c r="A1004" t="inlineStr">
-        <is>
-          <t>pa-blue-marsh-lake</t>
-        </is>
-      </c>
-      <c r="B1004" t="inlineStr">
-        <is>
-          <t>Blue Marsh Lake Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1004" t="inlineStr">
-        <is>
-          <t>Leesport</t>
-        </is>
-      </c>
-      <c r="D1004" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1004" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1004" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1004" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1004" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1005">
-      <c r="A1005" t="inlineStr">
-        <is>
-          <t>pa-blue-mountain-r</t>
-        </is>
-      </c>
-      <c r="B1005" t="inlineStr">
-        <is>
-          <t>Blue Mountain Resort - Skyline Park</t>
-        </is>
-      </c>
-      <c r="C1005" t="inlineStr">
-        <is>
-          <t>Palmerton</t>
-        </is>
-      </c>
-      <c r="D1005" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1005" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1005" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1005" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1005" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1006">
-      <c r="A1006" t="inlineStr">
-        <is>
-          <t>pa-blue-mountain-r</t>
-        </is>
-      </c>
-      <c r="B1006" t="inlineStr">
-        <is>
-          <t>Blue Mountain Resort - Slopeside 9 at Summit Lodge</t>
-        </is>
-      </c>
-      <c r="C1006" t="inlineStr">
-        <is>
-          <t>Palmerton</t>
-        </is>
-      </c>
-      <c r="D1006" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1006" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1006" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1006" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1006" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1007">
-      <c r="A1007" t="inlineStr">
-        <is>
-          <t>pa-blue-mountain-r</t>
-        </is>
-      </c>
-      <c r="B1007" t="inlineStr">
-        <is>
-          <t>Blue Mountain Resort - Valley Park</t>
-        </is>
-      </c>
-      <c r="C1007" t="inlineStr">
-        <is>
-          <t>Palmerton</t>
-        </is>
-      </c>
-      <c r="D1007" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1007" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1007" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1007" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1007" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1008">
-      <c r="A1008" t="inlineStr">
-        <is>
-          <t>pa-body-and-soul-c</t>
-        </is>
-      </c>
-      <c r="B1008" t="inlineStr">
-        <is>
-          <t>Body and Soul Community Center</t>
-        </is>
-      </c>
-      <c r="C1008" t="inlineStr">
-        <is>
-          <t>McVeytown</t>
-        </is>
-      </c>
-      <c r="D1008" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1008" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1008" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1008" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1008" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1009">
-      <c r="A1009" t="inlineStr">
-        <is>
-          <t>pa-bootleggers-cav</t>
-        </is>
-      </c>
-      <c r="B1009" t="inlineStr">
-        <is>
-          <t>Bootleggers Cave</t>
-        </is>
-      </c>
-      <c r="C1009" t="inlineStr">
-        <is>
-          <t>Green Lane</t>
-        </is>
-      </c>
-      <c r="D1009" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1009" t="n">
-        <v>19</v>
-      </c>
-      <c r="F1009" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1009" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1009" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1010">
-      <c r="A1010" t="inlineStr">
-        <is>
-          <t>pa-boulder-woods-a</t>
-        </is>
-      </c>
-      <c r="B1010" t="inlineStr">
-        <is>
-          <t>Boulder Woods at Pinchot State Park</t>
-        </is>
-      </c>
-      <c r="C1010" t="inlineStr">
-        <is>
-          <t>Lewisberry</t>
-        </is>
-      </c>
-      <c r="D1010" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1010" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1010" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1010" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1010" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1011">
-      <c r="A1011" t="inlineStr">
-        <is>
-          <t>pa-boyertown-park-</t>
-        </is>
-      </c>
-      <c r="B1011" t="inlineStr">
-        <is>
-          <t>Boyertown Park Disc Golf</t>
-        </is>
-      </c>
-      <c r="C1011" t="inlineStr">
-        <is>
-          <t>Boyertown</t>
-        </is>
-      </c>
-      <c r="D1011" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1011" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1011" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1011" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1011" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1012">
-      <c r="A1012" t="inlineStr">
-        <is>
-          <t>pa-branchwood-park</t>
-        </is>
-      </c>
-      <c r="B1012" t="inlineStr">
-        <is>
-          <t>Branchwood Park Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1012" t="inlineStr">
-        <is>
-          <t>Franconia</t>
-        </is>
-      </c>
-      <c r="D1012" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1012" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1012" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1012" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1012" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1013">
-      <c r="A1013" t="inlineStr">
-        <is>
-          <t>pa-briar-creek-lak</t>
-        </is>
-      </c>
-      <c r="B1013" t="inlineStr">
-        <is>
-          <t>Briar Creek Lake</t>
-        </is>
-      </c>
-      <c r="C1013" t="inlineStr">
-        <is>
-          <t>Berwick</t>
-        </is>
-      </c>
-      <c r="D1013" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1013" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1013" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1013" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1013" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1014">
-      <c r="A1014" t="inlineStr">
-        <is>
-          <t>pa-broken-chains-d</t>
-        </is>
-      </c>
-      <c r="B1014" t="inlineStr">
-        <is>
-          <t>Broken Chains Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1014" t="inlineStr">
-        <is>
-          <t>Lincoln University</t>
-        </is>
-      </c>
-      <c r="D1014" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1014" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1014" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1014" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1014" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1015">
-      <c r="A1015" t="inlineStr">
-        <is>
-          <t>pa-brubaker-park</t>
-        </is>
-      </c>
-      <c r="B1015" t="inlineStr">
-        <is>
-          <t>Brubaker Park</t>
-        </is>
-      </c>
-      <c r="C1015" t="inlineStr">
-        <is>
-          <t>East Earl</t>
-        </is>
-      </c>
-      <c r="D1015" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1015" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1015" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1015" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1015" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1016">
-      <c r="A1016" t="inlineStr">
-        <is>
-          <t>pa-brush-creek-par</t>
-        </is>
-      </c>
-      <c r="B1016" t="inlineStr">
-        <is>
-          <t>Brush Creek Park Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1016" t="inlineStr">
-        <is>
-          <t>Beaver Falls</t>
-        </is>
-      </c>
-      <c r="D1016" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1016" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1016" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1016" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1016" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1017">
-      <c r="A1017" t="inlineStr">
-        <is>
-          <t>pa-buhl-park-disc-</t>
-        </is>
-      </c>
-      <c r="B1017" t="inlineStr">
-        <is>
-          <t>Buhl Park Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1017" t="inlineStr">
-        <is>
-          <t>Hermitage</t>
-        </is>
-      </c>
-      <c r="D1017" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1017" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1017" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1017" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1017" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1018">
-      <c r="A1018" t="inlineStr">
-        <is>
-          <t>pa-butler-farm</t>
-        </is>
-      </c>
-      <c r="B1018" t="inlineStr">
-        <is>
-          <t>Butler Farm</t>
-        </is>
-      </c>
-      <c r="C1018" t="inlineStr">
-        <is>
-          <t>Waynesburg</t>
-        </is>
-      </c>
-      <c r="D1018" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1018" t="n">
-        <v>20</v>
-      </c>
-      <c r="F1018" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1018" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1018" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1019">
-      <c r="A1019" t="inlineStr">
-        <is>
-          <t>pa-butter-valley-g</t>
-        </is>
-      </c>
-      <c r="B1019" t="inlineStr">
-        <is>
-          <t>Butter Valley Golf Port</t>
-        </is>
-      </c>
-      <c r="C1019" t="inlineStr">
-        <is>
-          <t>Barto</t>
-        </is>
-      </c>
-      <c r="D1019" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1019" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1019" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1019" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1019" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1020">
-      <c r="A1020" t="inlineStr">
-        <is>
-          <t>pa-california-univ</t>
-        </is>
-      </c>
-      <c r="B1020" t="inlineStr">
-        <is>
-          <t>California University of PA</t>
-        </is>
-      </c>
-      <c r="C1020" t="inlineStr">
-        <is>
-          <t>Coal Center</t>
-        </is>
-      </c>
-      <c r="D1020" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1020" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1020" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1020" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1020" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1021">
-      <c r="A1021" t="inlineStr">
-        <is>
-          <t>pa-camp-kon-o-kwee</t>
-        </is>
-      </c>
-      <c r="B1021" t="inlineStr">
-        <is>
-          <t>Camp Kon-O-Kwee</t>
-        </is>
-      </c>
-      <c r="C1021" t="inlineStr">
-        <is>
-          <t>Fombell</t>
-        </is>
-      </c>
-      <c r="D1021" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1021" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1021" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1021" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1021" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1022">
-      <c r="A1022" t="inlineStr">
-        <is>
-          <t>pa-camp-mt-luther</t>
-        </is>
-      </c>
-      <c r="B1022" t="inlineStr">
-        <is>
-          <t>Camp Mt. Luther Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1022" t="inlineStr">
-        <is>
-          <t>Mifflinburg</t>
-        </is>
-      </c>
-      <c r="D1022" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1022" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1022" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1022" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1022" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1023">
-      <c r="A1023" t="inlineStr">
-        <is>
-          <t>pa-camp-olympic-pa</t>
-        </is>
-      </c>
-      <c r="B1023" t="inlineStr">
-        <is>
-          <t>Camp Olympic Park</t>
-        </is>
-      </c>
-      <c r="C1023" t="inlineStr">
-        <is>
-          <t>Emmaus</t>
-        </is>
-      </c>
-      <c r="D1023" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1023" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1023" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1023" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1023" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1024">
-      <c r="A1024" t="inlineStr">
-        <is>
-          <t>pa-camp-sankanac-d</t>
-        </is>
-      </c>
-      <c r="B1024" t="inlineStr">
-        <is>
-          <t>Camp Sankanac Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1024" t="inlineStr">
-        <is>
-          <t>Spring City</t>
-        </is>
-      </c>
-      <c r="D1024" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1024" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1024" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1024" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1024" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1025">
-      <c r="A1025" t="inlineStr">
-        <is>
-          <t>pa-camp-swatara</t>
-        </is>
-      </c>
-      <c r="B1025" t="inlineStr">
-        <is>
-          <t>Camp Swatara</t>
-        </is>
-      </c>
-      <c r="C1025" t="inlineStr">
-        <is>
-          <t>Bethel</t>
-        </is>
-      </c>
-      <c r="D1025" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1025" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1025" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1025" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1025" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1026">
-      <c r="A1026" t="inlineStr">
-        <is>
-          <t>pa-canoe-creek-sta</t>
-        </is>
-      </c>
-      <c r="B1026" t="inlineStr">
-        <is>
-          <t>Canoe Creek State Park</t>
-        </is>
-      </c>
-      <c r="C1026" t="inlineStr">
-        <is>
-          <t>Hollidaysburg</t>
-        </is>
-      </c>
-      <c r="D1026" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1026" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1026" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1026" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1026" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1027">
-      <c r="A1027" t="inlineStr">
-        <is>
-          <t>pa-cbk-mountain-ad</t>
-        </is>
-      </c>
-      <c r="B1027" t="inlineStr">
-        <is>
-          <t>CBK Mountain Adventures Disc Golf</t>
-        </is>
-      </c>
-      <c r="C1027" t="inlineStr">
-        <is>
-          <t>Tannersville</t>
-        </is>
-      </c>
-      <c r="D1027" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1027" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1027" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1027" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1027" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1028">
-      <c r="A1028" t="inlineStr">
-        <is>
-          <t>pa-central-park-di</t>
-        </is>
-      </c>
-      <c r="B1028" t="inlineStr">
-        <is>
-          <t>Central Park Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1028" t="inlineStr">
-        <is>
-          <t>Doylestown</t>
-        </is>
-      </c>
-      <c r="D1028" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1028" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1028" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1028" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1028" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1029">
-      <c r="A1029" t="inlineStr">
-        <is>
-          <t>pa-circleville-par</t>
-        </is>
-      </c>
-      <c r="B1029" t="inlineStr">
-        <is>
-          <t>Circleville Park Disc Golf</t>
-        </is>
-      </c>
-      <c r="C1029" t="inlineStr">
-        <is>
-          <t>State College</t>
-        </is>
-      </c>
-      <c r="D1029" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1029" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1029" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1029" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1029" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1030">
-      <c r="A1030" t="inlineStr">
-        <is>
-          <t>pa-clarion-county-</t>
-        </is>
-      </c>
-      <c r="B1030" t="inlineStr">
-        <is>
-          <t>Clarion County Park Disc Golf</t>
-        </is>
-      </c>
-      <c r="C1030" t="inlineStr">
-        <is>
-          <t>Shippenville</t>
-        </is>
-      </c>
-      <c r="D1030" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1030" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1030" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1030" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1030" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1031">
-      <c r="A1031" t="inlineStr">
-        <is>
-          <t>pa-clarion-disc-go</t>
-        </is>
-      </c>
-      <c r="B1031" t="inlineStr">
-        <is>
-          <t>Clarion Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1031" t="inlineStr">
-        <is>
-          <t>Shippenville</t>
-        </is>
-      </c>
-      <c r="D1031" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1031" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1031" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1031" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1031" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1032">
-      <c r="A1032" t="inlineStr">
-        <is>
-          <t>pa-clear-creek-sta</t>
-        </is>
-      </c>
-      <c r="B1032" t="inlineStr">
-        <is>
-          <t>Clear Creek State Park</t>
-        </is>
-      </c>
-      <c r="C1032" t="inlineStr">
-        <is>
-          <t>Sigel</t>
-        </is>
-      </c>
-      <c r="D1032" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1032" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1032" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1032" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1032" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1033">
-      <c r="A1033" t="inlineStr">
-        <is>
-          <t>pa-clearview-eleme</t>
-        </is>
-      </c>
-      <c r="B1033" t="inlineStr">
-        <is>
-          <t>Clearview Elementary School Disc Golf</t>
-        </is>
-      </c>
-      <c r="C1033" t="inlineStr">
-        <is>
-          <t>Brogue</t>
-        </is>
-      </c>
-      <c r="D1033" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1033" t="n">
-        <v>5</v>
-      </c>
-      <c r="F1033" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1033" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1033" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1034">
-      <c r="A1034" t="inlineStr">
-        <is>
-          <t>pa-clemens-food-gr</t>
-        </is>
-      </c>
-      <c r="B1034" t="inlineStr">
-        <is>
-          <t>Clemens Food Group Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1034" t="inlineStr">
-        <is>
-          <t>Harfield</t>
-        </is>
-      </c>
-      <c r="D1034" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1034" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1034" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1034" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1034" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1035">
-      <c r="A1035" t="inlineStr">
-        <is>
-          <t>pa-codorus-state-p</t>
-        </is>
-      </c>
-      <c r="B1035" t="inlineStr">
-        <is>
-          <t>Codorus State Park - Blue</t>
-        </is>
-      </c>
-      <c r="C1035" t="inlineStr">
-        <is>
-          <t>Hanover</t>
-        </is>
-      </c>
-      <c r="D1035" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1035" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1035" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1035" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1035" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1036">
-      <c r="A1036" t="inlineStr">
-        <is>
-          <t>pa-codorus-state-p</t>
-        </is>
-      </c>
-      <c r="B1036" t="inlineStr">
-        <is>
-          <t>Codorus State Park - Purple</t>
-        </is>
-      </c>
-      <c r="C1036" t="inlineStr">
-        <is>
-          <t>Hanover</t>
-        </is>
-      </c>
-      <c r="D1036" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1036" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1036" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1036" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1036" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1037">
-      <c r="A1037" t="inlineStr">
-        <is>
-          <t>pa-codorus-state-p</t>
-        </is>
-      </c>
-      <c r="B1037" t="inlineStr">
-        <is>
-          <t>Codorus State Park - Red</t>
-        </is>
-      </c>
-      <c r="C1037" t="inlineStr">
-        <is>
-          <t>Hanover</t>
-        </is>
-      </c>
-      <c r="D1037" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1037" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1037" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1037" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1037" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1038">
-      <c r="A1038" t="inlineStr">
-        <is>
-          <t>pa-codorus-townshi</t>
-        </is>
-      </c>
-      <c r="B1038" t="inlineStr">
-        <is>
-          <t>Codorus Township Park</t>
-        </is>
-      </c>
-      <c r="C1038" t="inlineStr">
-        <is>
-          <t>Glen Rock</t>
-        </is>
-      </c>
-      <c r="D1038" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1038" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1038" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1038" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1038" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1039">
-      <c r="A1039" t="inlineStr">
-        <is>
-          <t>pa-coleman-memoria</t>
-        </is>
-      </c>
-      <c r="B1039" t="inlineStr">
-        <is>
-          <t>Coleman Memorial Park</t>
-        </is>
-      </c>
-      <c r="C1039" t="inlineStr">
-        <is>
-          <t>Lebanon</t>
-        </is>
-      </c>
-      <c r="D1039" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1039" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1039" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1039" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1039" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1040">
-      <c r="A1040" t="inlineStr">
-        <is>
-          <t>pa-conestoga-creek</t>
-        </is>
-      </c>
-      <c r="B1040" t="inlineStr">
-        <is>
-          <t>Conestoga Creek Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1040" t="inlineStr">
-        <is>
-          <t>Lancaster</t>
-        </is>
-      </c>
-      <c r="D1040" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1040" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1040" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1040" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1040" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1041">
-      <c r="A1041" t="inlineStr">
-        <is>
-          <t>pa-conrad-weiser-h</t>
-        </is>
-      </c>
-      <c r="B1041" t="inlineStr">
-        <is>
-          <t>Conrad Weiser Homestead</t>
-        </is>
-      </c>
-      <c r="C1041" t="inlineStr">
-        <is>
-          <t>Womelsdorf</t>
-        </is>
-      </c>
-      <c r="D1041" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1041" t="n">
-        <v>20</v>
-      </c>
-      <c r="F1041" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1041" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1041" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1042">
-      <c r="A1042" t="inlineStr">
-        <is>
-          <t>pa-cooley-crest-dg</t>
-        </is>
-      </c>
-      <c r="B1042" t="inlineStr">
-        <is>
-          <t>Cooley Crest DGC</t>
-        </is>
-      </c>
-      <c r="C1042" t="inlineStr">
-        <is>
-          <t>Centerville</t>
-        </is>
-      </c>
-      <c r="D1042" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1042" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1042" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1042" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1042" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1043">
-      <c r="A1043" t="inlineStr">
-        <is>
-          <t>pa-cove-valley-chr</t>
-        </is>
-      </c>
-      <c r="B1043" t="inlineStr">
-        <is>
-          <t>Cove Valley Christian Youth Camp</t>
-        </is>
-      </c>
-      <c r="C1043" t="inlineStr">
-        <is>
-          <t>Merscersburg</t>
-        </is>
-      </c>
-      <c r="D1043" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1043" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1043" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1043" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1043" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1044">
-      <c r="A1044" t="inlineStr">
-        <is>
-          <t>pa-covenant-villag</t>
-        </is>
-      </c>
-      <c r="B1044" t="inlineStr">
-        <is>
-          <t>Covenant Village Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1044" t="inlineStr">
-        <is>
-          <t>Clearville</t>
-        </is>
-      </c>
-      <c r="D1044" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1044" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1044" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1044" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1044" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1045">
-      <c r="A1045" t="inlineStr">
-        <is>
-          <t>pa-covered-bridge-</t>
-        </is>
-      </c>
-      <c r="B1045" t="inlineStr">
-        <is>
-          <t>Covered Bridge Park</t>
-        </is>
-      </c>
-      <c r="C1045" t="inlineStr">
-        <is>
-          <t>Orefield</t>
-        </is>
-      </c>
-      <c r="D1045" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1045" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1045" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1045" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1045" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1046">
-      <c r="A1046" t="inlineStr">
-        <is>
-          <t>pa-coyote-hills</t>
-        </is>
-      </c>
-      <c r="B1046" t="inlineStr">
-        <is>
-          <t>Coyote Hills</t>
-        </is>
-      </c>
-      <c r="C1046" t="inlineStr">
-        <is>
-          <t>Carlisle</t>
-        </is>
-      </c>
-      <c r="D1046" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1046" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1046" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1046" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1046" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1047">
-      <c r="A1047" t="inlineStr">
-        <is>
-          <t>pa-creekside-disc-</t>
-        </is>
-      </c>
-      <c r="B1047" t="inlineStr">
-        <is>
-          <t>Creekside Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1047" t="inlineStr">
-        <is>
-          <t>Camp Hill</t>
-        </is>
-      </c>
-      <c r="D1047" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1047" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1047" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1047" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1047" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1048">
-      <c r="A1048" t="inlineStr">
-        <is>
-          <t>pa-crestwood-high-</t>
-        </is>
-      </c>
-      <c r="B1048" t="inlineStr">
-        <is>
-          <t>Crestwood High School</t>
-        </is>
-      </c>
-      <c r="C1048" t="inlineStr">
-        <is>
-          <t>Mountaintop</t>
-        </is>
-      </c>
-      <c r="D1048" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1048" t="n">
-        <v>6</v>
-      </c>
-      <c r="F1048" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1048" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1048" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1049">
-      <c r="A1049" t="inlineStr">
-        <is>
-          <t>pa-crooked-creek-l</t>
-        </is>
-      </c>
-      <c r="B1049" t="inlineStr">
-        <is>
-          <t>Crooked Creek Lake Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1049" t="inlineStr">
-        <is>
-          <t>Ford City</t>
-        </is>
-      </c>
-      <c r="D1049" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1049" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1049" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1049" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1049" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1050">
-      <c r="A1050" t="inlineStr">
-        <is>
-          <t>pa-cross-keys-comm</t>
-        </is>
-      </c>
-      <c r="B1050" t="inlineStr">
-        <is>
-          <t>Cross Keys Community Park</t>
-        </is>
-      </c>
-      <c r="C1050" t="inlineStr">
-        <is>
-          <t>New Oxford</t>
-        </is>
-      </c>
-      <c r="D1050" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1050" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1050" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1050" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1050" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1051">
-      <c r="A1051" t="inlineStr">
-        <is>
-          <t>pa-d-f-buchmille</t>
-        </is>
-      </c>
-      <c r="B1051" t="inlineStr">
-        <is>
-          <t>D. F. Buchmiller Park</t>
-        </is>
-      </c>
-      <c r="C1051" t="inlineStr">
-        <is>
-          <t>Lancaster</t>
-        </is>
-      </c>
-      <c r="D1051" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1051" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1051" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1051" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1051" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1052">
-      <c r="A1052" t="inlineStr">
-        <is>
-          <t>pa-deer-lakes-park</t>
-        </is>
-      </c>
-      <c r="B1052" t="inlineStr">
-        <is>
-          <t>Deer Lakes Park</t>
-        </is>
-      </c>
-      <c r="C1052" t="inlineStr">
-        <is>
-          <t>Tarentum</t>
-        </is>
-      </c>
-      <c r="D1052" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1052" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1052" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1052" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1052" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1053">
-      <c r="A1053" t="inlineStr">
-        <is>
-          <t>pa-denver-memorial</t>
-        </is>
-      </c>
-      <c r="B1053" t="inlineStr">
-        <is>
-          <t>Denver Memorial Park</t>
-        </is>
-      </c>
-      <c r="C1053" t="inlineStr">
-        <is>
-          <t>Denver</t>
-        </is>
-      </c>
-      <c r="D1053" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1053" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1053" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1053" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1053" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1054">
-      <c r="A1054" t="inlineStr">
-        <is>
-          <t>pa-dogwood-acres-c</t>
-        </is>
-      </c>
-      <c r="B1054" t="inlineStr">
-        <is>
-          <t>Dogwood Acres Campground</t>
-        </is>
-      </c>
-      <c r="C1054" t="inlineStr">
-        <is>
-          <t>Newville</t>
-        </is>
-      </c>
-      <c r="D1054" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1054" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1054" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1054" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1054" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1055">
-      <c r="A1055" t="inlineStr">
-        <is>
-          <t>pa-earl-township-c</t>
-        </is>
-      </c>
-      <c r="B1055" t="inlineStr">
-        <is>
-          <t>Earl Township Community Park</t>
-        </is>
-      </c>
-      <c r="C1055" t="inlineStr">
-        <is>
-          <t>Boyertown</t>
-        </is>
-      </c>
-      <c r="D1055" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1055" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1055" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1055" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1055" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1056">
-      <c r="A1056" t="inlineStr">
-        <is>
-          <t>pa-east-hanover-to</t>
-        </is>
-      </c>
-      <c r="B1056" t="inlineStr">
-        <is>
-          <t>East Hanover Township Community Park</t>
-        </is>
-      </c>
-      <c r="C1056" t="inlineStr">
-        <is>
-          <t>Grantville</t>
-        </is>
-      </c>
-      <c r="D1056" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1056" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1056" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1056" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1056" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1057">
-      <c r="A1057" t="inlineStr">
-        <is>
-          <t>pa-east-pike-lower</t>
-        </is>
-      </c>
-      <c r="B1057" t="inlineStr">
-        <is>
-          <t>East Pike Lower</t>
-        </is>
-      </c>
-      <c r="C1057" t="inlineStr">
-        <is>
-          <t>Indiana</t>
-        </is>
-      </c>
-      <c r="D1057" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1057" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1057" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1057" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1057" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1058">
-      <c r="A1058" t="inlineStr">
-        <is>
-          <t>pa-east-pike-upper</t>
-        </is>
-      </c>
-      <c r="B1058" t="inlineStr">
-        <is>
-          <t>East Pike Upper</t>
-        </is>
-      </c>
-      <c r="C1058" t="inlineStr">
-        <is>
-          <t>Indiana</t>
-        </is>
-      </c>
-      <c r="D1058" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1058" t="n">
-        <v>19</v>
-      </c>
-      <c r="F1058" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1058" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1058" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1059">
-      <c r="A1059" t="inlineStr">
-        <is>
-          <t>pa-edinboro-univer</t>
-        </is>
-      </c>
-      <c r="B1059" t="inlineStr">
-        <is>
-          <t>Edinboro University Royal Scots Disc Golf Links</t>
-        </is>
-      </c>
-      <c r="C1059" t="inlineStr">
-        <is>
-          <t>Edinboro</t>
-        </is>
-      </c>
-      <c r="D1059" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1059" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1059" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1059" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1059" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1060">
-      <c r="A1060" t="inlineStr">
-        <is>
-          <t>pa-elizabeth-towns</t>
-        </is>
-      </c>
-      <c r="B1060" t="inlineStr">
-        <is>
-          <t>Elizabeth Township Park</t>
-        </is>
-      </c>
-      <c r="C1060" t="inlineStr">
-        <is>
-          <t>Brickerville</t>
-        </is>
-      </c>
-      <c r="D1060" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1060" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1060" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1060" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1060" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1061">
-      <c r="A1061" t="inlineStr">
-        <is>
-          <t>pa-elizabethtown-c</t>
-        </is>
-      </c>
-      <c r="B1061" t="inlineStr">
-        <is>
-          <t>Elizabethtown College</t>
-        </is>
-      </c>
-      <c r="C1061" t="inlineStr">
-        <is>
-          <t>Elizabathtown</t>
-        </is>
-      </c>
-      <c r="D1061" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1061" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1061" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1061" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1061" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1062">
-      <c r="A1062" t="inlineStr">
-        <is>
-          <t>pa-eurana-park</t>
-        </is>
-      </c>
-      <c r="B1062" t="inlineStr">
-        <is>
-          <t>Eurana Park</t>
-        </is>
-      </c>
-      <c r="C1062" t="inlineStr">
-        <is>
-          <t>Weatherly</t>
-        </is>
-      </c>
-      <c r="D1062" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1062" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1062" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1062" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1062" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1063">
-      <c r="A1063" t="inlineStr">
-        <is>
-          <t>pa-fairview-park-d</t>
-        </is>
-      </c>
-      <c r="B1063" t="inlineStr">
-        <is>
-          <t>Fairview Park Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1063" t="inlineStr">
-        <is>
-          <t>Columbia</t>
-        </is>
-      </c>
-      <c r="D1063" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1063" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1063" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1063" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1063" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1064">
-      <c r="A1064" t="inlineStr">
-        <is>
-          <t>pa-farrandsville-p</t>
-        </is>
-      </c>
-      <c r="B1064" t="inlineStr">
-        <is>
-          <t>Farrandsville Park Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1064" t="inlineStr">
-        <is>
-          <t>Farrandsville</t>
-        </is>
-      </c>
-      <c r="D1064" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1064" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1064" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1064" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1064" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1065">
-      <c r="A1065" t="inlineStr">
-        <is>
-          <t>pa-faylor-lake-dis</t>
-        </is>
-      </c>
-      <c r="B1065" t="inlineStr">
-        <is>
-          <t>Faylor Lake DiscGolfPark</t>
-        </is>
-      </c>
-      <c r="C1065" t="inlineStr">
-        <is>
-          <t>Beaver Springs</t>
-        </is>
-      </c>
-      <c r="D1065" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1065" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1065" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1065" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1065" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1066">
-      <c r="A1066" t="inlineStr">
-        <is>
-          <t>pa-forest-hills-di</t>
-        </is>
-      </c>
-      <c r="B1066" t="inlineStr">
-        <is>
-          <t>Forest Hills DiscGolfPark</t>
-        </is>
-      </c>
-      <c r="C1066" t="inlineStr">
-        <is>
-          <t>Carlisle</t>
-        </is>
-      </c>
-      <c r="D1066" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1066" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1066" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1066" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1066" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1067">
-      <c r="A1067" t="inlineStr">
-        <is>
-          <t>pa-fort-washington</t>
-        </is>
-      </c>
-      <c r="B1067" t="inlineStr">
-        <is>
-          <t>Fort Washington State Park</t>
-        </is>
-      </c>
-      <c r="C1067" t="inlineStr">
-        <is>
-          <t>Fort Washington</t>
-        </is>
-      </c>
-      <c r="D1067" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1067" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1067" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1067" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1067" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1068">
-      <c r="A1068" t="inlineStr">
-        <is>
-          <t>pa-francis-e-walt</t>
-        </is>
-      </c>
-      <c r="B1068" t="inlineStr">
-        <is>
-          <t>Francis E. Walter Dam - Original</t>
-        </is>
-      </c>
-      <c r="C1068" t="inlineStr">
-        <is>
-          <t>White Haven</t>
-        </is>
-      </c>
-      <c r="D1068" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1068" t="n">
-        <v>20</v>
-      </c>
-      <c r="F1068" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1068" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1068" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1069">
-      <c r="A1069" t="inlineStr">
-        <is>
-          <t>pa-francis-e-walt</t>
-        </is>
-      </c>
-      <c r="B1069" t="inlineStr">
-        <is>
-          <t>Francis E. Walter Dam - Top</t>
-        </is>
-      </c>
-      <c r="C1069" t="inlineStr">
-        <is>
-          <t>White Haven</t>
-        </is>
-      </c>
-      <c r="D1069" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1069" t="n">
-        <v>17</v>
-      </c>
-      <c r="F1069" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1069" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1069" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1070">
-      <c r="A1070" t="inlineStr">
-        <is>
-          <t>pa-freedom-farms-p</t>
-        </is>
-      </c>
-      <c r="B1070" t="inlineStr">
-        <is>
-          <t>Freedom Farms Putt Patch</t>
-        </is>
-      </c>
-      <c r="C1070" t="inlineStr">
-        <is>
-          <t>Butler</t>
-        </is>
-      </c>
-      <c r="D1070" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1070" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1070" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1070" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1070" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1071">
-      <c r="A1071" t="inlineStr">
-        <is>
-          <t>pa-french-creek-st</t>
-        </is>
-      </c>
-      <c r="B1071" t="inlineStr">
-        <is>
-          <t>French Creek State Park</t>
-        </is>
-      </c>
-      <c r="C1071" t="inlineStr">
-        <is>
-          <t>Elverson</t>
-        </is>
-      </c>
-      <c r="D1071" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1071" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1071" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1071" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1071" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1072">
-      <c r="A1072" t="inlineStr">
-        <is>
-          <t>pa-getty-heights-p</t>
-        </is>
-      </c>
-      <c r="B1072" t="inlineStr">
-        <is>
-          <t>Getty Heights Park</t>
-        </is>
-      </c>
-      <c r="C1072" t="inlineStr">
-        <is>
-          <t>Indiana</t>
-        </is>
-      </c>
-      <c r="D1072" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1072" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1072" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1072" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1072" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1073">
-      <c r="A1073" t="inlineStr">
-        <is>
-          <t>pa-grove-city-disc</t>
-        </is>
-      </c>
-      <c r="B1073" t="inlineStr">
-        <is>
-          <t>Grove City Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1073" t="inlineStr">
-        <is>
-          <t>Grove City</t>
-        </is>
-      </c>
-      <c r="D1073" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1073" t="n">
-        <v>21</v>
-      </c>
-      <c r="F1073" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1073" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1073" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1074">
-      <c r="A1074" t="inlineStr">
-        <is>
-          <t>pa-hackett-park</t>
-        </is>
-      </c>
-      <c r="B1074" t="inlineStr">
-        <is>
-          <t>Hackett Park</t>
-        </is>
-      </c>
-      <c r="C1074" t="inlineStr">
-        <is>
-          <t>Easton</t>
-        </is>
-      </c>
-      <c r="D1074" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1074" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1074" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1074" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1074" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1075">
-      <c r="A1075" t="inlineStr">
-        <is>
-          <t>pa-hanover-townshi</t>
-        </is>
-      </c>
-      <c r="B1075" t="inlineStr">
-        <is>
-          <t>Hanover Township Community Center</t>
-        </is>
-      </c>
-      <c r="C1075" t="inlineStr">
-        <is>
-          <t>Bethlehem</t>
-        </is>
-      </c>
-      <c r="D1075" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1075" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1075" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1075" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1075" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1076">
-      <c r="A1076" t="inlineStr">
-        <is>
-          <t>pa-harcrest-park</t>
-        </is>
-      </c>
-      <c r="B1076" t="inlineStr">
-        <is>
-          <t>Harcrest Park</t>
-        </is>
-      </c>
-      <c r="C1076" t="inlineStr">
-        <is>
-          <t>Butler</t>
-        </is>
-      </c>
-      <c r="D1076" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1076" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1076" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1076" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1076" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1077">
-      <c r="A1077" t="inlineStr">
-        <is>
-          <t>pa-harmony-ridge-g</t>
-        </is>
-      </c>
-      <c r="B1077" t="inlineStr">
-        <is>
-          <t>Harmony Ridge Golf Club</t>
-        </is>
-      </c>
-      <c r="C1077" t="inlineStr">
-        <is>
-          <t>Ambridge</t>
-        </is>
-      </c>
-      <c r="D1077" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1077" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1077" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1077" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1077" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1078">
-      <c r="A1078" t="inlineStr">
-        <is>
-          <t>pa-harvest-fields</t>
-        </is>
-      </c>
-      <c r="B1078" t="inlineStr">
-        <is>
-          <t>Harvest Fields</t>
-        </is>
-      </c>
-      <c r="C1078" t="inlineStr">
-        <is>
-          <t>Boalsburg</t>
-        </is>
-      </c>
-      <c r="D1078" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1078" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1078" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1078" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1078" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1079">
-      <c r="A1079" t="inlineStr">
-        <is>
-          <t>pa-haverford-reser</t>
-        </is>
-      </c>
-      <c r="B1079" t="inlineStr">
-        <is>
-          <t>Haverford Reserve</t>
-        </is>
-      </c>
-      <c r="C1079" t="inlineStr">
-        <is>
-          <t>haverford</t>
-        </is>
-      </c>
-      <c r="D1079" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1079" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1079" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1079" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1079" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1080">
-      <c r="A1080" t="inlineStr">
-        <is>
-          <t>pa-herr-park-disc-</t>
-        </is>
-      </c>
-      <c r="B1080" t="inlineStr">
-        <is>
-          <t>Herr Park Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1080" t="inlineStr">
-        <is>
-          <t>Lancaster</t>
-        </is>
-      </c>
-      <c r="D1080" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1080" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1080" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1080" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1080" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1081">
-      <c r="A1081" t="inlineStr">
-        <is>
-          <t>pa-hickory-heights</t>
-        </is>
-      </c>
-      <c r="B1081" t="inlineStr">
-        <is>
-          <t>Hickory Heights Golf Course</t>
-        </is>
-      </c>
-      <c r="C1081" t="inlineStr">
-        <is>
-          <t>Spring Grove</t>
-        </is>
-      </c>
-      <c r="D1081" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1081" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1081" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1081" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1081" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1082">
-      <c r="A1082" t="inlineStr">
-        <is>
-          <t>pa-hickory-run-sta</t>
-        </is>
-      </c>
-      <c r="B1082" t="inlineStr">
-        <is>
-          <t>Hickory Run State Park</t>
-        </is>
-      </c>
-      <c r="C1082" t="inlineStr">
-        <is>
-          <t>White Haven</t>
-        </is>
-      </c>
-      <c r="D1082" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1082" t="n">
-        <v>19</v>
-      </c>
-      <c r="F1082" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1082" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1082" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1083">
-      <c r="A1083" t="inlineStr">
-        <is>
-          <t>pa-hidden-hollow-d</t>
-        </is>
-      </c>
-      <c r="B1083" t="inlineStr">
-        <is>
-          <t>Hidden Hollow Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1083" t="inlineStr">
-        <is>
-          <t>Dover</t>
-        </is>
-      </c>
-      <c r="D1083" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1083" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1083" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1083" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1083" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1084">
-      <c r="A1084" t="inlineStr">
-        <is>
-          <t>pa-highland-park</t>
-        </is>
-      </c>
-      <c r="B1084" t="inlineStr">
-        <is>
-          <t>Highland Park</t>
-        </is>
-      </c>
-      <c r="C1084" t="inlineStr">
-        <is>
-          <t>Altoona</t>
-        </is>
-      </c>
-      <c r="D1084" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1084" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1084" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1084" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1084" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1085">
-      <c r="A1085" t="inlineStr">
-        <is>
-          <t>pa-hobson-park-min</t>
-        </is>
-      </c>
-      <c r="B1085" t="inlineStr">
-        <is>
-          <t>Hobson Park Mini Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1085" t="inlineStr">
-        <is>
-          <t>Lancaster</t>
-        </is>
-      </c>
-      <c r="D1085" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1085" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1085" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1085" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1085" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1086">
-      <c r="A1086" t="inlineStr">
-        <is>
-          <t>pa-hollidaysburg-s</t>
-        </is>
-      </c>
-      <c r="B1086" t="inlineStr">
-        <is>
-          <t>Hollidaysburg School Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1086" t="inlineStr">
-        <is>
-          <t>Hollidaysburg</t>
-        </is>
-      </c>
-      <c r="D1086" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1086" t="n">
-        <v>12</v>
-      </c>
-      <c r="F1086" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1086" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1086" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1087">
-      <c r="A1087" t="inlineStr">
-        <is>
-          <t>pa-hometown-hollow</t>
-        </is>
-      </c>
-      <c r="B1087" t="inlineStr">
-        <is>
-          <t>Hometown Hollow at Ryan Memorial Park</t>
-        </is>
-      </c>
-      <c r="C1087" t="inlineStr">
-        <is>
-          <t>Tamaqua</t>
-        </is>
-      </c>
-      <c r="D1087" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1087" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1087" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1087" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1087" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1088">
-      <c r="A1088" t="inlineStr">
-        <is>
-          <t>pa-hotel-hershey</t>
-        </is>
-      </c>
-      <c r="B1088" t="inlineStr">
-        <is>
-          <t>Hotel Hershey</t>
-        </is>
-      </c>
-      <c r="C1088" t="inlineStr">
-        <is>
-          <t>Hershey</t>
-        </is>
-      </c>
-      <c r="D1088" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1088" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1088" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1088" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1088" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1089">
-      <c r="A1089" t="inlineStr">
-        <is>
-          <t>pa-hpc-disk-golf</t>
-        </is>
-      </c>
-      <c r="B1089" t="inlineStr">
-        <is>
-          <t>HPC Disk Golf</t>
-        </is>
-      </c>
-      <c r="C1089" t="inlineStr">
-        <is>
-          <t>gibsonia</t>
-        </is>
-      </c>
-      <c r="D1089" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1089" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1089" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1089" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1089" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1090">
-      <c r="A1090" t="inlineStr">
-        <is>
-          <t>pa-hunter-farm</t>
-        </is>
-      </c>
-      <c r="B1090" t="inlineStr">
-        <is>
-          <t>Hunter Farm</t>
-        </is>
-      </c>
-      <c r="C1090" t="inlineStr">
-        <is>
-          <t>Grove City</t>
-        </is>
-      </c>
-      <c r="D1090" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1090" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1090" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1090" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1090" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1091">
-      <c r="A1091" t="inlineStr">
-        <is>
-          <t>pa-indian-park-dis</t>
-        </is>
-      </c>
-      <c r="B1091" t="inlineStr">
-        <is>
-          <t>Indian Park Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1091" t="inlineStr">
-        <is>
-          <t>Montoursville</t>
-        </is>
-      </c>
-      <c r="D1091" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1091" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1091" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1091" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1091" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1092">
-      <c r="A1092" t="inlineStr">
-        <is>
-          <t>pa-iup-college-lod</t>
-        </is>
-      </c>
-      <c r="B1092" t="inlineStr">
-        <is>
-          <t>IUP College Lodge</t>
-        </is>
-      </c>
-      <c r="C1092" t="inlineStr">
-        <is>
-          <t>Indiana</t>
-        </is>
-      </c>
-      <c r="D1092" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1092" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1092" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1092" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1092" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1093">
-      <c r="A1093" t="inlineStr">
-        <is>
-          <t>pa-jackson-recreat</t>
-        </is>
-      </c>
-      <c r="B1093" t="inlineStr">
-        <is>
-          <t>Jackson Recreational Park Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1093" t="inlineStr">
-        <is>
-          <t>Myerstown</t>
-        </is>
-      </c>
-      <c r="D1093" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1093" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1093" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1093" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1093" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1094">
-      <c r="A1094" t="inlineStr">
-        <is>
-          <t>pa-jordan-creek-pa</t>
-        </is>
-      </c>
-      <c r="B1094" t="inlineStr">
-        <is>
-          <t>Jordan Creek Park</t>
-        </is>
-      </c>
-      <c r="C1094" t="inlineStr">
-        <is>
-          <t>Whitehall</t>
-        </is>
-      </c>
-      <c r="D1094" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1094" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1094" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1094" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1094" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1095">
-      <c r="A1095" t="inlineStr">
-        <is>
-          <t>pa-jumonville-camp</t>
-        </is>
-      </c>
-      <c r="B1095" t="inlineStr">
-        <is>
-          <t>Jumonville Camp &amp; Retreat Center</t>
-        </is>
-      </c>
-      <c r="C1095" t="inlineStr">
-        <is>
-          <t>Hopwood</t>
-        </is>
-      </c>
-      <c r="D1095" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1095" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1095" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1095" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1095" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1096">
-      <c r="A1096" t="inlineStr">
-        <is>
-          <t>pa-juniata-college</t>
-        </is>
-      </c>
-      <c r="B1096" t="inlineStr">
-        <is>
-          <t>Juniata College</t>
-        </is>
-      </c>
-      <c r="C1096" t="inlineStr">
-        <is>
-          <t>Huntingdon</t>
-        </is>
-      </c>
-      <c r="D1096" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1096" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1096" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1096" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1096" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1097">
-      <c r="A1097" t="inlineStr">
-        <is>
-          <t>pa-kenilworth-park</t>
-        </is>
-      </c>
-      <c r="B1097" t="inlineStr">
-        <is>
-          <t>Kenilworth Park</t>
-        </is>
-      </c>
-      <c r="C1097" t="inlineStr">
-        <is>
-          <t>Kenilworth</t>
-        </is>
-      </c>
-      <c r="D1097" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1097" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1097" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1097" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1097" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1098">
-      <c r="A1098" t="inlineStr">
-        <is>
-          <t>pa-kennedy-park-di</t>
-        </is>
-      </c>
-      <c r="B1098" t="inlineStr">
-        <is>
-          <t>Kennedy Park Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1098" t="inlineStr">
-        <is>
-          <t>Forest City</t>
-        </is>
-      </c>
-      <c r="D1098" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1098" t="n">
-        <v>12</v>
-      </c>
-      <c r="F1098" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1098" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1098" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1099">
-      <c r="A1099" t="inlineStr">
-        <is>
-          <t>pa-kerr-park</t>
-        </is>
-      </c>
-      <c r="B1099" t="inlineStr">
-        <is>
-          <t>Kerr Park</t>
-        </is>
-      </c>
-      <c r="C1099" t="inlineStr">
-        <is>
-          <t>Downingtown</t>
-        </is>
-      </c>
-      <c r="D1099" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1099" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1099" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1099" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1099" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1100">
-      <c r="A1100" t="inlineStr">
-        <is>
-          <t>pa-kirchenwald-cro</t>
-        </is>
-      </c>
-      <c r="B1100" t="inlineStr">
-        <is>
-          <t>Kirchenwald Crossing</t>
-        </is>
-      </c>
-      <c r="C1100" t="inlineStr">
-        <is>
-          <t>Palmyra</t>
-        </is>
-      </c>
-      <c r="D1100" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1100" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1100" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1100" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1100" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1101">
-      <c r="A1101" t="inlineStr">
-        <is>
-          <t>pa-klines-run-disc</t>
-        </is>
-      </c>
-      <c r="B1101" t="inlineStr">
-        <is>
-          <t>Klines Run Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1101" t="inlineStr">
-        <is>
-          <t>Wrightsville</t>
-        </is>
-      </c>
-      <c r="D1101" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1101" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1101" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1101" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1101" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1102">
-      <c r="A1102" t="inlineStr">
-        <is>
-          <t>pa-knob-hill-park</t>
-        </is>
-      </c>
-      <c r="B1102" t="inlineStr">
-        <is>
-          <t>Knob Hill Park</t>
-        </is>
-      </c>
-      <c r="C1102" t="inlineStr">
-        <is>
-          <t>Warrendale</t>
-        </is>
-      </c>
-      <c r="D1102" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1102" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1102" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1102" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1102" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1103">
-      <c r="A1103" t="inlineStr">
-        <is>
-          <t>pa-lakeside-discgo</t>
-        </is>
-      </c>
-      <c r="B1103" t="inlineStr">
-        <is>
-          <t>Lakeside DiscGolfPark</t>
-        </is>
-      </c>
-      <c r="C1103" t="inlineStr">
-        <is>
-          <t>Myerstown</t>
-        </is>
-      </c>
-      <c r="D1103" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1103" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1103" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1103" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1103" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1104">
-      <c r="A1104" t="inlineStr">
-        <is>
-          <t>pa-laserdome-mini-</t>
-        </is>
-      </c>
-      <c r="B1104" t="inlineStr">
-        <is>
-          <t>Laserdome Mini Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1104" t="inlineStr">
-        <is>
-          <t>Manheim</t>
-        </is>
-      </c>
-      <c r="D1104" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1104" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1104" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1104" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1104" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1105">
-      <c r="A1105" t="inlineStr">
-        <is>
-          <t>pa-laurelain-disc-</t>
-        </is>
-      </c>
-      <c r="B1105" t="inlineStr">
-        <is>
-          <t>Laurelain Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1105" t="inlineStr">
-        <is>
-          <t>Reading</t>
-        </is>
-      </c>
-      <c r="D1105" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1105" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1105" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1105" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1105" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1106">
-      <c r="A1106" t="inlineStr">
-        <is>
-          <t>pa-lehigh-valley-s</t>
-        </is>
-      </c>
-      <c r="B1106" t="inlineStr">
-        <is>
-          <t>Lehigh Valley Sportsfest Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1106" t="inlineStr">
-        <is>
-          <t>Allentown</t>
-        </is>
-      </c>
-      <c r="D1106" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1106" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1106" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1106" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1106" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1107">
-      <c r="A1107" t="inlineStr">
-        <is>
-          <t>pa-lenape-park-(sk</t>
-        </is>
-      </c>
-      <c r="B1107" t="inlineStr">
-        <is>
-          <t>Lenape Park (Skippack)</t>
-        </is>
-      </c>
-      <c r="C1107" t="inlineStr">
-        <is>
-          <t>Collegeville</t>
-        </is>
-      </c>
-      <c r="D1107" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1107" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1107" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1107" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1107" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1108">
-      <c r="A1108" t="inlineStr">
-        <is>
-          <t>pa-lenni-lenape-pa</t>
-        </is>
-      </c>
-      <c r="B1108" t="inlineStr">
-        <is>
-          <t>Lenni Lenape Park</t>
-        </is>
-      </c>
-      <c r="C1108" t="inlineStr">
-        <is>
-          <t>Lebanon</t>
-        </is>
-      </c>
-      <c r="D1108" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1108" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1108" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1108" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1108" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1109">
-      <c r="A1109" t="inlineStr">
-        <is>
-          <t>pa-lime-bluff-recr</t>
-        </is>
-      </c>
-      <c r="B1109" t="inlineStr">
-        <is>
-          <t>Lime Bluff Recreation Area</t>
-        </is>
-      </c>
-      <c r="C1109" t="inlineStr">
-        <is>
-          <t>Hughesville</t>
-        </is>
-      </c>
-      <c r="D1109" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1109" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1109" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1109" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1109" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1110">
-      <c r="A1110" t="inlineStr">
-        <is>
-          <t>pa-linbrook-park</t>
-        </is>
-      </c>
-      <c r="B1110" t="inlineStr">
-        <is>
-          <t>Linbrook Park</t>
-        </is>
-      </c>
-      <c r="C1110" t="inlineStr">
-        <is>
-          <t>Pittsburgh</t>
-        </is>
-      </c>
-      <c r="D1110" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1110" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1110" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1110" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1110" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1111">
-      <c r="A1111" t="inlineStr">
-        <is>
-          <t>pa-linesville-park</t>
-        </is>
-      </c>
-      <c r="B1111" t="inlineStr">
-        <is>
-          <t>Linesville Park</t>
-        </is>
-      </c>
-      <c r="C1111" t="inlineStr">
-        <is>
-          <t>White Haven</t>
-        </is>
-      </c>
-      <c r="D1111" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1111" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1111" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1111" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1111" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1112">
-      <c r="A1112" t="inlineStr">
-        <is>
-          <t>pa-little-chiques-</t>
-        </is>
-      </c>
-      <c r="B1112" t="inlineStr">
-        <is>
-          <t>Little Chiques Park</t>
-        </is>
-      </c>
-      <c r="C1112" t="inlineStr">
-        <is>
-          <t>Mount Joy</t>
-        </is>
-      </c>
-      <c r="D1112" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1112" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1112" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1112" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1112" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1113">
-      <c r="A1113" t="inlineStr">
-        <is>
-          <t>pa-little-lehigh-p</t>
-        </is>
-      </c>
-      <c r="B1113" t="inlineStr">
-        <is>
-          <t>Little Lehigh Parkway</t>
-        </is>
-      </c>
-      <c r="C1113" t="inlineStr">
-        <is>
-          <t>Allentown</t>
-        </is>
-      </c>
-      <c r="D1113" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1113" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1113" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1113" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1113" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1114">
-      <c r="A1114" t="inlineStr">
-        <is>
-          <t>pa-long-trout-wine</t>
-        </is>
-      </c>
-      <c r="B1114" t="inlineStr">
-        <is>
-          <t>Long Trout Winery</t>
-        </is>
-      </c>
-      <c r="C1114" t="inlineStr">
-        <is>
-          <t>Auburn</t>
-        </is>
-      </c>
-      <c r="D1114" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1114" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1114" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1114" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1114" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1115">
-      <c r="A1115" t="inlineStr">
-        <is>
-          <t>pa-mammoth-park</t>
-        </is>
-      </c>
-      <c r="B1115" t="inlineStr">
-        <is>
-          <t>Mammoth Park</t>
-        </is>
-      </c>
-      <c r="C1115" t="inlineStr">
-        <is>
-          <t>Mount Pleasant</t>
-        </is>
-      </c>
-      <c r="D1115" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1115" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1115" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1115" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1115" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1116">
-      <c r="A1116" t="inlineStr">
-        <is>
-          <t>pa-messiah-college</t>
-        </is>
-      </c>
-      <c r="B1116" t="inlineStr">
-        <is>
-          <t>Messiah College Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1116" t="inlineStr">
-        <is>
-          <t>Grantham</t>
-        </is>
-      </c>
-      <c r="D1116" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1116" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1116" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1116" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1116" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1117">
-      <c r="A1117" t="inlineStr">
-        <is>
-          <t>pa-messiah-lifeway</t>
-        </is>
-      </c>
-      <c r="B1117" t="inlineStr">
-        <is>
-          <t>Messiah Lifeways Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1117" t="inlineStr">
-        <is>
-          <t>Mechanicsburg</t>
-        </is>
-      </c>
-      <c r="D1117" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1117" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1117" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1117" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1117" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1118">
-      <c r="A1118" t="inlineStr">
-        <is>
-          <t>pa-midd-west-disc-</t>
-        </is>
-      </c>
-      <c r="B1118" t="inlineStr">
-        <is>
-          <t>Midd-West Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1118" t="inlineStr">
-        <is>
-          <t>Middleburg</t>
-        </is>
-      </c>
-      <c r="D1118" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1118" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1118" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1118" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1118" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1119">
-      <c r="A1119" t="inlineStr">
-        <is>
-          <t>pa-middle-smithfie</t>
-        </is>
-      </c>
-      <c r="B1119" t="inlineStr">
-        <is>
-          <t>Middle Smithfield Park at Echo Lake</t>
-        </is>
-      </c>
-      <c r="C1119" t="inlineStr">
-        <is>
-          <t>East Stroudsburg</t>
-        </is>
-      </c>
-      <c r="D1119" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1119" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1119" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1119" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1119" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1120">
-      <c r="A1120" t="inlineStr">
-        <is>
-          <t>pa-mini-disc-golf-</t>
-        </is>
-      </c>
-      <c r="B1120" t="inlineStr">
-        <is>
-          <t>Mini Disc Golf Course at Mushroom Manor</t>
-        </is>
-      </c>
-      <c r="C1120" t="inlineStr">
-        <is>
-          <t>Lancaster</t>
-        </is>
-      </c>
-      <c r="D1120" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1120" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1120" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1120" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1120" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1121">
-      <c r="A1121" t="inlineStr">
-        <is>
-          <t>pa-misericordia-un</t>
-        </is>
-      </c>
-      <c r="B1121" t="inlineStr">
-        <is>
-          <t>Misericordia University DIsc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1121" t="inlineStr">
-        <is>
-          <t>Dallas</t>
-        </is>
-      </c>
-      <c r="D1121" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1121" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1121" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1121" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1121" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1122">
-      <c r="A1122" t="inlineStr">
-        <is>
-          <t>pa-monroe-township</t>
-        </is>
-      </c>
-      <c r="B1122" t="inlineStr">
-        <is>
-          <t>Monroe Township PA Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1122" t="inlineStr">
-        <is>
-          <t>Mechanicsburg</t>
-        </is>
-      </c>
-      <c r="D1122" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1122" t="n">
-        <v>6</v>
-      </c>
-      <c r="F1122" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1122" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1122" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1123">
-      <c r="A1123" t="inlineStr">
-        <is>
-          <t>pa-monroeville-par</t>
-        </is>
-      </c>
-      <c r="B1123" t="inlineStr">
-        <is>
-          <t>Monroeville Park</t>
-        </is>
-      </c>
-      <c r="C1123" t="inlineStr">
-        <is>
-          <t>Monroeville</t>
-        </is>
-      </c>
-      <c r="D1123" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1123" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1123" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1123" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1123" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1124">
-      <c r="A1124" t="inlineStr">
-        <is>
-          <t>pa-moon-lake-park</t>
-        </is>
-      </c>
-      <c r="B1124" t="inlineStr">
-        <is>
-          <t>Moon Lake Park</t>
-        </is>
-      </c>
-      <c r="C1124" t="inlineStr">
-        <is>
-          <t>Hunlock Creek</t>
-        </is>
-      </c>
-      <c r="D1124" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1124" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1124" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1124" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1124" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1125">
-      <c r="A1125" t="inlineStr">
-        <is>
-          <t>pa-moore-township-</t>
-        </is>
-      </c>
-      <c r="B1125" t="inlineStr">
-        <is>
-          <t>Moore Township Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1125" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
-      <c r="D1125" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1125" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1125" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1125" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1125" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1126">
-      <c r="A1126" t="inlineStr">
-        <is>
-          <t>pa-moraine-state-p</t>
-        </is>
-      </c>
-      <c r="B1126" t="inlineStr">
-        <is>
-          <t>Moraine State Park Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1126" t="inlineStr">
-        <is>
-          <t>Portersville</t>
-        </is>
-      </c>
-      <c r="D1126" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1126" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1126" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1126" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1126" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1127">
-      <c r="A1127" t="inlineStr">
-        <is>
-          <t>pa-morrisons-cove-</t>
-        </is>
-      </c>
-      <c r="B1127" t="inlineStr">
-        <is>
-          <t>Morrisons Cove Memorial Park</t>
-        </is>
-      </c>
-      <c r="C1127" t="inlineStr">
-        <is>
-          <t>Martinsburg</t>
-        </is>
-      </c>
-      <c r="D1127" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1127" t="n">
-        <v>6</v>
-      </c>
-      <c r="F1127" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1127" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1127" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1128">
-      <c r="A1128" t="inlineStr">
-        <is>
-          <t>pa-mt-lebanon-cam</t>
-        </is>
-      </c>
-      <c r="B1128" t="inlineStr">
-        <is>
-          <t>Mt. Lebanon Camp Meeting</t>
-        </is>
-      </c>
-      <c r="C1128" t="inlineStr">
-        <is>
-          <t>Lebanon</t>
-        </is>
-      </c>
-      <c r="D1128" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1128" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1128" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1128" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1128" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1129">
-      <c r="A1129" t="inlineStr">
-        <is>
-          <t>pa-muddy-run-disc-</t>
-        </is>
-      </c>
-      <c r="B1129" t="inlineStr">
-        <is>
-          <t>Muddy Run Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1129" t="inlineStr">
-        <is>
-          <t>Holtwood</t>
-        </is>
-      </c>
-      <c r="D1129" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1129" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1129" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1129" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1129" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1130">
-      <c r="A1130" t="inlineStr">
-        <is>
-          <t>pa-nawakwa-woods-d</t>
-        </is>
-      </c>
-      <c r="B1130" t="inlineStr">
-        <is>
-          <t>Nawakwa Woods Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1130" t="inlineStr">
-        <is>
-          <t>Biglerville</t>
-        </is>
-      </c>
-      <c r="D1130" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1130" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1130" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1130" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1130" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1131">
-      <c r="A1131" t="inlineStr">
-        <is>
-          <t>pa-neff's-valley</t>
-        </is>
-      </c>
-      <c r="B1131" t="inlineStr">
-        <is>
-          <t>Neff's Valley</t>
-        </is>
-      </c>
-      <c r="C1131" t="inlineStr">
-        <is>
-          <t>Schnecksville</t>
-        </is>
-      </c>
-      <c r="D1131" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1131" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1131" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1131" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1131" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1132">
-      <c r="A1132" t="inlineStr">
-        <is>
-          <t>pa-nesbitt-park</t>
-        </is>
-      </c>
-      <c r="B1132" t="inlineStr">
-        <is>
-          <t>Nesbitt Park</t>
-        </is>
-      </c>
-      <c r="C1132" t="inlineStr">
-        <is>
-          <t>Wilkes-Barre</t>
-        </is>
-      </c>
-      <c r="D1132" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1132" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1132" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1132" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1132" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1133">
-      <c r="A1133" t="inlineStr">
-        <is>
-          <t>pa-new-hanover-com</t>
-        </is>
-      </c>
-      <c r="B1133" t="inlineStr">
-        <is>
-          <t>New Hanover Community Park</t>
-        </is>
-      </c>
-      <c r="C1133" t="inlineStr">
-        <is>
-          <t>Gilbertsville</t>
-        </is>
-      </c>
-      <c r="D1133" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1133" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1133" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1133" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1133" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1134">
-      <c r="A1134" t="inlineStr">
-        <is>
-          <t>pa-new-hopewell-di</t>
-        </is>
-      </c>
-      <c r="B1134" t="inlineStr">
-        <is>
-          <t>New Hopewell Disc Golf Course</t>
-        </is>
-      </c>
-      <c r="C1134" t="inlineStr">
-        <is>
-          <t>Shippensburg</t>
-        </is>
-      </c>
-      <c r="D1134" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1134" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1134" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1134" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1134" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1135">
-      <c r="A1135" t="inlineStr">
-        <is>
-          <t>pa-nockamixon-stat</t>
-        </is>
-      </c>
-      <c r="B1135" t="inlineStr">
-        <is>
-          <t>Nockamixon State Park</t>
-        </is>
-      </c>
-      <c r="C1135" t="inlineStr">
-        <is>
-          <t>Quakertown</t>
-        </is>
-      </c>
-      <c r="D1135" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1135" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1135" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1135" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1135" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1136">
-      <c r="A1136" t="inlineStr">
-        <is>
-          <t>pa-north-boundary-</t>
-        </is>
-      </c>
-      <c r="B1136" t="inlineStr">
-        <is>
-          <t>North Boundary - Learn-to-Play</t>
-        </is>
-      </c>
-      <c r="C1136" t="inlineStr">
-        <is>
-          <t>Cranberry Township</t>
-        </is>
-      </c>
-      <c r="D1136" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1136" t="n">
-        <v>6</v>
-      </c>
-      <c r="F1136" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1136" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1136" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="1137">
-      <c r="A1137" t="inlineStr">
-        <is>
-          <t>pa-north-boundary-</t>
-        </is>
-      </c>
-      <c r="B1137" t="inlineStr">
-        <is>
-          <t>North Boundary Disc Golf Complex - Championship</t>
-        </is>
-      </c>
-      <c r="C1137" t="inlineStr">
-        <is>
-          <t>Cranberry Township</t>
-        </is>
-      </c>
-      <c r="D1137" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="E1137" t="n">
-        <v>18</v>
-      </c>
-      <c r="F1137" t="n">
-        <v>40.5908</v>
-      </c>
-      <c r="G1137" t="n">
-        <v>-77.2098</v>
-      </c>
-      <c r="H1137" t="inlineStr">
-        <is>
-          <t>PDGA</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:K474"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Chains Course Catalog.xlsx
+++ b/data/Chains Course Catalog.xlsx
@@ -579,11 +579,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -595,12 +595,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pass 1: top 150 of 169 PDGA×DGS cross-verified courses (318 DGS-listed total). 19 verified remain — finish next pass.</t>
+          <t>Complete: 150 pass 1 + 20 pass 2 = 170 total. No per-hole data (option d); users add pars in-app.</t>
         </is>
       </c>
     </row>

--- a/data/Chains Course Catalog.xlsx
+++ b/data/Chains Course Catalog.xlsx
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>150</v>
+        <v>315</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -557,12 +557,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pass 1 of ~3: top 150 of 283 PDGA×DGS cross-verified courses (443 DGS-listed total). Continue next pass.</t>
+          <t>Pass 1+2: 165 + 150 new = 315 total. 66 pass 2 geocoded; 84 pending. Pass 3: ~14 remain of 329 PDGA-listed.</t>
         </is>
       </c>
     </row>
@@ -621,11 +621,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>None (0/70) — no compliant public per-hole source; users add pars in-app</t>
+          <t>None (0/30)</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pass 1 of ~3: top 70 of 393 DiscGolfScene-listed courses. Geo: city centroid. Continue next pass.</t>
+          <t>Pass 1 rebuild: 30 OSM courses recovered (original 70 lost). ~363 remain.</t>
         </is>
       </c>
     </row>
@@ -653,16 +653,31 @@
           <t>thin - revisit</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Revisit - state filter issue; found: 4-H Camp Riversite (Hingham)</t>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>69</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>None (0/69) — no compliant public per-hole source; users add pars in-app</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>5</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Pass 1: OSM Overpass (69 courses, precise lat/lng). ~50-100+ remain via PDGA cross-check (needs JS rendering).</t>
+        </is>
       </c>
     </row>
     <row r="7">

--- a/data/Chains Course Catalog.xlsx
+++ b/data/Chains Course Catalog.xlsx
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>315</v>
+        <v>270</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -562,7 +562,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pass 1+2: 165 + 150 new = 315 total. 66 pass 2 geocoded; 84 pending. Pass 3: ~14 remain of 329 PDGA-listed.</t>
+          <t>270/315 geocoded (85%); 45 small-town gaps remain. Geocoding pass 3 via Nominatim (top 8 cities).</t>
         </is>
       </c>
     </row>
